--- a/OWP.xlsx
+++ b/OWP.xlsx
@@ -2817,54 +2817,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2909,6 +2861,54 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4854,6 +4854,82 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2756647</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1616769</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13615147" y="7048501"/>
+          <a:ext cx="2756647" cy="1616768"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>3035709</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>1524001</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13615147" y="20753295"/>
+          <a:ext cx="3035709" cy="1524000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5246,25 +5322,25 @@
       <c r="R3" s="14"/>
     </row>
     <row r="4" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="55" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="15">
         <v>1</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="56" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="16" t="s">
@@ -5299,15 +5375,15 @@
       <c r="AA4" s="20"/>
     </row>
     <row r="5" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="15">
         <v>2</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
       <c r="H5" s="16" t="s">
         <v>30</v>
       </c>
@@ -5340,15 +5416,15 @@
       <c r="AA5" s="20"/>
     </row>
     <row r="6" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="52"/>
       <c r="C6" s="15">
         <v>3</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
       <c r="H6" s="16" t="s">
         <v>32</v>
       </c>
@@ -5381,12 +5457,12 @@
       <c r="AA6" s="20"/>
     </row>
     <row r="7" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="15">
         <v>4</v>
       </c>
-      <c r="D7" s="37"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="16" t="s">
         <v>34</v>
       </c>
@@ -5430,19 +5506,19 @@
       <c r="AA7" s="20"/>
     </row>
     <row r="8" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="15">
         <v>5</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="46" t="s">
+      <c r="D8" s="52"/>
+      <c r="E8" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="48" t="s">
+      <c r="G8" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="16" t="s">
@@ -5481,15 +5557,15 @@
       <c r="AA8" s="20"/>
     </row>
     <row r="9" spans="1:27" ht="150" customHeight="1">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="15">
         <v>6</v>
       </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
       <c r="H9" s="16" t="s">
         <v>41</v>
       </c>
@@ -5524,15 +5600,15 @@
       <c r="AA9" s="20"/>
     </row>
     <row r="10" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="15">
         <v>7</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="16" t="s">
         <v>44</v>
       </c>
@@ -5569,16 +5645,16 @@
       <c r="AA10" s="20"/>
     </row>
     <row r="11" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="55" t="s">
         <v>47</v>
       </c>
       <c r="C11" s="15">
         <v>1</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="51" t="s">
         <v>48</v>
       </c>
       <c r="E11" s="16" t="s">
@@ -5626,19 +5702,19 @@
       <c r="AA11" s="20"/>
     </row>
     <row r="12" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
+      <c r="A12" s="52"/>
+      <c r="B12" s="52"/>
       <c r="C12" s="15">
         <v>2</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="46" t="s">
+      <c r="D12" s="52"/>
+      <c r="E12" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="F12" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H12" s="16" t="s">
@@ -5677,15 +5753,15 @@
       <c r="AA12" s="20"/>
     </row>
     <row r="13" spans="1:27" ht="150" customHeight="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
+      <c r="A13" s="52"/>
+      <c r="B13" s="52"/>
       <c r="C13" s="15">
         <v>3</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
       <c r="H13" s="16" t="s">
         <v>41</v>
       </c>
@@ -5720,15 +5796,15 @@
       <c r="AA13" s="20"/>
     </row>
     <row r="14" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
+      <c r="A14" s="52"/>
+      <c r="B14" s="52"/>
       <c r="C14" s="15">
         <v>4</v>
       </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
       <c r="H14" s="16" t="s">
         <v>44</v>
       </c>
@@ -5765,12 +5841,12 @@
       <c r="AA14" s="20"/>
     </row>
     <row r="15" spans="1:27" ht="150" customHeight="1">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="22">
         <v>5</v>
       </c>
-      <c r="D15" s="40"/>
+      <c r="D15" s="53"/>
       <c r="E15" s="23" t="s">
         <v>57</v>
       </c>
@@ -5814,12 +5890,12 @@
       <c r="AA15" s="20"/>
     </row>
     <row r="16" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
+      <c r="A16" s="52"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="15">
         <v>6</v>
       </c>
-      <c r="D16" s="37"/>
+      <c r="D16" s="52"/>
       <c r="E16" s="16" t="s">
         <v>61</v>
       </c>
@@ -5861,12 +5937,12 @@
       <c r="AA16" s="20"/>
     </row>
     <row r="17" spans="1:27" ht="150" customHeight="1">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
+      <c r="A17" s="52"/>
+      <c r="B17" s="52"/>
       <c r="C17" s="15">
         <v>7</v>
       </c>
-      <c r="D17" s="37"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="25" t="s">
         <v>65</v>
       </c>
@@ -5883,7 +5959,7 @@
         <v>67</v>
       </c>
       <c r="J17" s="15"/>
-      <c r="K17" s="59"/>
+      <c r="K17" s="43"/>
       <c r="L17" s="17"/>
       <c r="M17" s="16"/>
       <c r="N17" s="18"/>
@@ -5908,12 +5984,12 @@
       <c r="AA17" s="20"/>
     </row>
     <row r="18" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
+      <c r="A18" s="52"/>
+      <c r="B18" s="52"/>
       <c r="C18" s="15">
         <v>8</v>
       </c>
-      <c r="D18" s="37"/>
+      <c r="D18" s="52"/>
       <c r="E18" s="25" t="s">
         <v>68</v>
       </c>
@@ -5957,12 +6033,12 @@
       <c r="AA18" s="18"/>
     </row>
     <row r="19" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A19" s="38"/>
-      <c r="B19" s="38"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="15">
         <v>9</v>
       </c>
-      <c r="D19" s="38"/>
+      <c r="D19" s="54"/>
       <c r="E19" s="25" t="s">
         <v>71</v>
       </c>
@@ -6004,16 +6080,16 @@
       <c r="AA19" s="18"/>
     </row>
     <row r="20" spans="1:27" ht="9.9499999999999993" customHeight="1">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B20" s="55" t="s">
         <v>75</v>
       </c>
       <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="51" t="s">
         <v>76</v>
       </c>
       <c r="E20" s="25" t="s">
@@ -6055,12 +6131,12 @@
       <c r="AA20" s="20"/>
     </row>
     <row r="21" spans="1:27" ht="9.9499999999999993" customHeight="1">
-      <c r="A21" s="37"/>
-      <c r="B21" s="37"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="52"/>
       <c r="C21" s="15">
         <v>2</v>
       </c>
-      <c r="D21" s="37"/>
+      <c r="D21" s="52"/>
       <c r="E21" s="25" t="s">
         <v>80</v>
       </c>
@@ -6100,12 +6176,12 @@
       <c r="AA21" s="20"/>
     </row>
     <row r="22" spans="1:27" ht="9.9499999999999993" customHeight="1">
-      <c r="A22" s="37"/>
-      <c r="B22" s="37"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
       <c r="C22" s="15">
         <v>3</v>
       </c>
-      <c r="D22" s="37"/>
+      <c r="D22" s="52"/>
       <c r="E22" s="25" t="s">
         <v>83</v>
       </c>
@@ -6145,12 +6221,12 @@
       <c r="AA22" s="20"/>
     </row>
     <row r="23" spans="1:27" ht="150" customHeight="1">
-      <c r="A23" s="37"/>
-      <c r="B23" s="37"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="15">
         <v>4</v>
       </c>
-      <c r="D23" s="37"/>
+      <c r="D23" s="52"/>
       <c r="E23" s="25" t="s">
         <v>86</v>
       </c>
@@ -6167,7 +6243,7 @@
         <v>88</v>
       </c>
       <c r="J23" s="15"/>
-      <c r="K23" s="59"/>
+      <c r="K23" s="43"/>
       <c r="L23" s="17"/>
       <c r="M23" s="16"/>
       <c r="N23" s="18"/>
@@ -6190,12 +6266,12 @@
       <c r="AA23" s="20"/>
     </row>
     <row r="24" spans="1:27" ht="150" customHeight="1">
-      <c r="A24" s="37"/>
-      <c r="B24" s="37"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="52"/>
       <c r="C24" s="15">
         <v>5</v>
       </c>
-      <c r="D24" s="37"/>
+      <c r="D24" s="52"/>
       <c r="E24" s="25" t="s">
         <v>89</v>
       </c>
@@ -6212,7 +6288,7 @@
         <v>91</v>
       </c>
       <c r="J24" s="15"/>
-      <c r="K24" s="59"/>
+      <c r="K24" s="43"/>
       <c r="L24" s="17"/>
       <c r="M24" s="16"/>
       <c r="N24" s="18"/>
@@ -6235,29 +6311,29 @@
       <c r="AA24" s="20"/>
     </row>
     <row r="25" spans="1:27" ht="150" customHeight="1">
-      <c r="A25" s="37"/>
-      <c r="B25" s="37"/>
+      <c r="A25" s="52"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="15">
         <v>6</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="60" t="s">
+      <c r="D25" s="52"/>
+      <c r="E25" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="F25" s="61" t="s">
+      <c r="F25" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="H25" s="63" t="s">
+      <c r="H25" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="I25" s="64" t="s">
+      <c r="I25" s="48" t="s">
         <v>94</v>
       </c>
       <c r="J25" s="15"/>
-      <c r="K25" s="59"/>
+      <c r="K25" s="43"/>
       <c r="L25" s="17"/>
       <c r="M25" s="16"/>
       <c r="N25" s="18"/>
@@ -6280,22 +6356,22 @@
       <c r="AA25" s="20"/>
     </row>
     <row r="26" spans="1:27" ht="150" customHeight="1">
-      <c r="A26" s="37"/>
-      <c r="B26" s="37"/>
+      <c r="A26" s="52"/>
+      <c r="B26" s="52"/>
       <c r="C26" s="15">
         <v>7</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="49" t="s">
+      <c r="D26" s="52"/>
+      <c r="E26" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G26" s="48" t="s">
+      <c r="G26" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="46" t="s">
+      <c r="H26" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I26" s="16" t="s">
@@ -6327,16 +6403,16 @@
       <c r="AA26" s="20"/>
     </row>
     <row r="27" spans="1:27" ht="150" customHeight="1">
-      <c r="A27" s="37"/>
-      <c r="B27" s="37"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="15">
         <v>8</v>
       </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
       <c r="I27" s="16" t="s">
         <v>98</v>
       </c>
@@ -6366,16 +6442,16 @@
       <c r="AA27" s="20"/>
     </row>
     <row r="28" spans="1:27" ht="150" customHeight="1">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38"/>
+      <c r="A28" s="54"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="15">
         <v>9</v>
       </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
       <c r="I28" s="16" t="s">
         <v>99</v>
       </c>
@@ -6405,16 +6481,16 @@
       <c r="AA28" s="20"/>
     </row>
     <row r="29" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="55" t="s">
         <v>101</v>
       </c>
       <c r="C29" s="15">
         <v>1</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="51" t="s">
         <v>102</v>
       </c>
       <c r="E29" s="16" t="s">
@@ -6458,12 +6534,12 @@
       <c r="AA29" s="18"/>
     </row>
     <row r="30" spans="1:27" ht="150" customHeight="1">
-      <c r="A30" s="38"/>
-      <c r="B30" s="38"/>
+      <c r="A30" s="54"/>
+      <c r="B30" s="54"/>
       <c r="C30" s="15">
         <v>2</v>
       </c>
-      <c r="D30" s="38"/>
+      <c r="D30" s="54"/>
       <c r="E30" s="16" t="s">
         <v>106</v>
       </c>
@@ -6480,7 +6556,7 @@
         <v>108</v>
       </c>
       <c r="J30" s="15"/>
-      <c r="K30" s="59"/>
+      <c r="K30" s="43"/>
       <c r="L30" s="17"/>
       <c r="M30" s="16"/>
       <c r="N30" s="18"/>
@@ -6503,16 +6579,16 @@
       <c r="AA30" s="18"/>
     </row>
     <row r="31" spans="1:27" ht="150" customHeight="1">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="57" t="s">
         <v>110</v>
       </c>
       <c r="C31" s="9">
         <v>1</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="59" t="s">
         <v>109</v>
       </c>
       <c r="E31" s="27" t="s">
@@ -6531,7 +6607,7 @@
         <v>113</v>
       </c>
       <c r="J31" s="15"/>
-      <c r="K31" s="59"/>
+      <c r="K31" s="43"/>
       <c r="L31" s="17"/>
       <c r="M31" s="25"/>
       <c r="N31" s="20"/>
@@ -6554,12 +6630,12 @@
       <c r="AA31" s="20"/>
     </row>
     <row r="32" spans="1:27" ht="150" customHeight="1">
-      <c r="A32" s="37"/>
-      <c r="B32" s="37"/>
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
       <c r="C32" s="9">
         <v>2</v>
       </c>
-      <c r="D32" s="37"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="12" t="s">
         <v>114</v>
       </c>
@@ -6576,7 +6652,7 @@
         <v>116</v>
       </c>
       <c r="J32" s="15"/>
-      <c r="K32" s="59"/>
+      <c r="K32" s="43"/>
       <c r="L32" s="17"/>
       <c r="M32" s="25"/>
       <c r="N32" s="20"/>
@@ -6599,12 +6675,12 @@
       <c r="AA32" s="20"/>
     </row>
     <row r="33" spans="1:27" ht="150" customHeight="1">
-      <c r="A33" s="37"/>
-      <c r="B33" s="37"/>
+      <c r="A33" s="52"/>
+      <c r="B33" s="52"/>
       <c r="C33" s="9">
         <v>3</v>
       </c>
-      <c r="D33" s="37"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="12" t="s">
         <v>117</v>
       </c>
@@ -6621,7 +6697,7 @@
         <v>113</v>
       </c>
       <c r="J33" s="15"/>
-      <c r="K33" s="59"/>
+      <c r="K33" s="43"/>
       <c r="L33" s="17"/>
       <c r="M33" s="25"/>
       <c r="N33" s="20"/>
@@ -6644,12 +6720,12 @@
       <c r="AA33" s="20"/>
     </row>
     <row r="34" spans="1:27" ht="150" customHeight="1">
-      <c r="A34" s="37"/>
-      <c r="B34" s="37"/>
+      <c r="A34" s="52"/>
+      <c r="B34" s="52"/>
       <c r="C34" s="9">
         <v>4</v>
       </c>
-      <c r="D34" s="37"/>
+      <c r="D34" s="52"/>
       <c r="E34" s="12" t="s">
         <v>119</v>
       </c>
@@ -6666,7 +6742,7 @@
         <v>121</v>
       </c>
       <c r="J34" s="15"/>
-      <c r="K34" s="59"/>
+      <c r="K34" s="43"/>
       <c r="L34" s="17"/>
       <c r="M34" s="25"/>
       <c r="N34" s="20"/>
@@ -6689,12 +6765,12 @@
       <c r="AA34" s="20"/>
     </row>
     <row r="35" spans="1:27" ht="150" customHeight="1">
-      <c r="A35" s="37"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="52"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="9">
         <v>5</v>
       </c>
-      <c r="D35" s="37"/>
+      <c r="D35" s="52"/>
       <c r="E35" s="12" t="s">
         <v>122</v>
       </c>
@@ -6734,12 +6810,12 @@
       <c r="AA35" s="20"/>
     </row>
     <row r="36" spans="1:27" ht="150" customHeight="1">
-      <c r="A36" s="37"/>
-      <c r="B36" s="37"/>
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
       <c r="C36" s="9">
         <v>6</v>
       </c>
-      <c r="D36" s="37"/>
+      <c r="D36" s="52"/>
       <c r="E36" s="12" t="s">
         <v>124</v>
       </c>
@@ -6756,7 +6832,7 @@
         <v>121</v>
       </c>
       <c r="J36" s="15"/>
-      <c r="K36" s="59"/>
+      <c r="K36" s="43"/>
       <c r="L36" s="17"/>
       <c r="M36" s="25"/>
       <c r="N36" s="20"/>
@@ -6779,19 +6855,19 @@
       <c r="AA36" s="20"/>
     </row>
     <row r="37" spans="1:27" ht="150" customHeight="1">
-      <c r="A37" s="37"/>
-      <c r="B37" s="37"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="52"/>
       <c r="C37" s="9">
         <v>7</v>
       </c>
-      <c r="D37" s="37"/>
-      <c r="E37" s="36" t="s">
+      <c r="D37" s="52"/>
+      <c r="E37" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="F37" s="45" t="s">
+      <c r="F37" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="G37" s="44" t="s">
+      <c r="G37" s="58" t="s">
         <v>24</v>
       </c>
       <c r="H37" s="12" t="s">
@@ -6801,7 +6877,7 @@
         <v>128</v>
       </c>
       <c r="J37" s="15"/>
-      <c r="K37" s="59"/>
+      <c r="K37" s="43"/>
       <c r="L37" s="17"/>
       <c r="M37" s="25"/>
       <c r="N37" s="20"/>
@@ -6824,15 +6900,15 @@
       <c r="AA37" s="20"/>
     </row>
     <row r="38" spans="1:27" ht="150" customHeight="1">
-      <c r="A38" s="37"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
       <c r="C38" s="9">
         <v>8</v>
       </c>
-      <c r="D38" s="37"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
       <c r="H38" s="12" t="s">
         <v>129</v>
       </c>
@@ -6863,12 +6939,12 @@
       <c r="AA38" s="20"/>
     </row>
     <row r="39" spans="1:27" ht="150" customHeight="1">
-      <c r="A39" s="37"/>
-      <c r="B39" s="37"/>
+      <c r="A39" s="52"/>
+      <c r="B39" s="52"/>
       <c r="C39" s="9">
         <v>9</v>
       </c>
-      <c r="D39" s="37"/>
+      <c r="D39" s="52"/>
       <c r="E39" s="12" t="s">
         <v>131</v>
       </c>
@@ -6908,13 +6984,13 @@
       <c r="AA39" s="20"/>
     </row>
     <row r="40" spans="1:27" ht="150" customHeight="1">
-      <c r="A40" s="37"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="52"/>
+      <c r="B40" s="52"/>
       <c r="C40" s="9">
         <v>10</v>
       </c>
-      <c r="D40" s="37"/>
-      <c r="E40" s="36" t="s">
+      <c r="D40" s="52"/>
+      <c r="E40" s="59" t="s">
         <v>133</v>
       </c>
       <c r="F40" s="14" t="s">
@@ -6930,7 +7006,7 @@
         <v>135</v>
       </c>
       <c r="J40" s="15"/>
-      <c r="K40" s="59"/>
+      <c r="K40" s="43"/>
       <c r="L40" s="17"/>
       <c r="M40" s="25"/>
       <c r="N40" s="18"/>
@@ -6953,13 +7029,13 @@
       <c r="AA40" s="20"/>
     </row>
     <row r="41" spans="1:27" ht="150" customHeight="1">
-      <c r="A41" s="37"/>
-      <c r="B41" s="37"/>
+      <c r="A41" s="52"/>
+      <c r="B41" s="52"/>
       <c r="C41" s="9">
         <v>11</v>
       </c>
-      <c r="D41" s="37"/>
-      <c r="E41" s="38"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="54"/>
       <c r="F41" s="14" t="s">
         <v>23</v>
       </c>
@@ -6973,7 +7049,7 @@
         <v>137</v>
       </c>
       <c r="J41" s="15"/>
-      <c r="K41" s="59"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="17"/>
       <c r="M41" s="25"/>
       <c r="N41" s="18"/>
@@ -6996,12 +7072,12 @@
       <c r="AA41" s="20"/>
     </row>
     <row r="42" spans="1:27" ht="150" customHeight="1">
-      <c r="A42" s="37"/>
-      <c r="B42" s="37"/>
+      <c r="A42" s="52"/>
+      <c r="B42" s="52"/>
       <c r="C42" s="9">
         <v>12</v>
       </c>
-      <c r="D42" s="37"/>
+      <c r="D42" s="52"/>
       <c r="E42" s="27" t="s">
         <v>138</v>
       </c>
@@ -7018,7 +7094,7 @@
         <v>140</v>
       </c>
       <c r="J42" s="15"/>
-      <c r="K42" s="59"/>
+      <c r="K42" s="43"/>
       <c r="L42" s="17"/>
       <c r="M42" s="25"/>
       <c r="N42" s="20"/>
@@ -7041,12 +7117,12 @@
       <c r="AA42" s="20"/>
     </row>
     <row r="43" spans="1:27" ht="150" customHeight="1">
-      <c r="A43" s="37"/>
-      <c r="B43" s="37"/>
+      <c r="A43" s="52"/>
+      <c r="B43" s="52"/>
       <c r="C43" s="9">
         <v>13</v>
       </c>
-      <c r="D43" s="37"/>
+      <c r="D43" s="52"/>
       <c r="E43" s="12" t="s">
         <v>142</v>
       </c>
@@ -7063,7 +7139,7 @@
         <v>140</v>
       </c>
       <c r="J43" s="15"/>
-      <c r="K43" s="59"/>
+      <c r="K43" s="43"/>
       <c r="L43" s="17"/>
       <c r="M43" s="25"/>
       <c r="N43" s="18"/>
@@ -7086,12 +7162,12 @@
       <c r="AA43" s="20"/>
     </row>
     <row r="44" spans="1:27" ht="150" customHeight="1">
-      <c r="A44" s="37"/>
-      <c r="B44" s="37"/>
+      <c r="A44" s="52"/>
+      <c r="B44" s="52"/>
       <c r="C44" s="9">
         <v>14</v>
       </c>
-      <c r="D44" s="37"/>
+      <c r="D44" s="52"/>
       <c r="E44" s="12" t="s">
         <v>144</v>
       </c>
@@ -7108,7 +7184,7 @@
         <v>140</v>
       </c>
       <c r="J44" s="15"/>
-      <c r="K44" s="59"/>
+      <c r="K44" s="43"/>
       <c r="L44" s="17"/>
       <c r="M44" s="25"/>
       <c r="N44" s="18"/>
@@ -7131,12 +7207,12 @@
       <c r="AA44" s="20"/>
     </row>
     <row r="45" spans="1:27" ht="150" customHeight="1">
-      <c r="A45" s="37"/>
-      <c r="B45" s="37"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="52"/>
       <c r="C45" s="9">
         <v>15</v>
       </c>
-      <c r="D45" s="37"/>
+      <c r="D45" s="52"/>
       <c r="E45" s="12" t="s">
         <v>146</v>
       </c>
@@ -7153,7 +7229,7 @@
         <v>148</v>
       </c>
       <c r="J45" s="15"/>
-      <c r="K45" s="59"/>
+      <c r="K45" s="43"/>
       <c r="L45" s="17"/>
       <c r="M45" s="25"/>
       <c r="N45" s="18"/>
@@ -7176,12 +7252,12 @@
       <c r="AA45" s="20"/>
     </row>
     <row r="46" spans="1:27" ht="150" customHeight="1">
-      <c r="A46" s="37"/>
-      <c r="B46" s="37"/>
+      <c r="A46" s="52"/>
+      <c r="B46" s="52"/>
       <c r="C46" s="9">
         <v>16</v>
       </c>
-      <c r="D46" s="37"/>
+      <c r="D46" s="52"/>
       <c r="E46" s="12" t="s">
         <v>149</v>
       </c>
@@ -7221,12 +7297,12 @@
       <c r="AA46" s="20"/>
     </row>
     <row r="47" spans="1:27" ht="150" customHeight="1">
-      <c r="A47" s="37"/>
-      <c r="B47" s="37"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
       <c r="C47" s="9">
         <v>17</v>
       </c>
-      <c r="D47" s="37"/>
+      <c r="D47" s="52"/>
       <c r="E47" s="12" t="s">
         <v>151</v>
       </c>
@@ -7243,7 +7319,7 @@
         <v>148</v>
       </c>
       <c r="J47" s="15"/>
-      <c r="K47" s="59"/>
+      <c r="K47" s="43"/>
       <c r="L47" s="17"/>
       <c r="M47" s="25"/>
       <c r="N47" s="18"/>
@@ -7266,12 +7342,12 @@
       <c r="AA47" s="20"/>
     </row>
     <row r="48" spans="1:27" ht="150" customHeight="1">
-      <c r="A48" s="37"/>
-      <c r="B48" s="37"/>
+      <c r="A48" s="52"/>
+      <c r="B48" s="52"/>
       <c r="C48" s="9">
         <v>18</v>
       </c>
-      <c r="D48" s="37"/>
+      <c r="D48" s="52"/>
       <c r="E48" s="12" t="s">
         <v>153</v>
       </c>
@@ -7311,19 +7387,19 @@
       <c r="AA48" s="20"/>
     </row>
     <row r="49" spans="1:27" ht="150" customHeight="1">
-      <c r="A49" s="37"/>
-      <c r="B49" s="37"/>
+      <c r="A49" s="52"/>
+      <c r="B49" s="52"/>
       <c r="C49" s="9">
         <v>19</v>
       </c>
-      <c r="D49" s="37"/>
-      <c r="E49" s="36" t="s">
+      <c r="D49" s="52"/>
+      <c r="E49" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="F49" s="45" t="s">
+      <c r="F49" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="G49" s="44" t="s">
+      <c r="G49" s="58" t="s">
         <v>24</v>
       </c>
       <c r="H49" s="12" t="s">
@@ -7333,7 +7409,7 @@
         <v>128</v>
       </c>
       <c r="J49" s="15"/>
-      <c r="K49" s="59"/>
+      <c r="K49" s="43"/>
       <c r="L49" s="17"/>
       <c r="M49" s="25"/>
       <c r="N49" s="18"/>
@@ -7356,15 +7432,15 @@
       <c r="AA49" s="20"/>
     </row>
     <row r="50" spans="1:27" ht="150" customHeight="1">
-      <c r="A50" s="37"/>
-      <c r="B50" s="37"/>
+      <c r="A50" s="52"/>
+      <c r="B50" s="52"/>
       <c r="C50" s="9">
         <v>20</v>
       </c>
-      <c r="D50" s="37"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
       <c r="H50" s="12" t="s">
         <v>129</v>
       </c>
@@ -7395,13 +7471,13 @@
       <c r="AA50" s="20"/>
     </row>
     <row r="51" spans="1:27" ht="150" customHeight="1">
-      <c r="A51" s="37"/>
-      <c r="B51" s="37"/>
+      <c r="A51" s="52"/>
+      <c r="B51" s="52"/>
       <c r="C51" s="9">
         <v>21</v>
       </c>
-      <c r="D51" s="37"/>
-      <c r="E51" s="36" t="s">
+      <c r="D51" s="52"/>
+      <c r="E51" s="59" t="s">
         <v>156</v>
       </c>
       <c r="F51" s="14" t="s">
@@ -7417,7 +7493,7 @@
         <v>158</v>
       </c>
       <c r="J51" s="15"/>
-      <c r="K51" s="59"/>
+      <c r="K51" s="43"/>
       <c r="L51" s="17"/>
       <c r="M51" s="25"/>
       <c r="N51" s="18"/>
@@ -7440,13 +7516,13 @@
       <c r="AA51" s="20"/>
     </row>
     <row r="52" spans="1:27" ht="150" customHeight="1">
-      <c r="A52" s="37"/>
-      <c r="B52" s="37"/>
+      <c r="A52" s="52"/>
+      <c r="B52" s="52"/>
       <c r="C52" s="9">
         <v>22</v>
       </c>
-      <c r="D52" s="37"/>
-      <c r="E52" s="38"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="54"/>
       <c r="F52" s="14" t="s">
         <v>23</v>
       </c>
@@ -7460,7 +7536,7 @@
         <v>137</v>
       </c>
       <c r="J52" s="15"/>
-      <c r="K52" s="59"/>
+      <c r="K52" s="43"/>
       <c r="L52" s="17"/>
       <c r="M52" s="25"/>
       <c r="N52" s="18"/>
@@ -7483,12 +7559,12 @@
       <c r="AA52" s="20"/>
     </row>
     <row r="53" spans="1:27" ht="150" customHeight="1">
-      <c r="A53" s="37"/>
-      <c r="B53" s="37"/>
+      <c r="A53" s="52"/>
+      <c r="B53" s="52"/>
       <c r="C53" s="9">
         <v>23</v>
       </c>
-      <c r="D53" s="37"/>
+      <c r="D53" s="52"/>
       <c r="E53" s="28" t="s">
         <v>159</v>
       </c>
@@ -7528,13 +7604,13 @@
       <c r="AA53" s="20"/>
     </row>
     <row r="54" spans="1:27" ht="150" customHeight="1">
-      <c r="A54" s="37"/>
-      <c r="B54" s="37"/>
+      <c r="A54" s="52"/>
+      <c r="B54" s="52"/>
       <c r="C54" s="9">
         <v>24</v>
       </c>
-      <c r="D54" s="37"/>
-      <c r="E54" s="36" t="s">
+      <c r="D54" s="52"/>
+      <c r="E54" s="59" t="s">
         <v>162</v>
       </c>
       <c r="F54" s="14" t="s">
@@ -7550,7 +7626,7 @@
         <v>164</v>
       </c>
       <c r="J54" s="15"/>
-      <c r="K54" s="59"/>
+      <c r="K54" s="43"/>
       <c r="L54" s="17"/>
       <c r="M54" s="25"/>
       <c r="N54" s="18"/>
@@ -7573,13 +7649,13 @@
       <c r="AA54" s="20"/>
     </row>
     <row r="55" spans="1:27" ht="150" customHeight="1">
-      <c r="A55" s="37"/>
-      <c r="B55" s="37"/>
+      <c r="A55" s="52"/>
+      <c r="B55" s="52"/>
       <c r="C55" s="9">
         <v>25</v>
       </c>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
       <c r="F55" s="14" t="s">
         <v>62</v>
       </c>
@@ -7593,7 +7669,7 @@
         <v>164</v>
       </c>
       <c r="J55" s="15"/>
-      <c r="K55" s="59"/>
+      <c r="K55" s="43"/>
       <c r="L55" s="17"/>
       <c r="M55" s="25"/>
       <c r="N55" s="18"/>
@@ -7616,23 +7692,23 @@
       <c r="AA55" s="20"/>
     </row>
     <row r="56" spans="1:27" ht="150" customHeight="1">
-      <c r="A56" s="38"/>
-      <c r="B56" s="38"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
       <c r="C56" s="9">
         <v>26</v>
       </c>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
       <c r="F56" s="14" t="s">
         <v>62</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H56" s="65" t="s">
+      <c r="H56" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="I56" s="66" t="s">
+      <c r="I56" s="50" t="s">
         <v>167</v>
       </c>
       <c r="J56" s="15"/>
@@ -7659,16 +7735,16 @@
       <c r="AA56" s="20"/>
     </row>
     <row r="57" spans="1:27" ht="150" customHeight="1">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="B57" s="45" t="s">
+      <c r="B57" s="57" t="s">
         <v>169</v>
       </c>
       <c r="C57" s="9">
         <v>1</v>
       </c>
-      <c r="D57" s="36" t="s">
+      <c r="D57" s="59" t="s">
         <v>170</v>
       </c>
       <c r="E57" s="12" t="s">
@@ -7687,7 +7763,7 @@
         <v>173</v>
       </c>
       <c r="J57" s="15"/>
-      <c r="K57" s="59"/>
+      <c r="K57" s="43"/>
       <c r="L57" s="17"/>
       <c r="M57" s="16"/>
       <c r="N57" s="18"/>
@@ -7710,12 +7786,12 @@
       <c r="AA57" s="20"/>
     </row>
     <row r="58" spans="1:27" ht="150" customHeight="1">
-      <c r="A58" s="37"/>
-      <c r="B58" s="37"/>
+      <c r="A58" s="52"/>
+      <c r="B58" s="52"/>
       <c r="C58" s="9">
         <v>2</v>
       </c>
-      <c r="D58" s="37"/>
+      <c r="D58" s="52"/>
       <c r="E58" s="12" t="s">
         <v>174</v>
       </c>
@@ -7732,7 +7808,7 @@
         <v>173</v>
       </c>
       <c r="J58" s="15"/>
-      <c r="K58" s="59"/>
+      <c r="K58" s="43"/>
       <c r="L58" s="17"/>
       <c r="M58" s="16"/>
       <c r="N58" s="18"/>
@@ -7755,12 +7831,12 @@
       <c r="AA58" s="20"/>
     </row>
     <row r="59" spans="1:27" ht="150" customHeight="1">
-      <c r="A59" s="37"/>
-      <c r="B59" s="37"/>
+      <c r="A59" s="52"/>
+      <c r="B59" s="52"/>
       <c r="C59" s="9">
         <v>3</v>
       </c>
-      <c r="D59" s="37"/>
+      <c r="D59" s="52"/>
       <c r="E59" s="12" t="s">
         <v>176</v>
       </c>
@@ -7777,7 +7853,7 @@
         <v>173</v>
       </c>
       <c r="J59" s="15"/>
-      <c r="K59" s="59"/>
+      <c r="K59" s="43"/>
       <c r="L59" s="17"/>
       <c r="M59" s="16"/>
       <c r="N59" s="18"/>
@@ -7800,12 +7876,12 @@
       <c r="AA59" s="20"/>
     </row>
     <row r="60" spans="1:27" ht="150" customHeight="1">
-      <c r="A60" s="38"/>
-      <c r="B60" s="37"/>
+      <c r="A60" s="54"/>
+      <c r="B60" s="52"/>
       <c r="C60" s="9">
         <v>4</v>
       </c>
-      <c r="D60" s="37"/>
+      <c r="D60" s="52"/>
       <c r="E60" s="12" t="s">
         <v>178</v>
       </c>
@@ -7822,7 +7898,7 @@
         <v>173</v>
       </c>
       <c r="J60" s="15"/>
-      <c r="K60" s="59"/>
+      <c r="K60" s="43"/>
       <c r="L60" s="17"/>
       <c r="M60" s="16"/>
       <c r="N60" s="18"/>
@@ -7850,11 +7926,11 @@
       <c r="A61" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="B61" s="37"/>
+      <c r="B61" s="52"/>
       <c r="C61" s="9">
         <v>5</v>
       </c>
-      <c r="D61" s="37"/>
+      <c r="D61" s="52"/>
       <c r="E61" s="12" t="s">
         <v>181</v>
       </c>
@@ -7871,7 +7947,7 @@
         <v>173</v>
       </c>
       <c r="J61" s="15"/>
-      <c r="K61" s="59"/>
+      <c r="K61" s="43"/>
       <c r="L61" s="17"/>
       <c r="M61" s="16"/>
       <c r="N61" s="29"/>
@@ -7894,14 +7970,14 @@
       <c r="AA61" s="20"/>
     </row>
     <row r="62" spans="1:27" ht="150" customHeight="1">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="B62" s="37"/>
+      <c r="B62" s="52"/>
       <c r="C62" s="9">
         <v>6</v>
       </c>
-      <c r="D62" s="37"/>
+      <c r="D62" s="52"/>
       <c r="E62" s="12" t="s">
         <v>184</v>
       </c>
@@ -7918,7 +7994,7 @@
         <v>173</v>
       </c>
       <c r="J62" s="15"/>
-      <c r="K62" s="59"/>
+      <c r="K62" s="43"/>
       <c r="L62" s="17"/>
       <c r="M62" s="16"/>
       <c r="N62" s="18"/>
@@ -7941,12 +8017,12 @@
       <c r="AA62" s="20"/>
     </row>
     <row r="63" spans="1:27" ht="150" customHeight="1">
-      <c r="A63" s="38"/>
-      <c r="B63" s="38"/>
+      <c r="A63" s="54"/>
+      <c r="B63" s="54"/>
       <c r="C63" s="9">
         <v>7</v>
       </c>
-      <c r="D63" s="38"/>
+      <c r="D63" s="54"/>
       <c r="E63" s="12" t="s">
         <v>186</v>
       </c>
@@ -7963,7 +8039,7 @@
         <v>173</v>
       </c>
       <c r="J63" s="15"/>
-      <c r="K63" s="59"/>
+      <c r="K63" s="43"/>
       <c r="L63" s="17"/>
       <c r="M63" s="16"/>
       <c r="N63" s="18"/>
@@ -8007,25 +8083,25 @@
       <c r="R64" s="14"/>
     </row>
     <row r="65" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A65" s="46" t="s">
+      <c r="A65" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="B65" s="47" t="s">
+      <c r="B65" s="55" t="s">
         <v>190</v>
       </c>
       <c r="C65" s="15">
         <v>1</v>
       </c>
-      <c r="D65" s="46" t="s">
+      <c r="D65" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="E65" s="46" t="s">
+      <c r="E65" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="F65" s="47" t="s">
+      <c r="F65" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G65" s="48" t="s">
+      <c r="G65" s="56" t="s">
         <v>24</v>
       </c>
       <c r="H65" s="16" t="s">
@@ -8060,15 +8136,15 @@
       <c r="AA65" s="20"/>
     </row>
     <row r="66" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A66" s="37"/>
-      <c r="B66" s="37"/>
+      <c r="A66" s="52"/>
+      <c r="B66" s="52"/>
       <c r="C66" s="15">
         <v>2</v>
       </c>
-      <c r="D66" s="37"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38"/>
+      <c r="D66" s="52"/>
+      <c r="E66" s="54"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="54"/>
       <c r="H66" s="16" t="s">
         <v>195</v>
       </c>
@@ -8101,12 +8177,12 @@
       <c r="AA66" s="20"/>
     </row>
     <row r="67" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A67" s="37"/>
-      <c r="B67" s="37"/>
+      <c r="A67" s="52"/>
+      <c r="B67" s="52"/>
       <c r="C67" s="15">
         <v>3</v>
       </c>
-      <c r="D67" s="37"/>
+      <c r="D67" s="52"/>
       <c r="E67" s="16" t="s">
         <v>197</v>
       </c>
@@ -8150,10 +8226,10 @@
       <c r="AA67" s="20"/>
     </row>
     <row r="68" spans="1:27" ht="150" customHeight="1">
-      <c r="A68" s="40"/>
-      <c r="B68" s="40"/>
+      <c r="A68" s="53"/>
+      <c r="B68" s="53"/>
       <c r="C68" s="22"/>
-      <c r="D68" s="40"/>
+      <c r="D68" s="53"/>
       <c r="E68" s="23" t="s">
         <v>200</v>
       </c>
@@ -8191,13 +8267,13 @@
       <c r="AA68" s="20"/>
     </row>
     <row r="69" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A69" s="37"/>
-      <c r="B69" s="37"/>
+      <c r="A69" s="52"/>
+      <c r="B69" s="52"/>
       <c r="C69" s="15">
         <v>4</v>
       </c>
-      <c r="D69" s="37"/>
-      <c r="E69" s="46" t="s">
+      <c r="D69" s="52"/>
+      <c r="E69" s="51" t="s">
         <v>203</v>
       </c>
       <c r="F69" s="21" t="s">
@@ -8240,17 +8316,17 @@
       <c r="AA69" s="20"/>
     </row>
     <row r="70" spans="1:27" ht="150" customHeight="1">
-      <c r="A70" s="37"/>
-      <c r="B70" s="37"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="52"/>
       <c r="C70" s="15">
         <v>5</v>
       </c>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="47" t="s">
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G70" s="48" t="s">
+      <c r="G70" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H70" s="16" t="s">
@@ -8285,15 +8361,15 @@
       <c r="AA70" s="20"/>
     </row>
     <row r="71" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A71" s="37"/>
-      <c r="B71" s="37"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="52"/>
       <c r="C71" s="15">
         <v>6</v>
       </c>
-      <c r="D71" s="37"/>
-      <c r="E71" s="38"/>
-      <c r="F71" s="38"/>
-      <c r="G71" s="38"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="54"/>
+      <c r="F71" s="54"/>
+      <c r="G71" s="54"/>
       <c r="H71" s="16" t="s">
         <v>44</v>
       </c>
@@ -8328,19 +8404,19 @@
       <c r="AA71" s="20"/>
     </row>
     <row r="72" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A72" s="37"/>
-      <c r="B72" s="37"/>
+      <c r="A72" s="52"/>
+      <c r="B72" s="52"/>
       <c r="C72" s="15">
         <v>7</v>
       </c>
-      <c r="D72" s="37"/>
-      <c r="E72" s="46" t="s">
+      <c r="D72" s="52"/>
+      <c r="E72" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F72" s="47" t="s">
+      <c r="F72" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G72" s="48" t="s">
+      <c r="G72" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H72" s="16" t="s">
@@ -8377,15 +8453,15 @@
       <c r="AA72" s="20"/>
     </row>
     <row r="73" spans="1:27" ht="150" customHeight="1">
-      <c r="A73" s="37"/>
-      <c r="B73" s="37"/>
+      <c r="A73" s="52"/>
+      <c r="B73" s="52"/>
       <c r="C73" s="15">
         <v>8</v>
       </c>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
+      <c r="D73" s="52"/>
+      <c r="E73" s="52"/>
+      <c r="F73" s="52"/>
+      <c r="G73" s="52"/>
       <c r="H73" s="16" t="s">
         <v>41</v>
       </c>
@@ -8418,15 +8494,15 @@
       <c r="AA73" s="20"/>
     </row>
     <row r="74" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A74" s="37"/>
-      <c r="B74" s="37"/>
+      <c r="A74" s="52"/>
+      <c r="B74" s="52"/>
       <c r="C74" s="15">
         <v>9</v>
       </c>
-      <c r="D74" s="37"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
       <c r="H74" s="16" t="s">
         <v>44</v>
       </c>
@@ -8461,12 +8537,12 @@
       <c r="AA74" s="20"/>
     </row>
     <row r="75" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A75" s="37"/>
-      <c r="B75" s="37"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
       <c r="C75" s="15">
         <v>10</v>
       </c>
-      <c r="D75" s="37"/>
+      <c r="D75" s="52"/>
       <c r="E75" s="16" t="s">
         <v>213</v>
       </c>
@@ -8510,12 +8586,12 @@
       <c r="AA75" s="20"/>
     </row>
     <row r="76" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A76" s="37"/>
-      <c r="B76" s="37"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
       <c r="C76" s="15">
         <v>11</v>
       </c>
-      <c r="D76" s="37"/>
+      <c r="D76" s="52"/>
       <c r="E76" s="16" t="s">
         <v>216</v>
       </c>
@@ -8559,12 +8635,12 @@
       <c r="AA76" s="20"/>
     </row>
     <row r="77" spans="1:27" ht="150" customHeight="1">
-      <c r="A77" s="37"/>
-      <c r="B77" s="37"/>
+      <c r="A77" s="52"/>
+      <c r="B77" s="52"/>
       <c r="C77" s="15">
         <v>12</v>
       </c>
-      <c r="D77" s="37"/>
+      <c r="D77" s="52"/>
       <c r="E77" s="25" t="s">
         <v>219</v>
       </c>
@@ -8581,7 +8657,7 @@
         <v>221</v>
       </c>
       <c r="J77" s="15"/>
-      <c r="K77" s="59"/>
+      <c r="K77" s="43"/>
       <c r="L77" s="17"/>
       <c r="M77" s="16"/>
       <c r="N77" s="18"/>
@@ -8606,22 +8682,22 @@
       <c r="AA77" s="20"/>
     </row>
     <row r="78" spans="1:27" ht="150" customHeight="1">
-      <c r="A78" s="37"/>
-      <c r="B78" s="37"/>
+      <c r="A78" s="52"/>
+      <c r="B78" s="52"/>
       <c r="C78" s="15">
         <v>13</v>
       </c>
-      <c r="D78" s="37"/>
-      <c r="E78" s="49" t="s">
+      <c r="D78" s="52"/>
+      <c r="E78" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="F78" s="47" t="s">
+      <c r="F78" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G78" s="48" t="s">
+      <c r="G78" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="H78" s="46" t="s">
+      <c r="H78" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I78" s="16" t="s">
@@ -8653,16 +8729,16 @@
       <c r="AA78" s="20"/>
     </row>
     <row r="79" spans="1:27" ht="150" customHeight="1">
-      <c r="A79" s="37"/>
-      <c r="B79" s="37"/>
+      <c r="A79" s="52"/>
+      <c r="B79" s="52"/>
       <c r="C79" s="15">
         <v>14</v>
       </c>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
       <c r="I79" s="16" t="s">
         <v>223</v>
       </c>
@@ -8692,16 +8768,16 @@
       <c r="AA79" s="20"/>
     </row>
     <row r="80" spans="1:27" ht="150" customHeight="1">
-      <c r="A80" s="37"/>
-      <c r="B80" s="37"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="52"/>
       <c r="C80" s="15">
         <v>15</v>
       </c>
-      <c r="D80" s="37"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="54"/>
       <c r="I80" s="16" t="s">
         <v>99</v>
       </c>
@@ -8731,12 +8807,12 @@
       <c r="AA80" s="20"/>
     </row>
     <row r="81" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A81" s="38"/>
-      <c r="B81" s="38"/>
+      <c r="A81" s="54"/>
+      <c r="B81" s="54"/>
       <c r="C81" s="15">
         <v>16</v>
       </c>
-      <c r="D81" s="38"/>
+      <c r="D81" s="54"/>
       <c r="E81" s="25" t="s">
         <v>224</v>
       </c>
@@ -8778,19 +8854,19 @@
       <c r="AA81" s="20"/>
     </row>
     <row r="82" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A82" s="46" t="s">
+      <c r="A82" s="51" t="s">
         <v>227</v>
       </c>
-      <c r="B82" s="47" t="s">
+      <c r="B82" s="55" t="s">
         <v>228</v>
       </c>
       <c r="C82" s="15">
         <v>1</v>
       </c>
-      <c r="D82" s="46" t="s">
+      <c r="D82" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="E82" s="46" t="s">
+      <c r="E82" s="51" t="s">
         <v>229</v>
       </c>
       <c r="F82" s="21" t="s">
@@ -8831,17 +8907,17 @@
       <c r="AA82" s="20"/>
     </row>
     <row r="83" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A83" s="37"/>
-      <c r="B83" s="37"/>
+      <c r="A83" s="52"/>
+      <c r="B83" s="52"/>
       <c r="C83" s="15">
         <v>2</v>
       </c>
-      <c r="D83" s="37"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="47" t="s">
+      <c r="D83" s="52"/>
+      <c r="E83" s="52"/>
+      <c r="F83" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G83" s="48" t="s">
+      <c r="G83" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H83" s="16" t="s">
@@ -8876,15 +8952,15 @@
       <c r="AA83" s="20"/>
     </row>
     <row r="84" spans="1:27" ht="150" customHeight="1">
-      <c r="A84" s="37"/>
-      <c r="B84" s="37"/>
+      <c r="A84" s="52"/>
+      <c r="B84" s="52"/>
       <c r="C84" s="15">
         <v>3</v>
       </c>
-      <c r="D84" s="37"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="37"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="52"/>
+      <c r="G84" s="52"/>
       <c r="H84" s="16" t="s">
         <v>41</v>
       </c>
@@ -8915,15 +8991,15 @@
       <c r="AA84" s="20"/>
     </row>
     <row r="85" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A85" s="37"/>
-      <c r="B85" s="37"/>
+      <c r="A85" s="52"/>
+      <c r="B85" s="52"/>
       <c r="C85" s="15">
         <v>4</v>
       </c>
-      <c r="D85" s="37"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="38"/>
-      <c r="G85" s="38"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="54"/>
+      <c r="F85" s="54"/>
+      <c r="G85" s="54"/>
       <c r="H85" s="16" t="s">
         <v>44</v>
       </c>
@@ -8956,12 +9032,12 @@
       <c r="AA85" s="20"/>
     </row>
     <row r="86" spans="1:27" ht="150" customHeight="1">
-      <c r="A86" s="37"/>
-      <c r="B86" s="37"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="52"/>
       <c r="C86" s="15">
         <v>5</v>
       </c>
-      <c r="D86" s="37"/>
+      <c r="D86" s="52"/>
       <c r="E86" s="16" t="s">
         <v>235</v>
       </c>
@@ -8978,7 +9054,7 @@
         <v>237</v>
       </c>
       <c r="J86" s="15"/>
-      <c r="K86" s="59"/>
+      <c r="K86" s="43"/>
       <c r="L86" s="17"/>
       <c r="M86" s="16"/>
       <c r="N86" s="18"/>
@@ -9001,13 +9077,13 @@
       <c r="AA86" s="20"/>
     </row>
     <row r="87" spans="1:27" ht="150" customHeight="1">
-      <c r="A87" s="37"/>
-      <c r="B87" s="37"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
       <c r="C87" s="15">
         <v>6</v>
       </c>
-      <c r="D87" s="37"/>
-      <c r="E87" s="46" t="s">
+      <c r="D87" s="52"/>
+      <c r="E87" s="51" t="s">
         <v>238</v>
       </c>
       <c r="F87" s="21" t="s">
@@ -9023,7 +9099,7 @@
         <v>240</v>
       </c>
       <c r="J87" s="15"/>
-      <c r="K87" s="59"/>
+      <c r="K87" s="43"/>
       <c r="L87" s="17"/>
       <c r="M87" s="16"/>
       <c r="N87" s="18"/>
@@ -9046,13 +9122,13 @@
       <c r="AA87" s="20"/>
     </row>
     <row r="88" spans="1:27" ht="150" customHeight="1">
-      <c r="A88" s="37"/>
-      <c r="B88" s="37"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
       <c r="C88" s="15">
         <v>7</v>
       </c>
-      <c r="D88" s="37"/>
-      <c r="E88" s="38"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="54"/>
       <c r="F88" s="21" t="s">
         <v>62</v>
       </c>
@@ -9066,7 +9142,7 @@
         <v>240</v>
       </c>
       <c r="J88" s="15"/>
-      <c r="K88" s="59"/>
+      <c r="K88" s="43"/>
       <c r="L88" s="17"/>
       <c r="M88" s="16"/>
       <c r="N88" s="18"/>
@@ -9089,13 +9165,13 @@
       <c r="AA88" s="20"/>
     </row>
     <row r="89" spans="1:27" ht="150" customHeight="1">
-      <c r="A89" s="37"/>
-      <c r="B89" s="37"/>
+      <c r="A89" s="52"/>
+      <c r="B89" s="52"/>
       <c r="C89" s="15">
         <v>8</v>
       </c>
-      <c r="D89" s="37"/>
-      <c r="E89" s="46" t="s">
+      <c r="D89" s="52"/>
+      <c r="E89" s="51" t="s">
         <v>238</v>
       </c>
       <c r="F89" s="21" t="s">
@@ -9111,7 +9187,7 @@
         <v>240</v>
       </c>
       <c r="J89" s="15"/>
-      <c r="K89" s="59"/>
+      <c r="K89" s="43"/>
       <c r="L89" s="17"/>
       <c r="M89" s="16"/>
       <c r="N89" s="18"/>
@@ -9134,13 +9210,13 @@
       <c r="AA89" s="20"/>
     </row>
     <row r="90" spans="1:27" ht="150" customHeight="1">
-      <c r="A90" s="37"/>
-      <c r="B90" s="37"/>
+      <c r="A90" s="52"/>
+      <c r="B90" s="52"/>
       <c r="C90" s="15">
         <v>9</v>
       </c>
-      <c r="D90" s="37"/>
-      <c r="E90" s="38"/>
+      <c r="D90" s="52"/>
+      <c r="E90" s="54"/>
       <c r="F90" s="21" t="s">
         <v>62</v>
       </c>
@@ -9154,7 +9230,7 @@
         <v>240</v>
       </c>
       <c r="J90" s="15"/>
-      <c r="K90" s="59"/>
+      <c r="K90" s="43"/>
       <c r="L90" s="17"/>
       <c r="M90" s="16"/>
       <c r="N90" s="18"/>
@@ -9177,19 +9253,19 @@
       <c r="AA90" s="20"/>
     </row>
     <row r="91" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A91" s="37"/>
-      <c r="B91" s="37"/>
+      <c r="A91" s="52"/>
+      <c r="B91" s="52"/>
       <c r="C91" s="15">
         <v>10</v>
       </c>
-      <c r="D91" s="37"/>
-      <c r="E91" s="46" t="s">
+      <c r="D91" s="52"/>
+      <c r="E91" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="F91" s="47" t="s">
+      <c r="F91" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G91" s="48" t="s">
+      <c r="G91" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H91" s="16" t="s">
@@ -9224,15 +9300,15 @@
       <c r="AA91" s="20"/>
     </row>
     <row r="92" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A92" s="37"/>
-      <c r="B92" s="37"/>
+      <c r="A92" s="52"/>
+      <c r="B92" s="52"/>
       <c r="C92" s="15">
         <v>11</v>
       </c>
-      <c r="D92" s="37"/>
-      <c r="E92" s="38"/>
-      <c r="F92" s="38"/>
-      <c r="G92" s="38"/>
+      <c r="D92" s="52"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="54"/>
       <c r="H92" s="16" t="s">
         <v>247</v>
       </c>
@@ -9265,19 +9341,19 @@
       <c r="AA92" s="20"/>
     </row>
     <row r="93" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A93" s="37"/>
-      <c r="B93" s="37"/>
+      <c r="A93" s="52"/>
+      <c r="B93" s="52"/>
       <c r="C93" s="15">
         <v>12</v>
       </c>
-      <c r="D93" s="37"/>
-      <c r="E93" s="46" t="s">
+      <c r="D93" s="52"/>
+      <c r="E93" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="F93" s="47" t="s">
+      <c r="F93" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G93" s="48" t="s">
+      <c r="G93" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H93" s="16" t="s">
@@ -9312,15 +9388,15 @@
       <c r="AA93" s="20"/>
     </row>
     <row r="94" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A94" s="37"/>
-      <c r="B94" s="37"/>
+      <c r="A94" s="52"/>
+      <c r="B94" s="52"/>
       <c r="C94" s="15">
         <v>13</v>
       </c>
-      <c r="D94" s="37"/>
-      <c r="E94" s="38"/>
-      <c r="F94" s="38"/>
-      <c r="G94" s="38"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="54"/>
+      <c r="F94" s="54"/>
+      <c r="G94" s="54"/>
       <c r="H94" s="16" t="s">
         <v>247</v>
       </c>
@@ -9353,12 +9429,12 @@
       <c r="AA94" s="20"/>
     </row>
     <row r="95" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A95" s="38"/>
-      <c r="B95" s="38"/>
+      <c r="A95" s="54"/>
+      <c r="B95" s="54"/>
       <c r="C95" s="15">
         <v>14</v>
       </c>
-      <c r="D95" s="38"/>
+      <c r="D95" s="54"/>
       <c r="E95" s="25" t="s">
         <v>71</v>
       </c>
@@ -9400,25 +9476,25 @@
       <c r="AA95" s="20"/>
     </row>
     <row r="96" spans="1:27" ht="150" customHeight="1">
-      <c r="A96" s="46" t="s">
+      <c r="A96" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="B96" s="47" t="s">
+      <c r="B96" s="55" t="s">
         <v>255</v>
       </c>
       <c r="C96" s="15">
         <v>1</v>
       </c>
-      <c r="D96" s="46" t="s">
+      <c r="D96" s="51" t="s">
         <v>256</v>
       </c>
       <c r="E96" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="F96" s="47" t="s">
+      <c r="F96" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G96" s="48" t="s">
+      <c r="G96" s="56" t="s">
         <v>24</v>
       </c>
       <c r="H96" s="16" t="s">
@@ -9428,7 +9504,7 @@
         <v>259</v>
       </c>
       <c r="J96" s="15"/>
-      <c r="K96" s="59"/>
+      <c r="K96" s="43"/>
       <c r="L96" s="17"/>
       <c r="M96" s="16"/>
       <c r="N96" s="18"/>
@@ -9453,17 +9529,17 @@
       <c r="AA96" s="20"/>
     </row>
     <row r="97" spans="1:27" ht="150" customHeight="1">
-      <c r="A97" s="37"/>
-      <c r="B97" s="37"/>
+      <c r="A97" s="52"/>
+      <c r="B97" s="52"/>
       <c r="C97" s="15">
         <v>2</v>
       </c>
-      <c r="D97" s="37"/>
+      <c r="D97" s="52"/>
       <c r="E97" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="F97" s="37"/>
-      <c r="G97" s="37"/>
+      <c r="F97" s="52"/>
+      <c r="G97" s="52"/>
       <c r="H97" s="16" t="s">
         <v>258</v>
       </c>
@@ -9471,7 +9547,7 @@
         <v>261</v>
       </c>
       <c r="J97" s="15"/>
-      <c r="K97" s="59"/>
+      <c r="K97" s="43"/>
       <c r="L97" s="17"/>
       <c r="M97" s="16"/>
       <c r="N97" s="18"/>
@@ -9494,17 +9570,17 @@
       <c r="AA97" s="20"/>
     </row>
     <row r="98" spans="1:27" ht="150" customHeight="1">
-      <c r="A98" s="37"/>
-      <c r="B98" s="37"/>
+      <c r="A98" s="52"/>
+      <c r="B98" s="52"/>
       <c r="C98" s="15">
         <v>3</v>
       </c>
-      <c r="D98" s="37"/>
+      <c r="D98" s="52"/>
       <c r="E98" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="F98" s="37"/>
-      <c r="G98" s="37"/>
+      <c r="F98" s="52"/>
+      <c r="G98" s="52"/>
       <c r="H98" s="16" t="s">
         <v>258</v>
       </c>
@@ -9512,7 +9588,7 @@
         <v>263</v>
       </c>
       <c r="J98" s="15"/>
-      <c r="K98" s="59"/>
+      <c r="K98" s="43"/>
       <c r="L98" s="17"/>
       <c r="M98" s="16"/>
       <c r="N98" s="18"/>
@@ -9535,17 +9611,17 @@
       <c r="AA98" s="20"/>
     </row>
     <row r="99" spans="1:27" ht="150" customHeight="1">
-      <c r="A99" s="37"/>
-      <c r="B99" s="37"/>
+      <c r="A99" s="52"/>
+      <c r="B99" s="52"/>
       <c r="C99" s="15">
         <v>4</v>
       </c>
-      <c r="D99" s="37"/>
+      <c r="D99" s="52"/>
       <c r="E99" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="F99" s="37"/>
-      <c r="G99" s="37"/>
+      <c r="F99" s="52"/>
+      <c r="G99" s="52"/>
       <c r="H99" s="16" t="s">
         <v>258</v>
       </c>
@@ -9553,7 +9629,7 @@
         <v>265</v>
       </c>
       <c r="J99" s="15"/>
-      <c r="K99" s="59"/>
+      <c r="K99" s="43"/>
       <c r="L99" s="17"/>
       <c r="M99" s="16"/>
       <c r="N99" s="18"/>
@@ -9576,17 +9652,17 @@
       <c r="AA99" s="20"/>
     </row>
     <row r="100" spans="1:27" ht="150" customHeight="1">
-      <c r="A100" s="37"/>
-      <c r="B100" s="37"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="52"/>
       <c r="C100" s="15">
         <v>5</v>
       </c>
-      <c r="D100" s="37"/>
+      <c r="D100" s="52"/>
       <c r="E100" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="F100" s="37"/>
-      <c r="G100" s="37"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
       <c r="H100" s="16" t="s">
         <v>258</v>
       </c>
@@ -9594,7 +9670,7 @@
         <v>267</v>
       </c>
       <c r="J100" s="15"/>
-      <c r="K100" s="59"/>
+      <c r="K100" s="43"/>
       <c r="L100" s="17"/>
       <c r="M100" s="16"/>
       <c r="N100" s="18"/>
@@ -9617,17 +9693,17 @@
       <c r="AA100" s="20"/>
     </row>
     <row r="101" spans="1:27" ht="150" customHeight="1">
-      <c r="A101" s="37"/>
-      <c r="B101" s="37"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="52"/>
       <c r="C101" s="15">
         <v>6</v>
       </c>
-      <c r="D101" s="37"/>
+      <c r="D101" s="52"/>
       <c r="E101" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="F101" s="37"/>
-      <c r="G101" s="37"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
       <c r="H101" s="16" t="s">
         <v>258</v>
       </c>
@@ -9635,7 +9711,7 @@
         <v>269</v>
       </c>
       <c r="J101" s="15"/>
-      <c r="K101" s="59"/>
+      <c r="K101" s="43"/>
       <c r="L101" s="17"/>
       <c r="M101" s="16"/>
       <c r="N101" s="18"/>
@@ -9658,17 +9734,17 @@
       <c r="AA101" s="20"/>
     </row>
     <row r="102" spans="1:27" ht="150" customHeight="1">
-      <c r="A102" s="37"/>
-      <c r="B102" s="37"/>
+      <c r="A102" s="52"/>
+      <c r="B102" s="52"/>
       <c r="C102" s="15">
         <v>7</v>
       </c>
-      <c r="D102" s="37"/>
+      <c r="D102" s="52"/>
       <c r="E102" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="F102" s="37"/>
-      <c r="G102" s="37"/>
+      <c r="F102" s="52"/>
+      <c r="G102" s="52"/>
       <c r="H102" s="16" t="s">
         <v>258</v>
       </c>
@@ -9676,7 +9752,7 @@
         <v>271</v>
       </c>
       <c r="J102" s="15"/>
-      <c r="K102" s="59"/>
+      <c r="K102" s="43"/>
       <c r="L102" s="17"/>
       <c r="M102" s="16"/>
       <c r="N102" s="18"/>
@@ -9699,17 +9775,17 @@
       <c r="AA102" s="20"/>
     </row>
     <row r="103" spans="1:27" ht="150" customHeight="1">
-      <c r="A103" s="37"/>
-      <c r="B103" s="37"/>
+      <c r="A103" s="52"/>
+      <c r="B103" s="52"/>
       <c r="C103" s="15">
         <v>8</v>
       </c>
-      <c r="D103" s="37"/>
+      <c r="D103" s="52"/>
       <c r="E103" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="F103" s="37"/>
-      <c r="G103" s="37"/>
+      <c r="F103" s="52"/>
+      <c r="G103" s="52"/>
       <c r="H103" s="16" t="s">
         <v>258</v>
       </c>
@@ -9717,7 +9793,7 @@
         <v>273</v>
       </c>
       <c r="J103" s="15"/>
-      <c r="K103" s="59"/>
+      <c r="K103" s="43"/>
       <c r="L103" s="17"/>
       <c r="M103" s="16"/>
       <c r="N103" s="18"/>
@@ -9740,17 +9816,17 @@
       <c r="AA103" s="20"/>
     </row>
     <row r="104" spans="1:27" ht="150" customHeight="1">
-      <c r="A104" s="38"/>
-      <c r="B104" s="38"/>
+      <c r="A104" s="54"/>
+      <c r="B104" s="54"/>
       <c r="C104" s="15">
         <v>9</v>
       </c>
-      <c r="D104" s="38"/>
+      <c r="D104" s="54"/>
       <c r="E104" s="25" t="s">
         <v>274</v>
       </c>
-      <c r="F104" s="38"/>
-      <c r="G104" s="38"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="54"/>
       <c r="H104" s="16" t="s">
         <v>258</v>
       </c>
@@ -9758,7 +9834,7 @@
         <v>275</v>
       </c>
       <c r="J104" s="15"/>
-      <c r="K104" s="59"/>
+      <c r="K104" s="43"/>
       <c r="L104" s="17"/>
       <c r="M104" s="16"/>
       <c r="N104" s="18"/>
@@ -9783,22 +9859,22 @@
       <c r="AA104" s="20"/>
     </row>
     <row r="105" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A105" s="36" t="s">
+      <c r="A105" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="B105" s="45" t="s">
+      <c r="B105" s="57" t="s">
         <v>277</v>
       </c>
       <c r="C105" s="15">
         <v>1</v>
       </c>
-      <c r="D105" s="36" t="s">
+      <c r="D105" s="59" t="s">
         <v>278</v>
       </c>
-      <c r="E105" s="49" t="s">
+      <c r="E105" s="60" t="s">
         <v>279</v>
       </c>
-      <c r="F105" s="45" t="s">
+      <c r="F105" s="57" t="s">
         <v>23</v>
       </c>
       <c r="G105" s="9" t="s">
@@ -9836,14 +9912,14 @@
       <c r="AA105" s="20"/>
     </row>
     <row r="106" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A106" s="37"/>
-      <c r="B106" s="37"/>
+      <c r="A106" s="52"/>
+      <c r="B106" s="52"/>
       <c r="C106" s="15">
         <v>2</v>
       </c>
-      <c r="D106" s="37"/>
-      <c r="E106" s="37"/>
-      <c r="F106" s="38"/>
+      <c r="D106" s="52"/>
+      <c r="E106" s="52"/>
+      <c r="F106" s="54"/>
       <c r="G106" s="9" t="s">
         <v>38</v>
       </c>
@@ -9879,16 +9955,16 @@
       <c r="AA106" s="20"/>
     </row>
     <row r="107" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A107" s="37"/>
-      <c r="B107" s="37"/>
+      <c r="A107" s="52"/>
+      <c r="B107" s="52"/>
       <c r="C107" s="15">
         <v>3</v>
       </c>
-      <c r="D107" s="37"/>
-      <c r="E107" s="49" t="s">
+      <c r="D107" s="52"/>
+      <c r="E107" s="60" t="s">
         <v>284</v>
       </c>
-      <c r="F107" s="45" t="s">
+      <c r="F107" s="57" t="s">
         <v>23</v>
       </c>
       <c r="G107" s="9" t="s">
@@ -9926,14 +10002,14 @@
       <c r="AA107" s="20"/>
     </row>
     <row r="108" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A108" s="37"/>
-      <c r="B108" s="37"/>
+      <c r="A108" s="52"/>
+      <c r="B108" s="52"/>
       <c r="C108" s="15">
         <v>4</v>
       </c>
-      <c r="D108" s="37"/>
-      <c r="E108" s="37"/>
-      <c r="F108" s="38"/>
+      <c r="D108" s="52"/>
+      <c r="E108" s="52"/>
+      <c r="F108" s="54"/>
       <c r="G108" s="9" t="s">
         <v>38</v>
       </c>
@@ -9969,16 +10045,16 @@
       <c r="AA108" s="20"/>
     </row>
     <row r="109" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A109" s="37"/>
-      <c r="B109" s="37"/>
+      <c r="A109" s="52"/>
+      <c r="B109" s="52"/>
       <c r="C109" s="15">
         <v>5</v>
       </c>
-      <c r="D109" s="37"/>
-      <c r="E109" s="49" t="s">
+      <c r="D109" s="52"/>
+      <c r="E109" s="60" t="s">
         <v>287</v>
       </c>
-      <c r="F109" s="45" t="s">
+      <c r="F109" s="57" t="s">
         <v>23</v>
       </c>
       <c r="G109" s="9" t="s">
@@ -10016,14 +10092,14 @@
       <c r="AA109" s="20"/>
     </row>
     <row r="110" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A110" s="37"/>
-      <c r="B110" s="37"/>
+      <c r="A110" s="52"/>
+      <c r="B110" s="52"/>
       <c r="C110" s="15">
         <v>6</v>
       </c>
-      <c r="D110" s="37"/>
-      <c r="E110" s="37"/>
-      <c r="F110" s="38"/>
+      <c r="D110" s="52"/>
+      <c r="E110" s="52"/>
+      <c r="F110" s="54"/>
       <c r="G110" s="9" t="s">
         <v>38</v>
       </c>
@@ -10059,16 +10135,16 @@
       <c r="AA110" s="20"/>
     </row>
     <row r="111" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A111" s="37"/>
-      <c r="B111" s="37"/>
+      <c r="A111" s="52"/>
+      <c r="B111" s="52"/>
       <c r="C111" s="15">
         <v>7</v>
       </c>
-      <c r="D111" s="37"/>
-      <c r="E111" s="49" t="s">
+      <c r="D111" s="52"/>
+      <c r="E111" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="F111" s="45" t="s">
+      <c r="F111" s="57" t="s">
         <v>23</v>
       </c>
       <c r="G111" s="9" t="s">
@@ -10106,14 +10182,14 @@
       <c r="AA111" s="20"/>
     </row>
     <row r="112" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A112" s="37"/>
-      <c r="B112" s="37"/>
+      <c r="A112" s="52"/>
+      <c r="B112" s="52"/>
       <c r="C112" s="15">
         <v>8</v>
       </c>
-      <c r="D112" s="37"/>
-      <c r="E112" s="37"/>
-      <c r="F112" s="38"/>
+      <c r="D112" s="52"/>
+      <c r="E112" s="52"/>
+      <c r="F112" s="54"/>
       <c r="G112" s="9" t="s">
         <v>38</v>
       </c>
@@ -10149,16 +10225,16 @@
       <c r="AA112" s="20"/>
     </row>
     <row r="113" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A113" s="37"/>
-      <c r="B113" s="37"/>
+      <c r="A113" s="52"/>
+      <c r="B113" s="52"/>
       <c r="C113" s="15">
         <v>9</v>
       </c>
-      <c r="D113" s="37"/>
-      <c r="E113" s="49" t="s">
+      <c r="D113" s="52"/>
+      <c r="E113" s="60" t="s">
         <v>293</v>
       </c>
-      <c r="F113" s="45" t="s">
+      <c r="F113" s="57" t="s">
         <v>23</v>
       </c>
       <c r="G113" s="9" t="s">
@@ -10196,14 +10272,14 @@
       <c r="AA113" s="20"/>
     </row>
     <row r="114" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A114" s="37"/>
-      <c r="B114" s="37"/>
+      <c r="A114" s="52"/>
+      <c r="B114" s="52"/>
       <c r="C114" s="15">
         <v>10</v>
       </c>
-      <c r="D114" s="37"/>
-      <c r="E114" s="37"/>
-      <c r="F114" s="38"/>
+      <c r="D114" s="52"/>
+      <c r="E114" s="52"/>
+      <c r="F114" s="54"/>
       <c r="G114" s="9" t="s">
         <v>38</v>
       </c>
@@ -10239,22 +10315,22 @@
       <c r="AA114" s="20"/>
     </row>
     <row r="115" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A115" s="36" t="s">
+      <c r="A115" s="59" t="s">
         <v>296</v>
       </c>
-      <c r="B115" s="45" t="s">
+      <c r="B115" s="57" t="s">
         <v>297</v>
       </c>
       <c r="C115" s="9">
         <v>11</v>
       </c>
-      <c r="D115" s="36" t="s">
+      <c r="D115" s="59" t="s">
         <v>298</v>
       </c>
-      <c r="E115" s="51" t="s">
+      <c r="E115" s="61" t="s">
         <v>299</v>
       </c>
-      <c r="F115" s="45" t="s">
+      <c r="F115" s="57" t="s">
         <v>23</v>
       </c>
       <c r="G115" s="9" t="s">
@@ -10292,14 +10368,14 @@
       <c r="AA115" s="20"/>
     </row>
     <row r="116" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A116" s="37"/>
-      <c r="B116" s="37"/>
+      <c r="A116" s="52"/>
+      <c r="B116" s="52"/>
       <c r="C116" s="9">
         <v>12</v>
       </c>
-      <c r="D116" s="37"/>
-      <c r="E116" s="37"/>
-      <c r="F116" s="38"/>
+      <c r="D116" s="52"/>
+      <c r="E116" s="52"/>
+      <c r="F116" s="54"/>
       <c r="G116" s="9" t="s">
         <v>38</v>
       </c>
@@ -10339,16 +10415,16 @@
       <c r="AA116" s="20"/>
     </row>
     <row r="117" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A117" s="37"/>
-      <c r="B117" s="37"/>
+      <c r="A117" s="52"/>
+      <c r="B117" s="52"/>
       <c r="C117" s="9">
         <v>13</v>
       </c>
-      <c r="D117" s="37"/>
-      <c r="E117" s="51" t="s">
+      <c r="D117" s="52"/>
+      <c r="E117" s="61" t="s">
         <v>304</v>
       </c>
-      <c r="F117" s="45" t="s">
+      <c r="F117" s="57" t="s">
         <v>23</v>
       </c>
       <c r="G117" s="9" t="s">
@@ -10392,14 +10468,14 @@
       <c r="AA117" s="20"/>
     </row>
     <row r="118" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A118" s="37"/>
-      <c r="B118" s="37"/>
+      <c r="A118" s="52"/>
+      <c r="B118" s="52"/>
       <c r="C118" s="9">
         <v>14</v>
       </c>
-      <c r="D118" s="37"/>
-      <c r="E118" s="37"/>
-      <c r="F118" s="38"/>
+      <c r="D118" s="52"/>
+      <c r="E118" s="52"/>
+      <c r="F118" s="54"/>
       <c r="G118" s="9" t="s">
         <v>38</v>
       </c>
@@ -10439,16 +10515,16 @@
       <c r="AA118" s="20"/>
     </row>
     <row r="119" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A119" s="37"/>
-      <c r="B119" s="37"/>
+      <c r="A119" s="52"/>
+      <c r="B119" s="52"/>
       <c r="C119" s="9">
         <v>15</v>
       </c>
-      <c r="D119" s="37"/>
-      <c r="E119" s="51" t="s">
+      <c r="D119" s="52"/>
+      <c r="E119" s="61" t="s">
         <v>308</v>
       </c>
-      <c r="F119" s="45" t="s">
+      <c r="F119" s="57" t="s">
         <v>23</v>
       </c>
       <c r="G119" s="9" t="s">
@@ -10490,14 +10566,14 @@
       <c r="AA119" s="20"/>
     </row>
     <row r="120" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A120" s="38"/>
-      <c r="B120" s="38"/>
+      <c r="A120" s="54"/>
+      <c r="B120" s="54"/>
       <c r="C120" s="9">
         <v>16</v>
       </c>
-      <c r="D120" s="37"/>
-      <c r="E120" s="37"/>
-      <c r="F120" s="38"/>
+      <c r="D120" s="52"/>
+      <c r="E120" s="52"/>
+      <c r="F120" s="54"/>
       <c r="G120" s="9" t="s">
         <v>38</v>
       </c>
@@ -10537,25 +10613,25 @@
       <c r="AA120" s="20"/>
     </row>
     <row r="121" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A121" s="46" t="s">
+      <c r="A121" s="51" t="s">
         <v>310</v>
       </c>
-      <c r="B121" s="47" t="s">
+      <c r="B121" s="55" t="s">
         <v>311</v>
       </c>
       <c r="C121" s="15">
         <v>1</v>
       </c>
-      <c r="D121" s="46" t="s">
+      <c r="D121" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="E121" s="49" t="s">
+      <c r="E121" s="60" t="s">
         <v>313</v>
       </c>
-      <c r="F121" s="47" t="s">
+      <c r="F121" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G121" s="48" t="s">
+      <c r="G121" s="56" t="s">
         <v>24</v>
       </c>
       <c r="H121" s="16" t="s">
@@ -10590,15 +10666,15 @@
       <c r="AA121" s="20"/>
     </row>
     <row r="122" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A122" s="37"/>
-      <c r="B122" s="37"/>
+      <c r="A122" s="52"/>
+      <c r="B122" s="52"/>
       <c r="C122" s="15">
         <v>2</v>
       </c>
-      <c r="D122" s="37"/>
-      <c r="E122" s="37"/>
-      <c r="F122" s="37"/>
-      <c r="G122" s="37"/>
+      <c r="D122" s="52"/>
+      <c r="E122" s="52"/>
+      <c r="F122" s="52"/>
+      <c r="G122" s="52"/>
       <c r="H122" s="16" t="s">
         <v>317</v>
       </c>
@@ -10631,15 +10707,15 @@
       <c r="AA122" s="20"/>
     </row>
     <row r="123" spans="1:27" ht="150" customHeight="1">
-      <c r="A123" s="37"/>
-      <c r="B123" s="37"/>
+      <c r="A123" s="52"/>
+      <c r="B123" s="52"/>
       <c r="C123" s="15">
         <v>3</v>
       </c>
-      <c r="D123" s="37"/>
-      <c r="E123" s="37"/>
-      <c r="F123" s="37"/>
-      <c r="G123" s="37"/>
+      <c r="D123" s="52"/>
+      <c r="E123" s="52"/>
+      <c r="F123" s="52"/>
+      <c r="G123" s="52"/>
       <c r="H123" s="16" t="s">
         <v>41</v>
       </c>
@@ -10670,15 +10746,15 @@
       <c r="AA123" s="20"/>
     </row>
     <row r="124" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A124" s="37"/>
-      <c r="B124" s="37"/>
+      <c r="A124" s="52"/>
+      <c r="B124" s="52"/>
       <c r="C124" s="15">
         <v>4</v>
       </c>
-      <c r="D124" s="37"/>
-      <c r="E124" s="38"/>
-      <c r="F124" s="38"/>
-      <c r="G124" s="38"/>
+      <c r="D124" s="52"/>
+      <c r="E124" s="54"/>
+      <c r="F124" s="54"/>
+      <c r="G124" s="54"/>
       <c r="H124" s="16" t="s">
         <v>320</v>
       </c>
@@ -10711,19 +10787,19 @@
       <c r="AA124" s="20"/>
     </row>
     <row r="125" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A125" s="37"/>
-      <c r="B125" s="37"/>
+      <c r="A125" s="52"/>
+      <c r="B125" s="52"/>
       <c r="C125" s="15">
         <v>5</v>
       </c>
-      <c r="D125" s="37"/>
-      <c r="E125" s="49" t="s">
+      <c r="D125" s="52"/>
+      <c r="E125" s="60" t="s">
         <v>322</v>
       </c>
-      <c r="F125" s="47" t="s">
+      <c r="F125" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G125" s="48" t="s">
+      <c r="G125" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H125" s="16" t="s">
@@ -10758,15 +10834,15 @@
       <c r="AA125" s="20"/>
     </row>
     <row r="126" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A126" s="37"/>
-      <c r="B126" s="37"/>
+      <c r="A126" s="52"/>
+      <c r="B126" s="52"/>
       <c r="C126" s="15">
         <v>6</v>
       </c>
-      <c r="D126" s="37"/>
-      <c r="E126" s="37"/>
-      <c r="F126" s="37"/>
-      <c r="G126" s="37"/>
+      <c r="D126" s="52"/>
+      <c r="E126" s="52"/>
+      <c r="F126" s="52"/>
+      <c r="G126" s="52"/>
       <c r="H126" s="12" t="s">
         <v>325</v>
       </c>
@@ -10799,15 +10875,15 @@
       <c r="AA126" s="20"/>
     </row>
     <row r="127" spans="1:27" ht="150" customHeight="1">
-      <c r="A127" s="37"/>
-      <c r="B127" s="37"/>
+      <c r="A127" s="52"/>
+      <c r="B127" s="52"/>
       <c r="C127" s="15">
         <v>7</v>
       </c>
-      <c r="D127" s="37"/>
-      <c r="E127" s="37"/>
-      <c r="F127" s="37"/>
-      <c r="G127" s="37"/>
+      <c r="D127" s="52"/>
+      <c r="E127" s="52"/>
+      <c r="F127" s="52"/>
+      <c r="G127" s="52"/>
       <c r="H127" s="16" t="s">
         <v>41</v>
       </c>
@@ -10838,15 +10914,15 @@
       <c r="AA127" s="20"/>
     </row>
     <row r="128" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A128" s="37"/>
-      <c r="B128" s="37"/>
+      <c r="A128" s="52"/>
+      <c r="B128" s="52"/>
       <c r="C128" s="15">
         <v>8</v>
       </c>
-      <c r="D128" s="37"/>
-      <c r="E128" s="38"/>
-      <c r="F128" s="38"/>
-      <c r="G128" s="38"/>
+      <c r="D128" s="52"/>
+      <c r="E128" s="54"/>
+      <c r="F128" s="54"/>
+      <c r="G128" s="54"/>
       <c r="H128" s="16" t="s">
         <v>320</v>
       </c>
@@ -10879,19 +10955,19 @@
       <c r="AA128" s="20"/>
     </row>
     <row r="129" spans="1:27" ht="150" customHeight="1">
-      <c r="A129" s="37"/>
-      <c r="B129" s="37"/>
+      <c r="A129" s="52"/>
+      <c r="B129" s="52"/>
       <c r="C129" s="15">
         <v>9</v>
       </c>
-      <c r="D129" s="37"/>
-      <c r="E129" s="49" t="s">
+      <c r="D129" s="52"/>
+      <c r="E129" s="60" t="s">
         <v>329</v>
       </c>
-      <c r="F129" s="47" t="s">
+      <c r="F129" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G129" s="48" t="s">
+      <c r="G129" s="56" t="s">
         <v>24</v>
       </c>
       <c r="H129" s="16" t="s">
@@ -10901,7 +10977,7 @@
         <v>331</v>
       </c>
       <c r="J129" s="15"/>
-      <c r="K129" s="59"/>
+      <c r="K129" s="43"/>
       <c r="L129" s="17"/>
       <c r="M129" s="16"/>
       <c r="N129" s="18"/>
@@ -10924,15 +11000,15 @@
       <c r="AA129" s="20"/>
     </row>
     <row r="130" spans="1:27" ht="150" customHeight="1">
-      <c r="A130" s="37"/>
-      <c r="B130" s="37"/>
+      <c r="A130" s="52"/>
+      <c r="B130" s="52"/>
       <c r="C130" s="15">
         <v>10</v>
       </c>
-      <c r="D130" s="37"/>
-      <c r="E130" s="38"/>
-      <c r="F130" s="38"/>
-      <c r="G130" s="38"/>
+      <c r="D130" s="52"/>
+      <c r="E130" s="54"/>
+      <c r="F130" s="54"/>
+      <c r="G130" s="54"/>
       <c r="H130" s="16" t="s">
         <v>332</v>
       </c>
@@ -10940,7 +11016,7 @@
         <v>333</v>
       </c>
       <c r="J130" s="15"/>
-      <c r="K130" s="59"/>
+      <c r="K130" s="43"/>
       <c r="L130" s="17"/>
       <c r="M130" s="16"/>
       <c r="N130" s="18"/>
@@ -10963,19 +11039,19 @@
       <c r="AA130" s="20"/>
     </row>
     <row r="131" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A131" s="37"/>
-      <c r="B131" s="37"/>
+      <c r="A131" s="52"/>
+      <c r="B131" s="52"/>
       <c r="C131" s="15">
         <v>11</v>
       </c>
-      <c r="D131" s="37"/>
-      <c r="E131" s="49" t="s">
+      <c r="D131" s="52"/>
+      <c r="E131" s="60" t="s">
         <v>334</v>
       </c>
-      <c r="F131" s="47" t="s">
+      <c r="F131" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G131" s="48" t="s">
+      <c r="G131" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H131" s="16" t="s">
@@ -11010,15 +11086,15 @@
       <c r="AA131" s="20"/>
     </row>
     <row r="132" spans="1:27" ht="150" customHeight="1">
-      <c r="A132" s="37"/>
-      <c r="B132" s="37"/>
+      <c r="A132" s="52"/>
+      <c r="B132" s="52"/>
       <c r="C132" s="15">
         <v>12</v>
       </c>
-      <c r="D132" s="37"/>
-      <c r="E132" s="37"/>
-      <c r="F132" s="37"/>
-      <c r="G132" s="37"/>
+      <c r="D132" s="52"/>
+      <c r="E132" s="52"/>
+      <c r="F132" s="52"/>
+      <c r="G132" s="52"/>
       <c r="H132" s="16" t="s">
         <v>41</v>
       </c>
@@ -11049,15 +11125,15 @@
       <c r="AA132" s="20"/>
     </row>
     <row r="133" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A133" s="37"/>
-      <c r="B133" s="37"/>
+      <c r="A133" s="52"/>
+      <c r="B133" s="52"/>
       <c r="C133" s="15">
         <v>13</v>
       </c>
-      <c r="D133" s="38"/>
-      <c r="E133" s="38"/>
-      <c r="F133" s="38"/>
-      <c r="G133" s="38"/>
+      <c r="D133" s="54"/>
+      <c r="E133" s="54"/>
+      <c r="F133" s="54"/>
+      <c r="G133" s="54"/>
       <c r="H133" s="16" t="s">
         <v>320</v>
       </c>
@@ -11090,21 +11166,21 @@
       <c r="AA133" s="20"/>
     </row>
     <row r="134" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A134" s="37"/>
-      <c r="B134" s="37"/>
+      <c r="A134" s="52"/>
+      <c r="B134" s="52"/>
       <c r="C134" s="9">
         <v>14</v>
       </c>
-      <c r="D134" s="36" t="s">
+      <c r="D134" s="59" t="s">
         <v>337</v>
       </c>
-      <c r="E134" s="51" t="s">
+      <c r="E134" s="61" t="s">
         <v>313</v>
       </c>
-      <c r="F134" s="45" t="s">
+      <c r="F134" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="G134" s="44" t="s">
+      <c r="G134" s="58" t="s">
         <v>24</v>
       </c>
       <c r="H134" s="12" t="s">
@@ -11139,15 +11215,15 @@
       <c r="AA134" s="20"/>
     </row>
     <row r="135" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A135" s="37"/>
-      <c r="B135" s="37"/>
+      <c r="A135" s="52"/>
+      <c r="B135" s="52"/>
       <c r="C135" s="9">
         <v>15</v>
       </c>
-      <c r="D135" s="37"/>
-      <c r="E135" s="37"/>
-      <c r="F135" s="37"/>
-      <c r="G135" s="37"/>
+      <c r="D135" s="52"/>
+      <c r="E135" s="52"/>
+      <c r="F135" s="52"/>
+      <c r="G135" s="52"/>
       <c r="H135" s="12" t="s">
         <v>317</v>
       </c>
@@ -11180,15 +11256,15 @@
       <c r="AA135" s="20"/>
     </row>
     <row r="136" spans="1:27" ht="150" customHeight="1">
-      <c r="A136" s="37"/>
-      <c r="B136" s="37"/>
+      <c r="A136" s="52"/>
+      <c r="B136" s="52"/>
       <c r="C136" s="9">
         <v>16</v>
       </c>
-      <c r="D136" s="37"/>
-      <c r="E136" s="37"/>
-      <c r="F136" s="37"/>
-      <c r="G136" s="37"/>
+      <c r="D136" s="52"/>
+      <c r="E136" s="52"/>
+      <c r="F136" s="52"/>
+      <c r="G136" s="52"/>
       <c r="H136" s="12" t="s">
         <v>41</v>
       </c>
@@ -11219,15 +11295,15 @@
       <c r="AA136" s="20"/>
     </row>
     <row r="137" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A137" s="37"/>
-      <c r="B137" s="37"/>
+      <c r="A137" s="52"/>
+      <c r="B137" s="52"/>
       <c r="C137" s="9">
         <v>17</v>
       </c>
-      <c r="D137" s="37"/>
-      <c r="E137" s="38"/>
-      <c r="F137" s="38"/>
-      <c r="G137" s="38"/>
+      <c r="D137" s="52"/>
+      <c r="E137" s="54"/>
+      <c r="F137" s="54"/>
+      <c r="G137" s="54"/>
       <c r="H137" s="12" t="s">
         <v>320</v>
       </c>
@@ -11260,19 +11336,19 @@
       <c r="AA137" s="20"/>
     </row>
     <row r="138" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A138" s="37"/>
-      <c r="B138" s="37"/>
+      <c r="A138" s="52"/>
+      <c r="B138" s="52"/>
       <c r="C138" s="9">
         <v>18</v>
       </c>
-      <c r="D138" s="37"/>
-      <c r="E138" s="51" t="s">
+      <c r="D138" s="52"/>
+      <c r="E138" s="61" t="s">
         <v>322</v>
       </c>
-      <c r="F138" s="45" t="s">
+      <c r="F138" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="G138" s="44" t="s">
+      <c r="G138" s="58" t="s">
         <v>38</v>
       </c>
       <c r="H138" s="12" t="s">
@@ -11307,15 +11383,15 @@
       <c r="AA138" s="20"/>
     </row>
     <row r="139" spans="1:27" ht="91.5" hidden="1" customHeight="1">
-      <c r="A139" s="37"/>
-      <c r="B139" s="37"/>
+      <c r="A139" s="52"/>
+      <c r="B139" s="52"/>
       <c r="C139" s="9">
         <v>19</v>
       </c>
-      <c r="D139" s="37"/>
-      <c r="E139" s="37"/>
-      <c r="F139" s="37"/>
-      <c r="G139" s="37"/>
+      <c r="D139" s="52"/>
+      <c r="E139" s="52"/>
+      <c r="F139" s="52"/>
+      <c r="G139" s="52"/>
       <c r="H139" s="12" t="s">
         <v>325</v>
       </c>
@@ -11348,15 +11424,15 @@
       <c r="AA139" s="20"/>
     </row>
     <row r="140" spans="1:27" ht="150" customHeight="1">
-      <c r="A140" s="37"/>
-      <c r="B140" s="37"/>
+      <c r="A140" s="52"/>
+      <c r="B140" s="52"/>
       <c r="C140" s="9">
         <v>20</v>
       </c>
-      <c r="D140" s="37"/>
-      <c r="E140" s="37"/>
-      <c r="F140" s="37"/>
-      <c r="G140" s="37"/>
+      <c r="D140" s="52"/>
+      <c r="E140" s="52"/>
+      <c r="F140" s="52"/>
+      <c r="G140" s="52"/>
       <c r="H140" s="12" t="s">
         <v>41</v>
       </c>
@@ -11387,15 +11463,15 @@
       <c r="AA140" s="20"/>
     </row>
     <row r="141" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A141" s="37"/>
-      <c r="B141" s="37"/>
+      <c r="A141" s="52"/>
+      <c r="B141" s="52"/>
       <c r="C141" s="9">
         <v>21</v>
       </c>
-      <c r="D141" s="37"/>
-      <c r="E141" s="38"/>
-      <c r="F141" s="38"/>
-      <c r="G141" s="38"/>
+      <c r="D141" s="52"/>
+      <c r="E141" s="54"/>
+      <c r="F141" s="54"/>
+      <c r="G141" s="54"/>
       <c r="H141" s="12" t="s">
         <v>320</v>
       </c>
@@ -11428,12 +11504,12 @@
       <c r="AA141" s="20"/>
     </row>
     <row r="142" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A142" s="37"/>
-      <c r="B142" s="37"/>
+      <c r="A142" s="52"/>
+      <c r="B142" s="52"/>
       <c r="C142" s="9">
         <v>22</v>
       </c>
-      <c r="D142" s="37"/>
+      <c r="D142" s="52"/>
       <c r="E142" s="10" t="s">
         <v>342</v>
       </c>
@@ -11475,19 +11551,19 @@
       <c r="AA142" s="20"/>
     </row>
     <row r="143" spans="1:27" ht="150" customHeight="1">
-      <c r="A143" s="37"/>
-      <c r="B143" s="37"/>
+      <c r="A143" s="52"/>
+      <c r="B143" s="52"/>
       <c r="C143" s="9">
         <v>23</v>
       </c>
-      <c r="D143" s="37"/>
-      <c r="E143" s="51" t="s">
+      <c r="D143" s="52"/>
+      <c r="E143" s="61" t="s">
         <v>329</v>
       </c>
-      <c r="F143" s="45" t="s">
+      <c r="F143" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="G143" s="44" t="s">
+      <c r="G143" s="58" t="s">
         <v>24</v>
       </c>
       <c r="H143" s="12" t="s">
@@ -11497,7 +11573,7 @@
         <v>331</v>
       </c>
       <c r="J143" s="15"/>
-      <c r="K143" s="59"/>
+      <c r="K143" s="43"/>
       <c r="L143" s="17"/>
       <c r="M143" s="16"/>
       <c r="N143" s="18"/>
@@ -11520,15 +11596,15 @@
       <c r="AA143" s="20"/>
     </row>
     <row r="144" spans="1:27" ht="150" customHeight="1">
-      <c r="A144" s="37"/>
-      <c r="B144" s="37"/>
+      <c r="A144" s="52"/>
+      <c r="B144" s="52"/>
       <c r="C144" s="9">
         <v>24</v>
       </c>
-      <c r="D144" s="37"/>
-      <c r="E144" s="38"/>
-      <c r="F144" s="38"/>
-      <c r="G144" s="38"/>
+      <c r="D144" s="52"/>
+      <c r="E144" s="54"/>
+      <c r="F144" s="54"/>
+      <c r="G144" s="54"/>
       <c r="H144" s="12" t="s">
         <v>332</v>
       </c>
@@ -11536,7 +11612,7 @@
         <v>333</v>
       </c>
       <c r="J144" s="15"/>
-      <c r="K144" s="59"/>
+      <c r="K144" s="43"/>
       <c r="L144" s="17"/>
       <c r="M144" s="16"/>
       <c r="N144" s="18"/>
@@ -11559,19 +11635,19 @@
       <c r="AA144" s="20"/>
     </row>
     <row r="145" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A145" s="37"/>
-      <c r="B145" s="37"/>
+      <c r="A145" s="52"/>
+      <c r="B145" s="52"/>
       <c r="C145" s="9">
         <v>25</v>
       </c>
-      <c r="D145" s="37"/>
-      <c r="E145" s="51" t="s">
+      <c r="D145" s="52"/>
+      <c r="E145" s="61" t="s">
         <v>334</v>
       </c>
-      <c r="F145" s="45" t="s">
+      <c r="F145" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="G145" s="44" t="s">
+      <c r="G145" s="58" t="s">
         <v>38</v>
       </c>
       <c r="H145" s="12" t="s">
@@ -11606,15 +11682,15 @@
       <c r="AA145" s="20"/>
     </row>
     <row r="146" spans="1:27" ht="150" customHeight="1">
-      <c r="A146" s="37"/>
-      <c r="B146" s="37"/>
+      <c r="A146" s="52"/>
+      <c r="B146" s="52"/>
       <c r="C146" s="9">
         <v>26</v>
       </c>
-      <c r="D146" s="37"/>
-      <c r="E146" s="37"/>
-      <c r="F146" s="37"/>
-      <c r="G146" s="37"/>
+      <c r="D146" s="52"/>
+      <c r="E146" s="52"/>
+      <c r="F146" s="52"/>
+      <c r="G146" s="52"/>
       <c r="H146" s="12" t="s">
         <v>41</v>
       </c>
@@ -11645,15 +11721,15 @@
       <c r="AA146" s="20"/>
     </row>
     <row r="147" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A147" s="38"/>
-      <c r="B147" s="38"/>
+      <c r="A147" s="54"/>
+      <c r="B147" s="54"/>
       <c r="C147" s="9">
         <v>27</v>
       </c>
-      <c r="D147" s="38"/>
-      <c r="E147" s="38"/>
-      <c r="F147" s="38"/>
-      <c r="G147" s="38"/>
+      <c r="D147" s="54"/>
+      <c r="E147" s="54"/>
+      <c r="F147" s="54"/>
+      <c r="G147" s="54"/>
       <c r="H147" s="12" t="s">
         <v>320</v>
       </c>
@@ -11686,16 +11762,16 @@
       <c r="AA147" s="20"/>
     </row>
     <row r="148" spans="1:27" ht="150" customHeight="1">
-      <c r="A148" s="46" t="s">
+      <c r="A148" s="51" t="s">
         <v>345</v>
       </c>
-      <c r="B148" s="50" t="s">
+      <c r="B148" s="62" t="s">
         <v>346</v>
       </c>
       <c r="C148" s="9">
         <v>1</v>
       </c>
-      <c r="D148" s="46" t="s">
+      <c r="D148" s="51" t="s">
         <v>347</v>
       </c>
       <c r="E148" s="25" t="s">
@@ -11739,12 +11815,12 @@
       <c r="AA148" s="18"/>
     </row>
     <row r="149" spans="1:27" ht="150" customHeight="1">
-      <c r="A149" s="37"/>
-      <c r="B149" s="37"/>
+      <c r="A149" s="52"/>
+      <c r="B149" s="52"/>
       <c r="C149" s="9">
         <v>2</v>
       </c>
-      <c r="D149" s="37"/>
+      <c r="D149" s="52"/>
       <c r="E149" s="25" t="s">
         <v>351</v>
       </c>
@@ -11786,12 +11862,12 @@
       <c r="AA149" s="18"/>
     </row>
     <row r="150" spans="1:27" ht="150" customHeight="1">
-      <c r="A150" s="37"/>
-      <c r="B150" s="37"/>
+      <c r="A150" s="52"/>
+      <c r="B150" s="52"/>
       <c r="C150" s="9">
         <v>3</v>
       </c>
-      <c r="D150" s="37"/>
+      <c r="D150" s="52"/>
       <c r="E150" s="25" t="s">
         <v>353</v>
       </c>
@@ -11831,12 +11907,12 @@
       <c r="AA150" s="18"/>
     </row>
     <row r="151" spans="1:27" ht="150" customHeight="1">
-      <c r="A151" s="37"/>
-      <c r="B151" s="37"/>
+      <c r="A151" s="52"/>
+      <c r="B151" s="52"/>
       <c r="C151" s="9">
         <v>4</v>
       </c>
-      <c r="D151" s="37"/>
+      <c r="D151" s="52"/>
       <c r="E151" s="25" t="s">
         <v>355</v>
       </c>
@@ -11876,12 +11952,12 @@
       <c r="AA151" s="18"/>
     </row>
     <row r="152" spans="1:27" ht="150" customHeight="1">
-      <c r="A152" s="37"/>
-      <c r="B152" s="37"/>
+      <c r="A152" s="52"/>
+      <c r="B152" s="52"/>
       <c r="C152" s="9">
         <v>5</v>
       </c>
-      <c r="D152" s="37"/>
+      <c r="D152" s="52"/>
       <c r="E152" s="25" t="s">
         <v>357</v>
       </c>
@@ -11921,12 +11997,12 @@
       <c r="AA152" s="18"/>
     </row>
     <row r="153" spans="1:27" ht="150" customHeight="1">
-      <c r="A153" s="37"/>
-      <c r="B153" s="37"/>
+      <c r="A153" s="52"/>
+      <c r="B153" s="52"/>
       <c r="C153" s="9">
         <v>6</v>
       </c>
-      <c r="D153" s="37"/>
+      <c r="D153" s="52"/>
       <c r="E153" s="25" t="s">
         <v>359</v>
       </c>
@@ -11966,12 +12042,12 @@
       <c r="AA153" s="18"/>
     </row>
     <row r="154" spans="1:27" ht="150" customHeight="1">
-      <c r="A154" s="37"/>
-      <c r="B154" s="37"/>
+      <c r="A154" s="52"/>
+      <c r="B154" s="52"/>
       <c r="C154" s="9">
         <v>7</v>
       </c>
-      <c r="D154" s="37"/>
+      <c r="D154" s="52"/>
       <c r="E154" s="25" t="s">
         <v>361</v>
       </c>
@@ -12011,12 +12087,12 @@
       <c r="AA154" s="18"/>
     </row>
     <row r="155" spans="1:27" ht="150" customHeight="1">
-      <c r="A155" s="37"/>
-      <c r="B155" s="37"/>
+      <c r="A155" s="52"/>
+      <c r="B155" s="52"/>
       <c r="C155" s="9">
         <v>8</v>
       </c>
-      <c r="D155" s="37"/>
+      <c r="D155" s="52"/>
       <c r="E155" s="25" t="s">
         <v>363</v>
       </c>
@@ -12056,12 +12132,12 @@
       <c r="AA155" s="18"/>
     </row>
     <row r="156" spans="1:27" ht="150" customHeight="1">
-      <c r="A156" s="37"/>
-      <c r="B156" s="37"/>
+      <c r="A156" s="52"/>
+      <c r="B156" s="52"/>
       <c r="C156" s="9">
         <v>9</v>
       </c>
-      <c r="D156" s="37"/>
+      <c r="D156" s="52"/>
       <c r="E156" s="25" t="s">
         <v>365</v>
       </c>
@@ -12103,12 +12179,12 @@
       <c r="AA156" s="18"/>
     </row>
     <row r="157" spans="1:27" ht="150" customHeight="1">
-      <c r="A157" s="37"/>
-      <c r="B157" s="37"/>
+      <c r="A157" s="52"/>
+      <c r="B157" s="52"/>
       <c r="C157" s="9">
         <v>10</v>
       </c>
-      <c r="D157" s="37"/>
+      <c r="D157" s="52"/>
       <c r="E157" s="25" t="s">
         <v>367</v>
       </c>
@@ -12150,12 +12226,12 @@
       <c r="AA157" s="18"/>
     </row>
     <row r="158" spans="1:27" ht="150" customHeight="1">
-      <c r="A158" s="37"/>
-      <c r="B158" s="37"/>
+      <c r="A158" s="52"/>
+      <c r="B158" s="52"/>
       <c r="C158" s="9">
         <v>11</v>
       </c>
-      <c r="D158" s="37"/>
+      <c r="D158" s="52"/>
       <c r="E158" s="25" t="s">
         <v>370</v>
       </c>
@@ -12195,12 +12271,12 @@
       <c r="AA158" s="18"/>
     </row>
     <row r="159" spans="1:27" ht="150" customHeight="1">
-      <c r="A159" s="38"/>
-      <c r="B159" s="38"/>
+      <c r="A159" s="54"/>
+      <c r="B159" s="54"/>
       <c r="C159" s="9">
         <v>12</v>
       </c>
-      <c r="D159" s="38"/>
+      <c r="D159" s="54"/>
       <c r="E159" s="25" t="s">
         <v>372</v>
       </c>
@@ -12240,16 +12316,16 @@
       <c r="AA159" s="18"/>
     </row>
     <row r="160" spans="1:27" ht="150" customHeight="1">
-      <c r="A160" s="46" t="s">
+      <c r="A160" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="B160" s="50" t="s">
+      <c r="B160" s="62" t="s">
         <v>375</v>
       </c>
       <c r="C160" s="9">
         <v>1</v>
       </c>
-      <c r="D160" s="46" t="s">
+      <c r="D160" s="51" t="s">
         <v>376</v>
       </c>
       <c r="E160" s="25" t="s">
@@ -12291,12 +12367,12 @@
       <c r="AA160" s="18"/>
     </row>
     <row r="161" spans="1:27" ht="150" customHeight="1">
-      <c r="A161" s="37"/>
-      <c r="B161" s="37"/>
+      <c r="A161" s="52"/>
+      <c r="B161" s="52"/>
       <c r="C161" s="9">
         <v>2</v>
       </c>
-      <c r="D161" s="37"/>
+      <c r="D161" s="52"/>
       <c r="E161" s="25" t="s">
         <v>351</v>
       </c>
@@ -12336,12 +12412,12 @@
       <c r="AA161" s="18"/>
     </row>
     <row r="162" spans="1:27" ht="150" customHeight="1">
-      <c r="A162" s="37"/>
-      <c r="B162" s="37"/>
+      <c r="A162" s="52"/>
+      <c r="B162" s="52"/>
       <c r="C162" s="9">
         <v>3</v>
       </c>
-      <c r="D162" s="37"/>
+      <c r="D162" s="52"/>
       <c r="E162" s="25" t="s">
         <v>353</v>
       </c>
@@ -12381,12 +12457,12 @@
       <c r="AA162" s="18"/>
     </row>
     <row r="163" spans="1:27" ht="150" customHeight="1">
-      <c r="A163" s="37"/>
-      <c r="B163" s="37"/>
+      <c r="A163" s="52"/>
+      <c r="B163" s="52"/>
       <c r="C163" s="9">
         <v>4</v>
       </c>
-      <c r="D163" s="37"/>
+      <c r="D163" s="52"/>
       <c r="E163" s="25" t="s">
         <v>355</v>
       </c>
@@ -12426,12 +12502,12 @@
       <c r="AA163" s="18"/>
     </row>
     <row r="164" spans="1:27" ht="150" customHeight="1">
-      <c r="A164" s="37"/>
-      <c r="B164" s="37"/>
+      <c r="A164" s="52"/>
+      <c r="B164" s="52"/>
       <c r="C164" s="9">
         <v>5</v>
       </c>
-      <c r="D164" s="37"/>
+      <c r="D164" s="52"/>
       <c r="E164" s="25" t="s">
         <v>357</v>
       </c>
@@ -12471,12 +12547,12 @@
       <c r="AA164" s="18"/>
     </row>
     <row r="165" spans="1:27" ht="150" customHeight="1">
-      <c r="A165" s="37"/>
-      <c r="B165" s="37"/>
+      <c r="A165" s="52"/>
+      <c r="B165" s="52"/>
       <c r="C165" s="9">
         <v>6</v>
       </c>
-      <c r="D165" s="37"/>
+      <c r="D165" s="52"/>
       <c r="E165" s="25" t="s">
         <v>359</v>
       </c>
@@ -12516,12 +12592,12 @@
       <c r="AA165" s="18"/>
     </row>
     <row r="166" spans="1:27" ht="150" customHeight="1">
-      <c r="A166" s="37"/>
-      <c r="B166" s="37"/>
+      <c r="A166" s="52"/>
+      <c r="B166" s="52"/>
       <c r="C166" s="9">
         <v>7</v>
       </c>
-      <c r="D166" s="37"/>
+      <c r="D166" s="52"/>
       <c r="E166" s="25" t="s">
         <v>361</v>
       </c>
@@ -12561,12 +12637,12 @@
       <c r="AA166" s="18"/>
     </row>
     <row r="167" spans="1:27" ht="150" customHeight="1">
-      <c r="A167" s="38"/>
-      <c r="B167" s="38"/>
+      <c r="A167" s="54"/>
+      <c r="B167" s="54"/>
       <c r="C167" s="9">
         <v>8</v>
       </c>
-      <c r="D167" s="38"/>
+      <c r="D167" s="54"/>
       <c r="E167" s="25" t="s">
         <v>363</v>
       </c>
@@ -12627,19 +12703,19 @@
       <c r="R168" s="14"/>
     </row>
     <row r="169" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A169" s="46" t="s">
+      <c r="A169" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="B169" s="47" t="s">
+      <c r="B169" s="55" t="s">
         <v>387</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
       </c>
-      <c r="D169" s="46" t="s">
+      <c r="D169" s="51" t="s">
         <v>388</v>
       </c>
-      <c r="E169" s="46" t="s">
+      <c r="E169" s="51" t="s">
         <v>203</v>
       </c>
       <c r="F169" s="21" t="s">
@@ -12680,17 +12756,17 @@
       <c r="AA169" s="20"/>
     </row>
     <row r="170" spans="1:27" ht="150" customHeight="1">
-      <c r="A170" s="37"/>
-      <c r="B170" s="37"/>
+      <c r="A170" s="52"/>
+      <c r="B170" s="52"/>
       <c r="C170" s="9">
         <v>2</v>
       </c>
-      <c r="D170" s="37"/>
-      <c r="E170" s="37"/>
-      <c r="F170" s="47" t="s">
+      <c r="D170" s="52"/>
+      <c r="E170" s="52"/>
+      <c r="F170" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G170" s="48" t="s">
+      <c r="G170" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H170" s="16" t="s">
@@ -12723,15 +12799,15 @@
       <c r="AA170" s="20"/>
     </row>
     <row r="171" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A171" s="37"/>
-      <c r="B171" s="37"/>
+      <c r="A171" s="52"/>
+      <c r="B171" s="52"/>
       <c r="C171" s="9">
         <v>3</v>
       </c>
-      <c r="D171" s="37"/>
-      <c r="E171" s="38"/>
-      <c r="F171" s="38"/>
-      <c r="G171" s="38"/>
+      <c r="D171" s="52"/>
+      <c r="E171" s="54"/>
+      <c r="F171" s="54"/>
+      <c r="G171" s="54"/>
       <c r="H171" s="16" t="s">
         <v>44</v>
       </c>
@@ -12764,22 +12840,22 @@
       <c r="AA171" s="20"/>
     </row>
     <row r="172" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A172" s="37"/>
-      <c r="B172" s="37"/>
+      <c r="A172" s="52"/>
+      <c r="B172" s="52"/>
       <c r="C172" s="9">
         <v>4</v>
       </c>
-      <c r="D172" s="37"/>
-      <c r="E172" s="46" t="s">
+      <c r="D172" s="52"/>
+      <c r="E172" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F172" s="47" t="s">
+      <c r="F172" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G172" s="48" t="s">
+      <c r="G172" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="H172" s="46" t="s">
+      <c r="H172" s="51" t="s">
         <v>391</v>
       </c>
       <c r="I172" s="16" t="s">
@@ -12815,16 +12891,16 @@
       <c r="AA172" s="20"/>
     </row>
     <row r="173" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A173" s="37"/>
-      <c r="B173" s="37"/>
+      <c r="A173" s="52"/>
+      <c r="B173" s="52"/>
       <c r="C173" s="9">
         <v>5</v>
       </c>
-      <c r="D173" s="37"/>
-      <c r="E173" s="37"/>
-      <c r="F173" s="37"/>
-      <c r="G173" s="37"/>
-      <c r="H173" s="38"/>
+      <c r="D173" s="52"/>
+      <c r="E173" s="52"/>
+      <c r="F173" s="52"/>
+      <c r="G173" s="52"/>
+      <c r="H173" s="54"/>
       <c r="I173" s="16" t="s">
         <v>393</v>
       </c>
@@ -12858,16 +12934,16 @@
       <c r="AA173" s="20"/>
     </row>
     <row r="174" spans="1:27" ht="150" customHeight="1">
-      <c r="A174" s="37"/>
-      <c r="B174" s="37"/>
+      <c r="A174" s="52"/>
+      <c r="B174" s="52"/>
       <c r="C174" s="9">
         <v>6</v>
       </c>
-      <c r="D174" s="37"/>
-      <c r="E174" s="37"/>
-      <c r="F174" s="37"/>
-      <c r="G174" s="37"/>
-      <c r="H174" s="46" t="s">
+      <c r="D174" s="52"/>
+      <c r="E174" s="52"/>
+      <c r="F174" s="52"/>
+      <c r="G174" s="52"/>
+      <c r="H174" s="51" t="s">
         <v>41</v>
       </c>
       <c r="I174" s="16" t="s">
@@ -12901,16 +12977,16 @@
       <c r="AA174" s="20"/>
     </row>
     <row r="175" spans="1:27" ht="150" customHeight="1">
-      <c r="A175" s="37"/>
-      <c r="B175" s="37"/>
+      <c r="A175" s="52"/>
+      <c r="B175" s="52"/>
       <c r="C175" s="9">
         <v>7</v>
       </c>
-      <c r="D175" s="37"/>
-      <c r="E175" s="37"/>
-      <c r="F175" s="37"/>
-      <c r="G175" s="37"/>
-      <c r="H175" s="38"/>
+      <c r="D175" s="52"/>
+      <c r="E175" s="52"/>
+      <c r="F175" s="52"/>
+      <c r="G175" s="52"/>
+      <c r="H175" s="54"/>
       <c r="I175" s="16" t="s">
         <v>393</v>
       </c>
@@ -12942,16 +13018,16 @@
       <c r="AA175" s="20"/>
     </row>
     <row r="176" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A176" s="37"/>
-      <c r="B176" s="37"/>
+      <c r="A176" s="52"/>
+      <c r="B176" s="52"/>
       <c r="C176" s="9">
         <v>8</v>
       </c>
-      <c r="D176" s="37"/>
-      <c r="E176" s="37"/>
-      <c r="F176" s="37"/>
-      <c r="G176" s="37"/>
-      <c r="H176" s="49" t="s">
+      <c r="D176" s="52"/>
+      <c r="E176" s="52"/>
+      <c r="F176" s="52"/>
+      <c r="G176" s="52"/>
+      <c r="H176" s="60" t="s">
         <v>44</v>
       </c>
       <c r="I176" s="16" t="s">
@@ -12987,16 +13063,16 @@
       <c r="AA176" s="20"/>
     </row>
     <row r="177" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A177" s="37"/>
-      <c r="B177" s="37"/>
+      <c r="A177" s="52"/>
+      <c r="B177" s="52"/>
       <c r="C177" s="9">
         <v>9</v>
       </c>
-      <c r="D177" s="37"/>
-      <c r="E177" s="38"/>
-      <c r="F177" s="38"/>
-      <c r="G177" s="38"/>
-      <c r="H177" s="38"/>
+      <c r="D177" s="52"/>
+      <c r="E177" s="54"/>
+      <c r="F177" s="54"/>
+      <c r="G177" s="54"/>
+      <c r="H177" s="54"/>
       <c r="I177" s="16" t="s">
         <v>393</v>
       </c>
@@ -13030,19 +13106,19 @@
       <c r="AA177" s="20"/>
     </row>
     <row r="178" spans="1:27" ht="150" customHeight="1">
-      <c r="A178" s="37"/>
-      <c r="B178" s="37"/>
+      <c r="A178" s="52"/>
+      <c r="B178" s="52"/>
       <c r="C178" s="9">
         <v>10</v>
       </c>
-      <c r="D178" s="37"/>
-      <c r="E178" s="49" t="s">
+      <c r="D178" s="52"/>
+      <c r="E178" s="60" t="s">
         <v>219</v>
       </c>
-      <c r="F178" s="47" t="s">
+      <c r="F178" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G178" s="48" t="s">
+      <c r="G178" s="56" t="s">
         <v>24</v>
       </c>
       <c r="H178" s="16" t="s">
@@ -13052,7 +13128,7 @@
         <v>397</v>
       </c>
       <c r="J178" s="15"/>
-      <c r="K178" s="59"/>
+      <c r="K178" s="43"/>
       <c r="L178" s="17"/>
       <c r="M178" s="16"/>
       <c r="N178" s="18"/>
@@ -13077,15 +13153,15 @@
       <c r="AA178" s="20"/>
     </row>
     <row r="179" spans="1:27" ht="150" customHeight="1">
-      <c r="A179" s="37"/>
-      <c r="B179" s="37"/>
+      <c r="A179" s="52"/>
+      <c r="B179" s="52"/>
       <c r="C179" s="9">
         <v>11</v>
       </c>
-      <c r="D179" s="37"/>
-      <c r="E179" s="38"/>
-      <c r="F179" s="38"/>
-      <c r="G179" s="38"/>
+      <c r="D179" s="52"/>
+      <c r="E179" s="54"/>
+      <c r="F179" s="54"/>
+      <c r="G179" s="54"/>
       <c r="H179" s="16" t="s">
         <v>332</v>
       </c>
@@ -13093,7 +13169,7 @@
         <v>398</v>
       </c>
       <c r="J179" s="15"/>
-      <c r="K179" s="59"/>
+      <c r="K179" s="43"/>
       <c r="L179" s="17"/>
       <c r="M179" s="16"/>
       <c r="N179" s="18"/>
@@ -13118,22 +13194,22 @@
       <c r="AA179" s="20"/>
     </row>
     <row r="180" spans="1:27" ht="150" customHeight="1">
-      <c r="A180" s="37"/>
-      <c r="B180" s="37"/>
+      <c r="A180" s="52"/>
+      <c r="B180" s="52"/>
       <c r="C180" s="15">
         <v>12</v>
       </c>
-      <c r="D180" s="37"/>
-      <c r="E180" s="49" t="s">
+      <c r="D180" s="52"/>
+      <c r="E180" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="F180" s="47" t="s">
+      <c r="F180" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G180" s="48" t="s">
+      <c r="G180" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="H180" s="46" t="s">
+      <c r="H180" s="51" t="s">
         <v>96</v>
       </c>
       <c r="I180" s="16" t="s">
@@ -13165,16 +13241,16 @@
       <c r="AA180" s="20"/>
     </row>
     <row r="181" spans="1:27" ht="150" customHeight="1">
-      <c r="A181" s="37"/>
-      <c r="B181" s="37"/>
+      <c r="A181" s="52"/>
+      <c r="B181" s="52"/>
       <c r="C181" s="15">
         <v>13</v>
       </c>
-      <c r="D181" s="37"/>
-      <c r="E181" s="37"/>
-      <c r="F181" s="37"/>
-      <c r="G181" s="37"/>
-      <c r="H181" s="37"/>
+      <c r="D181" s="52"/>
+      <c r="E181" s="52"/>
+      <c r="F181" s="52"/>
+      <c r="G181" s="52"/>
+      <c r="H181" s="52"/>
       <c r="I181" s="16" t="s">
         <v>223</v>
       </c>
@@ -13204,16 +13280,16 @@
       <c r="AA181" s="20"/>
     </row>
     <row r="182" spans="1:27" ht="150" customHeight="1">
-      <c r="A182" s="37"/>
-      <c r="B182" s="37"/>
+      <c r="A182" s="52"/>
+      <c r="B182" s="52"/>
       <c r="C182" s="15">
         <v>14</v>
       </c>
-      <c r="D182" s="37"/>
-      <c r="E182" s="38"/>
-      <c r="F182" s="38"/>
-      <c r="G182" s="38"/>
-      <c r="H182" s="38"/>
+      <c r="D182" s="52"/>
+      <c r="E182" s="54"/>
+      <c r="F182" s="54"/>
+      <c r="G182" s="54"/>
+      <c r="H182" s="54"/>
       <c r="I182" s="16" t="s">
         <v>99</v>
       </c>
@@ -13243,13 +13319,13 @@
       <c r="AA182" s="20"/>
     </row>
     <row r="183" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A183" s="37"/>
-      <c r="B183" s="37"/>
+      <c r="A183" s="52"/>
+      <c r="B183" s="52"/>
       <c r="C183" s="9">
         <v>15</v>
       </c>
-      <c r="D183" s="37"/>
-      <c r="E183" s="46" t="s">
+      <c r="D183" s="52"/>
+      <c r="E183" s="51" t="s">
         <v>229</v>
       </c>
       <c r="F183" s="21" t="s">
@@ -13290,17 +13366,17 @@
       <c r="AA183" s="20"/>
     </row>
     <row r="184" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A184" s="37"/>
-      <c r="B184" s="37"/>
+      <c r="A184" s="52"/>
+      <c r="B184" s="52"/>
       <c r="C184" s="9">
         <v>16</v>
       </c>
-      <c r="D184" s="37"/>
-      <c r="E184" s="37"/>
-      <c r="F184" s="47" t="s">
+      <c r="D184" s="52"/>
+      <c r="E184" s="52"/>
+      <c r="F184" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G184" s="48" t="s">
+      <c r="G184" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H184" s="16" t="s">
@@ -13335,15 +13411,15 @@
       <c r="AA184" s="20"/>
     </row>
     <row r="185" spans="1:27" ht="150" customHeight="1">
-      <c r="A185" s="37"/>
-      <c r="B185" s="37"/>
+      <c r="A185" s="52"/>
+      <c r="B185" s="52"/>
       <c r="C185" s="9">
         <v>17</v>
       </c>
-      <c r="D185" s="37"/>
-      <c r="E185" s="37"/>
-      <c r="F185" s="37"/>
-      <c r="G185" s="37"/>
+      <c r="D185" s="52"/>
+      <c r="E185" s="52"/>
+      <c r="F185" s="52"/>
+      <c r="G185" s="52"/>
       <c r="H185" s="16" t="s">
         <v>41</v>
       </c>
@@ -13374,15 +13450,15 @@
       <c r="AA185" s="20"/>
     </row>
     <row r="186" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A186" s="38"/>
-      <c r="B186" s="38"/>
+      <c r="A186" s="54"/>
+      <c r="B186" s="54"/>
       <c r="C186" s="9">
         <v>18</v>
       </c>
-      <c r="D186" s="38"/>
-      <c r="E186" s="38"/>
-      <c r="F186" s="38"/>
-      <c r="G186" s="38"/>
+      <c r="D186" s="54"/>
+      <c r="E186" s="54"/>
+      <c r="F186" s="54"/>
+      <c r="G186" s="54"/>
       <c r="H186" s="16" t="s">
         <v>44</v>
       </c>
@@ -13415,19 +13491,19 @@
       <c r="AA186" s="20"/>
     </row>
     <row r="187" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A187" s="46" t="s">
+      <c r="A187" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="B187" s="47" t="s">
+      <c r="B187" s="55" t="s">
         <v>402</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
       </c>
-      <c r="D187" s="46" t="s">
+      <c r="D187" s="51" t="s">
         <v>403</v>
       </c>
-      <c r="E187" s="46" t="s">
+      <c r="E187" s="51" t="s">
         <v>203</v>
       </c>
       <c r="F187" s="21" t="s">
@@ -13468,17 +13544,17 @@
       <c r="AA187" s="20"/>
     </row>
     <row r="188" spans="1:27" ht="150" customHeight="1">
-      <c r="A188" s="37"/>
-      <c r="B188" s="37"/>
+      <c r="A188" s="52"/>
+      <c r="B188" s="52"/>
       <c r="C188" s="9">
         <v>2</v>
       </c>
-      <c r="D188" s="37"/>
-      <c r="E188" s="37"/>
-      <c r="F188" s="47" t="s">
+      <c r="D188" s="52"/>
+      <c r="E188" s="52"/>
+      <c r="F188" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G188" s="48" t="s">
+      <c r="G188" s="56" t="s">
         <v>38</v>
       </c>
       <c r="H188" s="16" t="s">
@@ -13511,15 +13587,15 @@
       <c r="AA188" s="20"/>
     </row>
     <row r="189" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A189" s="37"/>
-      <c r="B189" s="37"/>
+      <c r="A189" s="52"/>
+      <c r="B189" s="52"/>
       <c r="C189" s="9">
         <v>3</v>
       </c>
-      <c r="D189" s="37"/>
-      <c r="E189" s="38"/>
-      <c r="F189" s="38"/>
-      <c r="G189" s="38"/>
+      <c r="D189" s="52"/>
+      <c r="E189" s="54"/>
+      <c r="F189" s="54"/>
+      <c r="G189" s="54"/>
       <c r="H189" s="16" t="s">
         <v>44</v>
       </c>
@@ -13552,22 +13628,22 @@
       <c r="AA189" s="20"/>
     </row>
     <row r="190" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A190" s="37"/>
-      <c r="B190" s="37"/>
+      <c r="A190" s="52"/>
+      <c r="B190" s="52"/>
       <c r="C190" s="9">
         <v>4</v>
       </c>
-      <c r="D190" s="37"/>
-      <c r="E190" s="46" t="s">
+      <c r="D190" s="52"/>
+      <c r="E190" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F190" s="47" t="s">
+      <c r="F190" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="G190" s="48" t="s">
+      <c r="G190" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="H190" s="46" t="s">
+      <c r="H190" s="51" t="s">
         <v>391</v>
       </c>
       <c r="I190" s="16" t="s">
@@ -13599,16 +13675,16 @@
       <c r="AA190" s="20"/>
     </row>
     <row r="191" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A191" s="37"/>
-      <c r="B191" s="37"/>
+      <c r="A191" s="52"/>
+      <c r="B191" s="52"/>
       <c r="C191" s="9">
         <v>5</v>
       </c>
-      <c r="D191" s="37"/>
-      <c r="E191" s="37"/>
-      <c r="F191" s="37"/>
-      <c r="G191" s="37"/>
-      <c r="H191" s="38"/>
+      <c r="D191" s="52"/>
+      <c r="E191" s="52"/>
+      <c r="F191" s="52"/>
+      <c r="G191" s="52"/>
+      <c r="H191" s="54"/>
       <c r="I191" s="16" t="s">
         <v>393</v>
       </c>
@@ -13638,16 +13714,16 @@
       <c r="AA191" s="20"/>
     </row>
     <row r="192" spans="1:27" ht="150" customHeight="1">
-      <c r="A192" s="37"/>
-      <c r="B192" s="37"/>
+      <c r="A192" s="52"/>
+      <c r="B192" s="52"/>
       <c r="C192" s="9">
         <v>6</v>
       </c>
-      <c r="D192" s="37"/>
-      <c r="E192" s="37"/>
-      <c r="F192" s="37"/>
-      <c r="G192" s="37"/>
-      <c r="H192" s="46" t="s">
+      <c r="D192" s="52"/>
+      <c r="E192" s="52"/>
+      <c r="F192" s="52"/>
+      <c r="G192" s="52"/>
+      <c r="H192" s="51" t="s">
         <v>41</v>
       </c>
       <c r="I192" s="16" t="s">
@@ -13677,16 +13753,16 @@
       <c r="AA192" s="20"/>
     </row>
     <row r="193" spans="1:27" ht="150" customHeight="1">
-      <c r="A193" s="37"/>
-      <c r="B193" s="37"/>
+      <c r="A193" s="52"/>
+      <c r="B193" s="52"/>
       <c r="C193" s="9">
         <v>7</v>
       </c>
-      <c r="D193" s="37"/>
-      <c r="E193" s="37"/>
-      <c r="F193" s="37"/>
-      <c r="G193" s="37"/>
-      <c r="H193" s="38"/>
+      <c r="D193" s="52"/>
+      <c r="E193" s="52"/>
+      <c r="F193" s="52"/>
+      <c r="G193" s="52"/>
+      <c r="H193" s="54"/>
       <c r="I193" s="16" t="s">
         <v>393</v>
       </c>
@@ -13714,16 +13790,16 @@
       <c r="AA193" s="20"/>
     </row>
     <row r="194" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A194" s="37"/>
-      <c r="B194" s="37"/>
+      <c r="A194" s="52"/>
+      <c r="B194" s="52"/>
       <c r="C194" s="9">
         <v>8</v>
       </c>
-      <c r="D194" s="37"/>
-      <c r="E194" s="37"/>
-      <c r="F194" s="37"/>
-      <c r="G194" s="37"/>
-      <c r="H194" s="46" t="s">
+      <c r="D194" s="52"/>
+      <c r="E194" s="52"/>
+      <c r="F194" s="52"/>
+      <c r="G194" s="52"/>
+      <c r="H194" s="51" t="s">
         <v>44</v>
       </c>
       <c r="I194" s="16" t="s">
@@ -13755,16 +13831,16 @@
       <c r="AA194" s="20"/>
     </row>
     <row r="195" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A195" s="38"/>
-      <c r="B195" s="38"/>
+      <c r="A195" s="54"/>
+      <c r="B195" s="54"/>
       <c r="C195" s="9">
         <v>9</v>
       </c>
-      <c r="D195" s="38"/>
-      <c r="E195" s="38"/>
-      <c r="F195" s="38"/>
-      <c r="G195" s="38"/>
-      <c r="H195" s="38"/>
+      <c r="D195" s="54"/>
+      <c r="E195" s="54"/>
+      <c r="F195" s="54"/>
+      <c r="G195" s="54"/>
+      <c r="H195" s="54"/>
       <c r="I195" s="16" t="s">
         <v>393</v>
       </c>
@@ -13815,25 +13891,25 @@
       <c r="R196" s="14"/>
     </row>
     <row r="197" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A197" s="36" t="s">
+      <c r="A197" s="59" t="s">
         <v>406</v>
       </c>
-      <c r="B197" s="44" t="s">
+      <c r="B197" s="58" t="s">
         <v>407</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
       </c>
-      <c r="D197" s="36" t="s">
+      <c r="D197" s="59" t="s">
         <v>408</v>
       </c>
-      <c r="E197" s="36" t="s">
+      <c r="E197" s="59" t="s">
         <v>409</v>
       </c>
-      <c r="F197" s="45" t="s">
+      <c r="F197" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="G197" s="45" t="s">
+      <c r="G197" s="57" t="s">
         <v>24</v>
       </c>
       <c r="H197" s="10" t="s">
@@ -13861,15 +13937,15 @@
       </c>
     </row>
     <row r="198" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A198" s="37"/>
-      <c r="B198" s="37"/>
+      <c r="A198" s="52"/>
+      <c r="B198" s="52"/>
       <c r="C198" s="9">
         <v>2</v>
       </c>
-      <c r="D198" s="37"/>
-      <c r="E198" s="37"/>
-      <c r="F198" s="37"/>
-      <c r="G198" s="37"/>
+      <c r="D198" s="52"/>
+      <c r="E198" s="52"/>
+      <c r="F198" s="52"/>
+      <c r="G198" s="52"/>
       <c r="H198" s="12" t="s">
         <v>30</v>
       </c>
@@ -13895,15 +13971,15 @@
       </c>
     </row>
     <row r="199" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A199" s="37"/>
-      <c r="B199" s="37"/>
+      <c r="A199" s="52"/>
+      <c r="B199" s="52"/>
       <c r="C199" s="9">
         <v>3</v>
       </c>
-      <c r="D199" s="37"/>
-      <c r="E199" s="37"/>
-      <c r="F199" s="37"/>
-      <c r="G199" s="37"/>
+      <c r="D199" s="52"/>
+      <c r="E199" s="52"/>
+      <c r="F199" s="52"/>
+      <c r="G199" s="52"/>
       <c r="H199" s="10" t="s">
         <v>412</v>
       </c>
@@ -13929,15 +14005,15 @@
       </c>
     </row>
     <row r="200" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A200" s="37"/>
-      <c r="B200" s="37"/>
+      <c r="A200" s="52"/>
+      <c r="B200" s="52"/>
       <c r="C200" s="9">
         <v>4</v>
       </c>
-      <c r="D200" s="37"/>
-      <c r="E200" s="38"/>
-      <c r="F200" s="38"/>
-      <c r="G200" s="38"/>
+      <c r="D200" s="52"/>
+      <c r="E200" s="54"/>
+      <c r="F200" s="54"/>
+      <c r="G200" s="54"/>
       <c r="H200" s="12" t="s">
         <v>414</v>
       </c>
@@ -13963,12 +14039,12 @@
       </c>
     </row>
     <row r="201" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A201" s="37"/>
-      <c r="B201" s="37"/>
+      <c r="A201" s="52"/>
+      <c r="B201" s="52"/>
       <c r="C201" s="9">
         <v>5</v>
       </c>
-      <c r="D201" s="37"/>
+      <c r="D201" s="52"/>
       <c r="E201" s="12" t="s">
         <v>416</v>
       </c>
@@ -14003,12 +14079,12 @@
       </c>
     </row>
     <row r="202" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A202" s="37"/>
-      <c r="B202" s="38"/>
+      <c r="A202" s="52"/>
+      <c r="B202" s="54"/>
       <c r="C202" s="9">
         <v>6</v>
       </c>
-      <c r="D202" s="38"/>
+      <c r="D202" s="54"/>
       <c r="E202" s="12" t="s">
         <v>418</v>
       </c>
@@ -14043,21 +14119,21 @@
       </c>
     </row>
     <row r="203" spans="1:27" ht="150" customHeight="1">
-      <c r="A203" s="37"/>
-      <c r="B203" s="44" t="s">
+      <c r="A203" s="52"/>
+      <c r="B203" s="58" t="s">
         <v>421</v>
       </c>
       <c r="C203" s="9">
         <v>1</v>
       </c>
-      <c r="D203" s="36" t="s">
+      <c r="D203" s="59" t="s">
         <v>422</v>
       </c>
-      <c r="E203" s="36" t="s">
+      <c r="E203" s="59" t="s">
         <v>423</v>
       </c>
-      <c r="F203" s="45"/>
-      <c r="G203" s="44" t="s">
+      <c r="F203" s="57"/>
+      <c r="G203" s="58" t="s">
         <v>38</v>
       </c>
       <c r="H203" s="12" t="s">
@@ -14083,15 +14159,15 @@
       </c>
     </row>
     <row r="204" spans="1:27" ht="150" customHeight="1">
-      <c r="A204" s="37"/>
-      <c r="B204" s="37"/>
+      <c r="A204" s="52"/>
+      <c r="B204" s="52"/>
       <c r="C204" s="9">
         <v>2</v>
       </c>
-      <c r="D204" s="37"/>
-      <c r="E204" s="37"/>
-      <c r="F204" s="37"/>
-      <c r="G204" s="37"/>
+      <c r="D204" s="52"/>
+      <c r="E204" s="52"/>
+      <c r="F204" s="52"/>
+      <c r="G204" s="52"/>
       <c r="H204" s="12" t="s">
         <v>41</v>
       </c>
@@ -14115,15 +14191,15 @@
       </c>
     </row>
     <row r="205" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A205" s="37"/>
-      <c r="B205" s="37"/>
+      <c r="A205" s="52"/>
+      <c r="B205" s="52"/>
       <c r="C205" s="9">
         <v>3</v>
       </c>
-      <c r="D205" s="37"/>
-      <c r="E205" s="38"/>
-      <c r="F205" s="38"/>
-      <c r="G205" s="38"/>
+      <c r="D205" s="52"/>
+      <c r="E205" s="54"/>
+      <c r="F205" s="54"/>
+      <c r="G205" s="54"/>
       <c r="H205" s="12" t="s">
         <v>44</v>
       </c>
@@ -14149,19 +14225,19 @@
       </c>
     </row>
     <row r="206" spans="1:27" ht="150" hidden="1" customHeight="1">
-      <c r="A206" s="37"/>
-      <c r="B206" s="37"/>
+      <c r="A206" s="52"/>
+      <c r="B206" s="52"/>
       <c r="C206" s="9">
         <v>4</v>
       </c>
-      <c r="D206" s="37"/>
-      <c r="E206" s="36" t="s">
+      <c r="D206" s="52"/>
+      <c r="E206" s="59" t="s">
         <v>426</v>
       </c>
-      <c r="F206" s="45" t="s">
+      <c r="F206" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="G206" s="45" t="s">
+      <c r="G206" s="57" t="s">
         <v>38</v>
       </c>
       <c r="H206" s="12" t="s">
@@ -14189,15 +14265,15 @@
       </c>
     </row>
     <row r="207" spans="1:27" ht="150" customHeight="1">
-      <c r="A207" s="37"/>
-      <c r="B207" s="37"/>
+      <c r="A207" s="52"/>
+      <c r="B207" s="52"/>
       <c r="C207" s="9">
         <v>5</v>
       </c>
-      <c r="D207" s="37"/>
-      <c r="E207" s="37"/>
-      <c r="F207" s="37"/>
-      <c r="G207" s="37"/>
+      <c r="D207" s="52"/>
+      <c r="E207" s="52"/>
+      <c r="F207" s="52"/>
+      <c r="G207" s="52"/>
       <c r="H207" s="12" t="s">
         <v>424</v>
       </c>
@@ -14221,15 +14297,15 @@
       </c>
     </row>
     <row r="208" spans="1:27" ht="150" customHeight="1">
-      <c r="A208" s="37"/>
-      <c r="B208" s="37"/>
+      <c r="A208" s="52"/>
+      <c r="B208" s="52"/>
       <c r="C208" s="9">
         <v>6</v>
       </c>
-      <c r="D208" s="37"/>
-      <c r="E208" s="37"/>
-      <c r="F208" s="37"/>
-      <c r="G208" s="37"/>
+      <c r="D208" s="52"/>
+      <c r="E208" s="52"/>
+      <c r="F208" s="52"/>
+      <c r="G208" s="52"/>
       <c r="H208" s="12" t="s">
         <v>430</v>
       </c>
@@ -14262,15 +14338,15 @@
       <c r="AA208" s="30"/>
     </row>
     <row r="209" spans="1:18" ht="150" customHeight="1">
-      <c r="A209" s="37"/>
-      <c r="B209" s="37"/>
+      <c r="A209" s="52"/>
+      <c r="B209" s="52"/>
       <c r="C209" s="9">
         <v>7</v>
       </c>
-      <c r="D209" s="37"/>
-      <c r="E209" s="37"/>
-      <c r="F209" s="37"/>
-      <c r="G209" s="37"/>
+      <c r="D209" s="52"/>
+      <c r="E209" s="52"/>
+      <c r="F209" s="52"/>
+      <c r="G209" s="52"/>
       <c r="H209" s="12" t="s">
         <v>41</v>
       </c>
@@ -14294,15 +14370,15 @@
       </c>
     </row>
     <row r="210" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A210" s="37"/>
-      <c r="B210" s="37"/>
+      <c r="A210" s="52"/>
+      <c r="B210" s="52"/>
       <c r="C210" s="9">
         <v>8</v>
       </c>
-      <c r="D210" s="37"/>
-      <c r="E210" s="37"/>
-      <c r="F210" s="37"/>
-      <c r="G210" s="37"/>
+      <c r="D210" s="52"/>
+      <c r="E210" s="52"/>
+      <c r="F210" s="52"/>
+      <c r="G210" s="52"/>
       <c r="H210" s="12" t="s">
         <v>44</v>
       </c>
@@ -14328,15 +14404,15 @@
       </c>
     </row>
     <row r="211" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A211" s="37"/>
-      <c r="B211" s="37"/>
+      <c r="A211" s="52"/>
+      <c r="B211" s="52"/>
       <c r="C211" s="9">
         <v>9</v>
       </c>
-      <c r="D211" s="37"/>
-      <c r="E211" s="37"/>
-      <c r="F211" s="38"/>
-      <c r="G211" s="38"/>
+      <c r="D211" s="52"/>
+      <c r="E211" s="52"/>
+      <c r="F211" s="54"/>
+      <c r="G211" s="54"/>
       <c r="H211" s="12" t="s">
         <v>433</v>
       </c>
@@ -14362,13 +14438,13 @@
       </c>
     </row>
     <row r="212" spans="1:18" ht="150" customHeight="1">
-      <c r="A212" s="37"/>
-      <c r="B212" s="37"/>
+      <c r="A212" s="52"/>
+      <c r="B212" s="52"/>
       <c r="C212" s="9">
         <v>10</v>
       </c>
-      <c r="D212" s="37"/>
-      <c r="E212" s="38"/>
+      <c r="D212" s="52"/>
+      <c r="E212" s="54"/>
       <c r="F212" s="14" t="s">
         <v>23</v>
       </c>
@@ -14382,7 +14458,7 @@
         <v>436</v>
       </c>
       <c r="J212" s="15"/>
-      <c r="K212" s="59"/>
+      <c r="K212" s="43"/>
       <c r="L212" s="17"/>
       <c r="M212" s="16"/>
       <c r="N212" s="18"/>
@@ -14398,13 +14474,13 @@
       </c>
     </row>
     <row r="213" spans="1:18" ht="150" customHeight="1">
-      <c r="A213" s="37"/>
-      <c r="B213" s="37"/>
+      <c r="A213" s="52"/>
+      <c r="B213" s="52"/>
       <c r="C213" s="9">
         <v>11</v>
       </c>
-      <c r="D213" s="37"/>
-      <c r="E213" s="36" t="s">
+      <c r="D213" s="52"/>
+      <c r="E213" s="59" t="s">
         <v>437</v>
       </c>
       <c r="F213" s="14" t="s">
@@ -14420,7 +14496,7 @@
         <v>429</v>
       </c>
       <c r="J213" s="15"/>
-      <c r="K213" s="59"/>
+      <c r="K213" s="43"/>
       <c r="L213" s="17"/>
       <c r="M213" s="16"/>
       <c r="N213" s="18"/>
@@ -14436,13 +14512,13 @@
       </c>
     </row>
     <row r="214" spans="1:18" ht="150" customHeight="1">
-      <c r="A214" s="37"/>
-      <c r="B214" s="37"/>
+      <c r="A214" s="52"/>
+      <c r="B214" s="52"/>
       <c r="C214" s="9">
         <v>12</v>
       </c>
-      <c r="D214" s="37"/>
-      <c r="E214" s="37"/>
+      <c r="D214" s="52"/>
+      <c r="E214" s="52"/>
       <c r="F214" s="14" t="s">
         <v>62</v>
       </c>
@@ -14456,7 +14532,7 @@
         <v>441</v>
       </c>
       <c r="J214" s="15"/>
-      <c r="K214" s="59"/>
+      <c r="K214" s="43"/>
       <c r="L214" s="17"/>
       <c r="M214" s="16"/>
       <c r="N214" s="18"/>
@@ -14472,13 +14548,13 @@
       </c>
     </row>
     <row r="215" spans="1:18" ht="150" customHeight="1">
-      <c r="A215" s="37"/>
-      <c r="B215" s="37"/>
+      <c r="A215" s="52"/>
+      <c r="B215" s="52"/>
       <c r="C215" s="9">
         <v>13</v>
       </c>
-      <c r="D215" s="37"/>
-      <c r="E215" s="37"/>
+      <c r="D215" s="52"/>
+      <c r="E215" s="52"/>
       <c r="F215" s="14" t="s">
         <v>62</v>
       </c>
@@ -14508,13 +14584,13 @@
       </c>
     </row>
     <row r="216" spans="1:18" ht="150" customHeight="1">
-      <c r="A216" s="37"/>
-      <c r="B216" s="37"/>
+      <c r="A216" s="52"/>
+      <c r="B216" s="52"/>
       <c r="C216" s="9">
         <v>14</v>
       </c>
-      <c r="D216" s="37"/>
-      <c r="E216" s="38"/>
+      <c r="D216" s="52"/>
+      <c r="E216" s="54"/>
       <c r="F216" s="14" t="s">
         <v>23</v>
       </c>
@@ -14544,13 +14620,13 @@
       </c>
     </row>
     <row r="217" spans="1:18" ht="150" customHeight="1">
-      <c r="A217" s="37"/>
-      <c r="B217" s="37"/>
+      <c r="A217" s="52"/>
+      <c r="B217" s="52"/>
       <c r="C217" s="9">
         <v>15</v>
       </c>
-      <c r="D217" s="37"/>
-      <c r="E217" s="36" t="s">
+      <c r="D217" s="52"/>
+      <c r="E217" s="59" t="s">
         <v>446</v>
       </c>
       <c r="F217" s="14" t="s">
@@ -14566,7 +14642,7 @@
         <v>429</v>
       </c>
       <c r="J217" s="15"/>
-      <c r="K217" s="59"/>
+      <c r="K217" s="43"/>
       <c r="L217" s="17"/>
       <c r="M217" s="16"/>
       <c r="N217" s="18"/>
@@ -14582,13 +14658,13 @@
       </c>
     </row>
     <row r="218" spans="1:18" ht="150" customHeight="1">
-      <c r="A218" s="37"/>
-      <c r="B218" s="37"/>
+      <c r="A218" s="52"/>
+      <c r="B218" s="52"/>
       <c r="C218" s="9">
         <v>16</v>
       </c>
-      <c r="D218" s="37"/>
-      <c r="E218" s="38"/>
+      <c r="D218" s="52"/>
+      <c r="E218" s="54"/>
       <c r="F218" s="14" t="s">
         <v>23</v>
       </c>
@@ -14618,12 +14694,12 @@
       </c>
     </row>
     <row r="219" spans="1:18" ht="150" customHeight="1">
-      <c r="A219" s="37"/>
-      <c r="B219" s="37"/>
+      <c r="A219" s="52"/>
+      <c r="B219" s="52"/>
       <c r="C219" s="9">
         <v>17</v>
       </c>
-      <c r="D219" s="37"/>
+      <c r="D219" s="52"/>
       <c r="E219" s="31" t="s">
         <v>450</v>
       </c>
@@ -14656,22 +14732,22 @@
       </c>
     </row>
     <row r="220" spans="1:18" ht="150" customHeight="1">
-      <c r="A220" s="37"/>
-      <c r="B220" s="37"/>
+      <c r="A220" s="52"/>
+      <c r="B220" s="52"/>
       <c r="C220" s="9">
         <v>18</v>
       </c>
-      <c r="D220" s="37"/>
-      <c r="E220" s="36" t="s">
+      <c r="D220" s="52"/>
+      <c r="E220" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="F220" s="45" t="s">
+      <c r="F220" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="G220" s="45" t="s">
+      <c r="G220" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="H220" s="36" t="s">
+      <c r="H220" s="59" t="s">
         <v>96</v>
       </c>
       <c r="I220" s="12" t="s">
@@ -14694,16 +14770,16 @@
       </c>
     </row>
     <row r="221" spans="1:18" ht="150" customHeight="1">
-      <c r="A221" s="37"/>
-      <c r="B221" s="37"/>
+      <c r="A221" s="52"/>
+      <c r="B221" s="52"/>
       <c r="C221" s="9">
         <v>19</v>
       </c>
-      <c r="D221" s="37"/>
-      <c r="E221" s="37"/>
-      <c r="F221" s="37"/>
-      <c r="G221" s="37"/>
-      <c r="H221" s="37"/>
+      <c r="D221" s="52"/>
+      <c r="E221" s="52"/>
+      <c r="F221" s="52"/>
+      <c r="G221" s="52"/>
+      <c r="H221" s="52"/>
       <c r="I221" s="12" t="s">
         <v>454</v>
       </c>
@@ -14724,16 +14800,16 @@
       </c>
     </row>
     <row r="222" spans="1:18" ht="150" customHeight="1">
-      <c r="A222" s="38"/>
-      <c r="B222" s="38"/>
+      <c r="A222" s="54"/>
+      <c r="B222" s="54"/>
       <c r="C222" s="9">
         <v>20</v>
       </c>
-      <c r="D222" s="38"/>
-      <c r="E222" s="38"/>
-      <c r="F222" s="38"/>
-      <c r="G222" s="38"/>
-      <c r="H222" s="38"/>
+      <c r="D222" s="54"/>
+      <c r="E222" s="54"/>
+      <c r="F222" s="54"/>
+      <c r="G222" s="54"/>
+      <c r="H222" s="54"/>
       <c r="I222" s="12" t="s">
         <v>99</v>
       </c>
@@ -14754,19 +14830,19 @@
       </c>
     </row>
     <row r="223" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A223" s="36" t="s">
+      <c r="A223" s="59" t="s">
         <v>455</v>
       </c>
-      <c r="B223" s="44" t="s">
+      <c r="B223" s="58" t="s">
         <v>456</v>
       </c>
       <c r="C223" s="9">
         <v>1</v>
       </c>
-      <c r="D223" s="36" t="s">
+      <c r="D223" s="59" t="s">
         <v>457</v>
       </c>
-      <c r="E223" s="36" t="s">
+      <c r="E223" s="59" t="s">
         <v>458</v>
       </c>
       <c r="F223" s="14" t="s">
@@ -14798,13 +14874,13 @@
       </c>
     </row>
     <row r="224" spans="1:18" ht="150" customHeight="1">
-      <c r="A224" s="37"/>
-      <c r="B224" s="37"/>
+      <c r="A224" s="52"/>
+      <c r="B224" s="52"/>
       <c r="C224" s="9">
         <v>2</v>
       </c>
-      <c r="D224" s="37"/>
-      <c r="E224" s="37"/>
+      <c r="D224" s="52"/>
+      <c r="E224" s="52"/>
       <c r="F224" s="14" t="s">
         <v>23</v>
       </c>
@@ -14818,7 +14894,7 @@
         <v>462</v>
       </c>
       <c r="J224" s="15"/>
-      <c r="K224" s="59"/>
+      <c r="K224" s="43"/>
       <c r="L224" s="17"/>
       <c r="M224" s="16"/>
       <c r="N224" s="18"/>
@@ -14832,13 +14908,13 @@
       </c>
     </row>
     <row r="225" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A225" s="37"/>
-      <c r="B225" s="38"/>
+      <c r="A225" s="52"/>
+      <c r="B225" s="54"/>
       <c r="C225" s="9">
         <v>3</v>
       </c>
-      <c r="D225" s="37"/>
-      <c r="E225" s="38"/>
+      <c r="D225" s="52"/>
+      <c r="E225" s="54"/>
       <c r="F225" s="14" t="s">
         <v>23</v>
       </c>
@@ -14868,15 +14944,15 @@
       </c>
     </row>
     <row r="226" spans="1:18" ht="150" customHeight="1">
-      <c r="A226" s="37"/>
-      <c r="B226" s="44" t="s">
+      <c r="A226" s="52"/>
+      <c r="B226" s="58" t="s">
         <v>465</v>
       </c>
       <c r="C226" s="9">
         <v>1</v>
       </c>
-      <c r="D226" s="37"/>
-      <c r="E226" s="36" t="s">
+      <c r="D226" s="52"/>
+      <c r="E226" s="59" t="s">
         <v>466</v>
       </c>
       <c r="F226" s="14" t="s">
@@ -14892,7 +14968,7 @@
         <v>468</v>
       </c>
       <c r="J226" s="15"/>
-      <c r="K226" s="59"/>
+      <c r="K226" s="43"/>
       <c r="L226" s="17"/>
       <c r="M226" s="16"/>
       <c r="N226" s="18"/>
@@ -14906,13 +14982,13 @@
       </c>
     </row>
     <row r="227" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A227" s="37"/>
-      <c r="B227" s="37"/>
+      <c r="A227" s="52"/>
+      <c r="B227" s="52"/>
       <c r="C227" s="9">
         <v>2</v>
       </c>
-      <c r="D227" s="37"/>
-      <c r="E227" s="37"/>
+      <c r="D227" s="52"/>
+      <c r="E227" s="52"/>
       <c r="F227" s="14" t="s">
         <v>23</v>
       </c>
@@ -14928,7 +15004,7 @@
       <c r="J227" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K227" s="59"/>
+      <c r="K227" s="43"/>
       <c r="L227" s="17"/>
       <c r="M227" s="16"/>
       <c r="N227" s="18"/>
@@ -14942,13 +15018,13 @@
       </c>
     </row>
     <row r="228" spans="1:18" ht="150" customHeight="1">
-      <c r="A228" s="37"/>
-      <c r="B228" s="37"/>
+      <c r="A228" s="52"/>
+      <c r="B228" s="52"/>
       <c r="C228" s="9">
         <v>3</v>
       </c>
-      <c r="D228" s="37"/>
-      <c r="E228" s="37"/>
+      <c r="D228" s="52"/>
+      <c r="E228" s="52"/>
       <c r="F228" s="14" t="s">
         <v>23</v>
       </c>
@@ -14962,7 +15038,7 @@
         <v>472</v>
       </c>
       <c r="J228" s="15"/>
-      <c r="K228" s="59"/>
+      <c r="K228" s="43"/>
       <c r="L228" s="17"/>
       <c r="M228" s="16"/>
       <c r="N228" s="18"/>
@@ -14976,13 +15052,13 @@
       </c>
     </row>
     <row r="229" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A229" s="37"/>
-      <c r="B229" s="37"/>
+      <c r="A229" s="52"/>
+      <c r="B229" s="52"/>
       <c r="C229" s="9">
         <v>4</v>
       </c>
-      <c r="D229" s="37"/>
-      <c r="E229" s="37"/>
+      <c r="D229" s="52"/>
+      <c r="E229" s="52"/>
       <c r="F229" s="14" t="s">
         <v>23</v>
       </c>
@@ -14998,7 +15074,7 @@
       <c r="J229" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K229" s="59"/>
+      <c r="K229" s="43"/>
       <c r="L229" s="17"/>
       <c r="M229" s="16"/>
       <c r="N229" s="18"/>
@@ -15012,13 +15088,13 @@
       </c>
     </row>
     <row r="230" spans="1:18" ht="150" customHeight="1">
-      <c r="A230" s="37"/>
-      <c r="B230" s="37"/>
+      <c r="A230" s="52"/>
+      <c r="B230" s="52"/>
       <c r="C230" s="9">
         <v>5</v>
       </c>
-      <c r="D230" s="37"/>
-      <c r="E230" s="37"/>
+      <c r="D230" s="52"/>
+      <c r="E230" s="52"/>
       <c r="F230" s="14" t="s">
         <v>23</v>
       </c>
@@ -15032,7 +15108,7 @@
         <v>474</v>
       </c>
       <c r="J230" s="15"/>
-      <c r="K230" s="59"/>
+      <c r="K230" s="43"/>
       <c r="L230" s="17"/>
       <c r="M230" s="16"/>
       <c r="N230" s="18"/>
@@ -15046,13 +15122,13 @@
       </c>
     </row>
     <row r="231" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A231" s="37"/>
-      <c r="B231" s="37"/>
+      <c r="A231" s="52"/>
+      <c r="B231" s="52"/>
       <c r="C231" s="9">
         <v>6</v>
       </c>
-      <c r="D231" s="37"/>
-      <c r="E231" s="37"/>
+      <c r="D231" s="52"/>
+      <c r="E231" s="52"/>
       <c r="F231" s="14" t="s">
         <v>23</v>
       </c>
@@ -15068,7 +15144,7 @@
       <c r="J231" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K231" s="59"/>
+      <c r="K231" s="43"/>
       <c r="L231" s="17"/>
       <c r="M231" s="16"/>
       <c r="N231" s="18"/>
@@ -15082,13 +15158,13 @@
       </c>
     </row>
     <row r="232" spans="1:18" ht="150" customHeight="1">
-      <c r="A232" s="37"/>
-      <c r="B232" s="37"/>
+      <c r="A232" s="52"/>
+      <c r="B232" s="52"/>
       <c r="C232" s="9">
         <v>7</v>
       </c>
-      <c r="D232" s="37"/>
-      <c r="E232" s="37"/>
+      <c r="D232" s="52"/>
+      <c r="E232" s="52"/>
       <c r="F232" s="14" t="s">
         <v>23</v>
       </c>
@@ -15102,7 +15178,7 @@
         <v>477</v>
       </c>
       <c r="J232" s="15"/>
-      <c r="K232" s="59"/>
+      <c r="K232" s="43"/>
       <c r="L232" s="17"/>
       <c r="M232" s="16"/>
       <c r="N232" s="18"/>
@@ -15116,13 +15192,13 @@
       </c>
     </row>
     <row r="233" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A233" s="37"/>
-      <c r="B233" s="37"/>
+      <c r="A233" s="52"/>
+      <c r="B233" s="52"/>
       <c r="C233" s="9">
         <v>8</v>
       </c>
-      <c r="D233" s="37"/>
-      <c r="E233" s="37"/>
+      <c r="D233" s="52"/>
+      <c r="E233" s="52"/>
       <c r="F233" s="14" t="s">
         <v>23</v>
       </c>
@@ -15138,7 +15214,7 @@
       <c r="J233" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K233" s="59"/>
+      <c r="K233" s="43"/>
       <c r="L233" s="17"/>
       <c r="M233" s="16"/>
       <c r="N233" s="18"/>
@@ -15152,13 +15228,13 @@
       </c>
     </row>
     <row r="234" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A234" s="38"/>
-      <c r="B234" s="38"/>
+      <c r="A234" s="54"/>
+      <c r="B234" s="54"/>
       <c r="C234" s="9">
         <v>9</v>
       </c>
-      <c r="D234" s="38"/>
-      <c r="E234" s="38"/>
+      <c r="D234" s="54"/>
+      <c r="E234" s="54"/>
       <c r="F234" s="14" t="s">
         <v>23</v>
       </c>
@@ -15174,7 +15250,7 @@
       <c r="J234" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K234" s="59"/>
+      <c r="K234" s="43"/>
       <c r="L234" s="17"/>
       <c r="M234" s="16"/>
       <c r="N234" s="18"/>
@@ -15188,19 +15264,19 @@
       </c>
     </row>
     <row r="235" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A235" s="36" t="s">
+      <c r="A235" s="59" t="s">
         <v>481</v>
       </c>
-      <c r="B235" s="45" t="s">
+      <c r="B235" s="57" t="s">
         <v>482</v>
       </c>
       <c r="C235" s="9">
         <v>1</v>
       </c>
-      <c r="D235" s="36" t="s">
+      <c r="D235" s="59" t="s">
         <v>483</v>
       </c>
-      <c r="E235" s="36" t="s">
+      <c r="E235" s="59" t="s">
         <v>484</v>
       </c>
       <c r="F235" s="14" t="s">
@@ -15218,7 +15294,7 @@
       <c r="J235" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K235" s="59"/>
+      <c r="K235" s="43"/>
       <c r="L235" s="17"/>
       <c r="M235" s="16"/>
       <c r="N235" s="18"/>
@@ -15232,13 +15308,13 @@
       </c>
     </row>
     <row r="236" spans="1:18" ht="150" customHeight="1">
-      <c r="A236" s="37"/>
-      <c r="B236" s="37"/>
+      <c r="A236" s="52"/>
+      <c r="B236" s="52"/>
       <c r="C236" s="9">
         <v>2</v>
       </c>
-      <c r="D236" s="37"/>
-      <c r="E236" s="38"/>
+      <c r="D236" s="52"/>
+      <c r="E236" s="54"/>
       <c r="F236" s="14" t="s">
         <v>23</v>
       </c>
@@ -15252,7 +15328,7 @@
         <v>488</v>
       </c>
       <c r="J236" s="15"/>
-      <c r="K236" s="59"/>
+      <c r="K236" s="43"/>
       <c r="L236" s="17"/>
       <c r="M236" s="16"/>
       <c r="N236" s="18"/>
@@ -15266,13 +15342,13 @@
       </c>
     </row>
     <row r="237" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A237" s="37"/>
-      <c r="B237" s="37"/>
+      <c r="A237" s="52"/>
+      <c r="B237" s="52"/>
       <c r="C237" s="9">
         <v>3</v>
       </c>
-      <c r="D237" s="37"/>
-      <c r="E237" s="36" t="s">
+      <c r="D237" s="52"/>
+      <c r="E237" s="59" t="s">
         <v>489</v>
       </c>
       <c r="F237" s="14" t="s">
@@ -15290,7 +15366,7 @@
       <c r="J237" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K237" s="59"/>
+      <c r="K237" s="43"/>
       <c r="L237" s="17"/>
       <c r="M237" s="16"/>
       <c r="O237" s="19"/>
@@ -15303,13 +15379,13 @@
       </c>
     </row>
     <row r="238" spans="1:18" ht="150" customHeight="1">
-      <c r="A238" s="38"/>
-      <c r="B238" s="38"/>
+      <c r="A238" s="54"/>
+      <c r="B238" s="54"/>
       <c r="C238" s="9">
         <v>4</v>
       </c>
-      <c r="D238" s="38"/>
-      <c r="E238" s="38"/>
+      <c r="D238" s="54"/>
+      <c r="E238" s="54"/>
       <c r="F238" s="14" t="s">
         <v>23</v>
       </c>
@@ -15323,7 +15399,7 @@
         <v>488</v>
       </c>
       <c r="J238" s="15"/>
-      <c r="K238" s="59"/>
+      <c r="K238" s="43"/>
       <c r="L238" s="17"/>
       <c r="M238" s="16"/>
       <c r="O238" s="19"/>
@@ -15336,16 +15412,16 @@
       </c>
     </row>
     <row r="239" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A239" s="36" t="s">
+      <c r="A239" s="59" t="s">
         <v>492</v>
       </c>
-      <c r="B239" s="44" t="s">
+      <c r="B239" s="58" t="s">
         <v>493</v>
       </c>
       <c r="C239" s="9">
         <v>1</v>
       </c>
-      <c r="D239" s="36" t="s">
+      <c r="D239" s="59" t="s">
         <v>494</v>
       </c>
       <c r="E239" s="12" t="s">
@@ -15379,13 +15455,13 @@
       </c>
     </row>
     <row r="240" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A240" s="37"/>
-      <c r="B240" s="37"/>
+      <c r="A240" s="52"/>
+      <c r="B240" s="52"/>
       <c r="C240" s="9">
         <v>2</v>
       </c>
-      <c r="D240" s="37"/>
-      <c r="E240" s="36" t="s">
+      <c r="D240" s="52"/>
+      <c r="E240" s="59" t="s">
         <v>498</v>
       </c>
       <c r="F240" s="14" t="s">
@@ -15416,23 +15492,23 @@
       </c>
     </row>
     <row r="241" spans="1:18" ht="150" customHeight="1">
-      <c r="A241" s="37"/>
-      <c r="B241" s="37"/>
+      <c r="A241" s="52"/>
+      <c r="B241" s="52"/>
       <c r="C241" s="9">
         <v>3</v>
       </c>
-      <c r="D241" s="37"/>
-      <c r="E241" s="38"/>
+      <c r="D241" s="52"/>
+      <c r="E241" s="54"/>
       <c r="F241" s="14" t="s">
         <v>62</v>
       </c>
       <c r="G241" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H241" s="52" t="s">
+      <c r="H241" s="36" t="s">
         <v>500</v>
       </c>
-      <c r="I241" s="53" t="s">
+      <c r="I241" s="37" t="s">
         <v>497</v>
       </c>
       <c r="J241" s="15"/>
@@ -15449,12 +15525,12 @@
       </c>
     </row>
     <row r="242" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A242" s="37"/>
-      <c r="B242" s="37"/>
+      <c r="A242" s="52"/>
+      <c r="B242" s="52"/>
       <c r="C242" s="9">
         <v>4</v>
       </c>
-      <c r="D242" s="37"/>
+      <c r="D242" s="52"/>
       <c r="E242" s="12" t="s">
         <v>501</v>
       </c>
@@ -15486,13 +15562,13 @@
       </c>
     </row>
     <row r="243" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A243" s="37"/>
-      <c r="B243" s="37"/>
+      <c r="A243" s="52"/>
+      <c r="B243" s="52"/>
       <c r="C243" s="9">
         <v>5</v>
       </c>
-      <c r="D243" s="37"/>
-      <c r="E243" s="36" t="s">
+      <c r="D243" s="52"/>
+      <c r="E243" s="59" t="s">
         <v>502</v>
       </c>
       <c r="F243" s="14" t="s">
@@ -15523,23 +15599,23 @@
       </c>
     </row>
     <row r="244" spans="1:18" ht="150" customHeight="1">
-      <c r="A244" s="37"/>
-      <c r="B244" s="37"/>
+      <c r="A244" s="52"/>
+      <c r="B244" s="52"/>
       <c r="C244" s="9">
         <v>6</v>
       </c>
-      <c r="D244" s="37"/>
-      <c r="E244" s="38"/>
+      <c r="D244" s="52"/>
+      <c r="E244" s="54"/>
       <c r="F244" s="14" t="s">
         <v>62</v>
       </c>
       <c r="G244" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H244" s="52" t="s">
+      <c r="H244" s="36" t="s">
         <v>500</v>
       </c>
-      <c r="I244" s="53" t="s">
+      <c r="I244" s="37" t="s">
         <v>497</v>
       </c>
       <c r="J244" s="15"/>
@@ -15556,12 +15632,12 @@
       </c>
     </row>
     <row r="245" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A245" s="37"/>
-      <c r="B245" s="37"/>
+      <c r="A245" s="52"/>
+      <c r="B245" s="52"/>
       <c r="C245" s="9">
         <v>7</v>
       </c>
-      <c r="D245" s="37"/>
+      <c r="D245" s="52"/>
       <c r="E245" s="12" t="s">
         <v>503</v>
       </c>
@@ -15593,13 +15669,13 @@
       </c>
     </row>
     <row r="246" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A246" s="37"/>
-      <c r="B246" s="37"/>
+      <c r="A246" s="52"/>
+      <c r="B246" s="52"/>
       <c r="C246" s="9">
         <v>8</v>
       </c>
-      <c r="D246" s="37"/>
-      <c r="E246" s="36" t="s">
+      <c r="D246" s="52"/>
+      <c r="E246" s="59" t="s">
         <v>504</v>
       </c>
       <c r="F246" s="14" t="s">
@@ -15630,13 +15706,13 @@
       </c>
     </row>
     <row r="247" spans="1:18" ht="150" hidden="1" customHeight="1">
-      <c r="A247" s="37"/>
-      <c r="B247" s="37"/>
+      <c r="A247" s="52"/>
+      <c r="B247" s="52"/>
       <c r="C247" s="9">
         <v>9</v>
       </c>
-      <c r="D247" s="37"/>
-      <c r="E247" s="37"/>
+      <c r="D247" s="52"/>
+      <c r="E247" s="52"/>
       <c r="F247" s="14" t="s">
         <v>62</v>
       </c>
@@ -15665,23 +15741,23 @@
       </c>
     </row>
     <row r="248" spans="1:18" ht="150" customHeight="1">
-      <c r="A248" s="38"/>
-      <c r="B248" s="38"/>
+      <c r="A248" s="54"/>
+      <c r="B248" s="54"/>
       <c r="C248" s="9">
         <v>10</v>
       </c>
-      <c r="D248" s="38"/>
-      <c r="E248" s="38"/>
+      <c r="D248" s="54"/>
+      <c r="E248" s="54"/>
       <c r="F248" s="14" t="s">
         <v>62</v>
       </c>
       <c r="G248" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H248" s="52" t="s">
+      <c r="H248" s="36" t="s">
         <v>500</v>
       </c>
-      <c r="I248" s="53" t="s">
+      <c r="I248" s="37" t="s">
         <v>497</v>
       </c>
       <c r="J248" s="15"/>
@@ -15698,16 +15774,16 @@
       </c>
     </row>
     <row r="249" spans="1:18" ht="150" customHeight="1">
-      <c r="A249" s="36" t="s">
+      <c r="A249" s="59" t="s">
         <v>507</v>
       </c>
-      <c r="B249" s="44" t="s">
+      <c r="B249" s="58" t="s">
         <v>508</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
       </c>
-      <c r="D249" s="45" t="s">
+      <c r="D249" s="57" t="s">
         <v>509</v>
       </c>
       <c r="E249" s="12" t="s">
@@ -15739,13 +15815,13 @@
       </c>
     </row>
     <row r="250" spans="1:18" ht="150" customHeight="1">
-      <c r="A250" s="37"/>
-      <c r="B250" s="37"/>
+      <c r="A250" s="52"/>
+      <c r="B250" s="52"/>
       <c r="C250" s="9">
         <v>2</v>
       </c>
-      <c r="D250" s="37"/>
-      <c r="E250" s="36" t="s">
+      <c r="D250" s="52"/>
+      <c r="E250" s="59" t="s">
         <v>513</v>
       </c>
       <c r="F250" s="14" t="s">
@@ -15774,13 +15850,13 @@
       </c>
     </row>
     <row r="251" spans="1:18" ht="150" customHeight="1">
-      <c r="A251" s="37"/>
-      <c r="B251" s="37"/>
+      <c r="A251" s="52"/>
+      <c r="B251" s="52"/>
       <c r="C251" s="9">
         <v>3</v>
       </c>
-      <c r="D251" s="37"/>
-      <c r="E251" s="38"/>
+      <c r="D251" s="52"/>
+      <c r="E251" s="54"/>
       <c r="F251" s="14" t="s">
         <v>62</v>
       </c>
@@ -15807,13 +15883,13 @@
       </c>
     </row>
     <row r="252" spans="1:18" ht="150" customHeight="1">
-      <c r="A252" s="37"/>
-      <c r="B252" s="37"/>
+      <c r="A252" s="52"/>
+      <c r="B252" s="52"/>
       <c r="C252" s="9">
         <v>4</v>
       </c>
-      <c r="D252" s="37"/>
-      <c r="E252" s="36" t="s">
+      <c r="D252" s="52"/>
+      <c r="E252" s="59" t="s">
         <v>518</v>
       </c>
       <c r="F252" s="14" t="s">
@@ -15842,13 +15918,13 @@
       </c>
     </row>
     <row r="253" spans="1:18" ht="150" customHeight="1">
-      <c r="A253" s="37"/>
-      <c r="B253" s="37"/>
+      <c r="A253" s="52"/>
+      <c r="B253" s="52"/>
       <c r="C253" s="9">
         <v>5</v>
       </c>
-      <c r="D253" s="37"/>
-      <c r="E253" s="38"/>
+      <c r="D253" s="52"/>
+      <c r="E253" s="54"/>
       <c r="F253" s="14" t="s">
         <v>62</v>
       </c>
@@ -15875,13 +15951,13 @@
       </c>
     </row>
     <row r="254" spans="1:18" ht="150" customHeight="1">
-      <c r="A254" s="37"/>
-      <c r="B254" s="37"/>
+      <c r="A254" s="52"/>
+      <c r="B254" s="52"/>
       <c r="C254" s="9">
         <v>6</v>
       </c>
-      <c r="D254" s="37"/>
-      <c r="E254" s="36" t="s">
+      <c r="D254" s="52"/>
+      <c r="E254" s="59" t="s">
         <v>523</v>
       </c>
       <c r="F254" s="14" t="s">
@@ -15910,13 +15986,13 @@
       </c>
     </row>
     <row r="255" spans="1:18" ht="150" customHeight="1">
-      <c r="A255" s="37"/>
-      <c r="B255" s="37"/>
+      <c r="A255" s="52"/>
+      <c r="B255" s="52"/>
       <c r="C255" s="9">
         <v>7</v>
       </c>
-      <c r="D255" s="37"/>
-      <c r="E255" s="38"/>
+      <c r="D255" s="52"/>
+      <c r="E255" s="54"/>
       <c r="F255" s="14" t="s">
         <v>62</v>
       </c>
@@ -15943,12 +16019,12 @@
       </c>
     </row>
     <row r="256" spans="1:18" ht="150" customHeight="1">
-      <c r="A256" s="37"/>
-      <c r="B256" s="37"/>
+      <c r="A256" s="52"/>
+      <c r="B256" s="52"/>
       <c r="C256" s="9">
         <v>8</v>
       </c>
-      <c r="D256" s="37"/>
+      <c r="D256" s="52"/>
       <c r="E256" s="12" t="s">
         <v>526</v>
       </c>
@@ -15978,13 +16054,13 @@
       </c>
     </row>
     <row r="257" spans="1:18" ht="150" customHeight="1">
-      <c r="A257" s="37"/>
-      <c r="B257" s="37"/>
+      <c r="A257" s="52"/>
+      <c r="B257" s="52"/>
       <c r="C257" s="9">
         <v>9</v>
       </c>
-      <c r="D257" s="37"/>
-      <c r="E257" s="36" t="s">
+      <c r="D257" s="52"/>
+      <c r="E257" s="59" t="s">
         <v>529</v>
       </c>
       <c r="F257" s="14" t="s">
@@ -16013,13 +16089,13 @@
       </c>
     </row>
     <row r="258" spans="1:18" ht="150" customHeight="1">
-      <c r="A258" s="37"/>
-      <c r="B258" s="37"/>
+      <c r="A258" s="52"/>
+      <c r="B258" s="52"/>
       <c r="C258" s="9">
         <v>10</v>
       </c>
-      <c r="D258" s="37"/>
-      <c r="E258" s="38"/>
+      <c r="D258" s="52"/>
+      <c r="E258" s="54"/>
       <c r="F258" s="14" t="s">
         <v>62</v>
       </c>
@@ -16046,12 +16122,12 @@
       </c>
     </row>
     <row r="259" spans="1:18" ht="150" customHeight="1">
-      <c r="A259" s="37"/>
-      <c r="B259" s="37"/>
+      <c r="A259" s="52"/>
+      <c r="B259" s="52"/>
       <c r="C259" s="9">
         <v>11</v>
       </c>
-      <c r="D259" s="37"/>
+      <c r="D259" s="52"/>
       <c r="E259" s="10" t="s">
         <v>533</v>
       </c>
@@ -16081,13 +16157,13 @@
       </c>
     </row>
     <row r="260" spans="1:18" ht="150" customHeight="1">
-      <c r="A260" s="37"/>
-      <c r="B260" s="37"/>
+      <c r="A260" s="52"/>
+      <c r="B260" s="52"/>
       <c r="C260" s="9">
         <v>12</v>
       </c>
-      <c r="D260" s="37"/>
-      <c r="E260" s="36" t="s">
+      <c r="D260" s="52"/>
+      <c r="E260" s="59" t="s">
         <v>536</v>
       </c>
       <c r="F260" s="14" t="s">
@@ -16116,13 +16192,13 @@
       </c>
     </row>
     <row r="261" spans="1:18" ht="150" customHeight="1">
-      <c r="A261" s="37"/>
-      <c r="B261" s="37"/>
+      <c r="A261" s="52"/>
+      <c r="B261" s="52"/>
       <c r="C261" s="9">
         <v>13</v>
       </c>
-      <c r="D261" s="37"/>
-      <c r="E261" s="38"/>
+      <c r="D261" s="52"/>
+      <c r="E261" s="54"/>
       <c r="F261" s="14" t="s">
         <v>62</v>
       </c>
@@ -16149,12 +16225,12 @@
       </c>
     </row>
     <row r="262" spans="1:18" ht="150" customHeight="1">
-      <c r="A262" s="37"/>
-      <c r="B262" s="37"/>
+      <c r="A262" s="52"/>
+      <c r="B262" s="52"/>
       <c r="C262" s="9">
         <v>14</v>
       </c>
-      <c r="D262" s="37"/>
+      <c r="D262" s="52"/>
       <c r="E262" s="10" t="s">
         <v>540</v>
       </c>
@@ -16184,12 +16260,12 @@
       </c>
     </row>
     <row r="263" spans="1:18" ht="150" customHeight="1">
-      <c r="A263" s="37"/>
-      <c r="B263" s="37"/>
+      <c r="A263" s="52"/>
+      <c r="B263" s="52"/>
       <c r="C263" s="9">
         <v>15</v>
       </c>
-      <c r="D263" s="37"/>
+      <c r="D263" s="52"/>
       <c r="E263" s="10" t="s">
         <v>543</v>
       </c>
@@ -16219,12 +16295,12 @@
       </c>
     </row>
     <row r="264" spans="1:18" ht="150" customHeight="1">
-      <c r="A264" s="37"/>
-      <c r="B264" s="37"/>
+      <c r="A264" s="52"/>
+      <c r="B264" s="52"/>
       <c r="C264" s="9">
         <v>16</v>
       </c>
-      <c r="D264" s="37"/>
+      <c r="D264" s="52"/>
       <c r="E264" s="10" t="s">
         <v>546</v>
       </c>
@@ -16254,12 +16330,12 @@
       </c>
     </row>
     <row r="265" spans="1:18" ht="150" customHeight="1">
-      <c r="A265" s="37"/>
-      <c r="B265" s="37"/>
+      <c r="A265" s="52"/>
+      <c r="B265" s="52"/>
       <c r="C265" s="9">
         <v>17</v>
       </c>
-      <c r="D265" s="37"/>
+      <c r="D265" s="52"/>
       <c r="E265" s="10" t="s">
         <v>549</v>
       </c>
@@ -16289,12 +16365,12 @@
       </c>
     </row>
     <row r="266" spans="1:18" ht="150" customHeight="1">
-      <c r="A266" s="37"/>
-      <c r="B266" s="37"/>
+      <c r="A266" s="52"/>
+      <c r="B266" s="52"/>
       <c r="C266" s="9">
         <v>18</v>
       </c>
-      <c r="D266" s="37"/>
+      <c r="D266" s="52"/>
       <c r="E266" s="10" t="s">
         <v>552</v>
       </c>
@@ -16324,12 +16400,12 @@
       </c>
     </row>
     <row r="267" spans="1:18" ht="150" customHeight="1">
-      <c r="A267" s="37"/>
-      <c r="B267" s="37"/>
+      <c r="A267" s="52"/>
+      <c r="B267" s="52"/>
       <c r="C267" s="9">
         <v>19</v>
       </c>
-      <c r="D267" s="37"/>
+      <c r="D267" s="52"/>
       <c r="E267" s="10" t="s">
         <v>554</v>
       </c>
@@ -16359,12 +16435,12 @@
       </c>
     </row>
     <row r="268" spans="1:18" ht="150" customHeight="1">
-      <c r="A268" s="38"/>
-      <c r="B268" s="37"/>
+      <c r="A268" s="54"/>
+      <c r="B268" s="52"/>
       <c r="C268" s="9">
         <v>20</v>
       </c>
-      <c r="D268" s="37"/>
+      <c r="D268" s="52"/>
       <c r="E268" s="10" t="s">
         <v>557</v>
       </c>
@@ -16395,24 +16471,24 @@
     </row>
     <row r="269" spans="1:18" ht="150" customHeight="1">
       <c r="A269" s="31"/>
-      <c r="B269" s="38"/>
+      <c r="B269" s="54"/>
       <c r="C269" s="9">
         <v>21</v>
       </c>
-      <c r="D269" s="38"/>
-      <c r="E269" s="54" t="s">
+      <c r="D269" s="54"/>
+      <c r="E269" s="38" t="s">
         <v>560</v>
       </c>
-      <c r="F269" s="55" t="s">
+      <c r="F269" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="G269" s="56" t="s">
+      <c r="G269" s="40" t="s">
         <v>561</v>
       </c>
-      <c r="H269" s="54" t="s">
+      <c r="H269" s="38" t="s">
         <v>562</v>
       </c>
-      <c r="I269" s="54" t="s">
+      <c r="I269" s="38" t="s">
         <v>563</v>
       </c>
       <c r="J269" s="15"/>
@@ -16429,19 +16505,19 @@
       </c>
     </row>
     <row r="270" spans="1:18" ht="150" customHeight="1">
-      <c r="A270" s="39" t="s">
+      <c r="A270" s="63" t="s">
         <v>564</v>
       </c>
-      <c r="B270" s="42" t="s">
+      <c r="B270" s="65" t="s">
         <v>565</v>
       </c>
       <c r="C270" s="22">
         <v>1</v>
       </c>
-      <c r="D270" s="43" t="s">
+      <c r="D270" s="66" t="s">
         <v>566</v>
       </c>
-      <c r="E270" s="39" t="s">
+      <c r="E270" s="63" t="s">
         <v>567</v>
       </c>
       <c r="F270" s="24" t="s">
@@ -16473,13 +16549,13 @@
       </c>
     </row>
     <row r="271" spans="1:18" ht="150" customHeight="1">
-      <c r="A271" s="40"/>
-      <c r="B271" s="40"/>
+      <c r="A271" s="53"/>
+      <c r="B271" s="53"/>
       <c r="C271" s="22">
         <v>2</v>
       </c>
-      <c r="D271" s="41"/>
-      <c r="E271" s="41"/>
+      <c r="D271" s="64"/>
+      <c r="E271" s="64"/>
       <c r="F271" s="24" t="s">
         <v>23</v>
       </c>
@@ -16509,8 +16585,8 @@
       </c>
     </row>
     <row r="272" spans="1:18" ht="150" customHeight="1">
-      <c r="A272" s="41"/>
-      <c r="B272" s="41"/>
+      <c r="A272" s="64"/>
+      <c r="B272" s="64"/>
       <c r="C272" s="22">
         <v>3</v>
       </c>
@@ -16549,19 +16625,19 @@
       </c>
     </row>
     <row r="273" spans="1:18" ht="150" customHeight="1">
-      <c r="A273" s="36" t="s">
+      <c r="A273" s="59" t="s">
         <v>578</v>
       </c>
-      <c r="B273" s="44" t="s">
+      <c r="B273" s="58" t="s">
         <v>579</v>
       </c>
       <c r="C273" s="9">
         <v>1</v>
       </c>
-      <c r="D273" s="45" t="s">
+      <c r="D273" s="57" t="s">
         <v>580</v>
       </c>
-      <c r="E273" s="36" t="s">
+      <c r="E273" s="59" t="s">
         <v>581</v>
       </c>
       <c r="F273" s="14" t="s">
@@ -16590,13 +16666,13 @@
       </c>
     </row>
     <row r="274" spans="1:18" ht="150" customHeight="1">
-      <c r="A274" s="37"/>
-      <c r="B274" s="37"/>
+      <c r="A274" s="52"/>
+      <c r="B274" s="52"/>
       <c r="C274" s="9">
         <v>2</v>
       </c>
-      <c r="D274" s="37"/>
-      <c r="E274" s="38"/>
+      <c r="D274" s="52"/>
+      <c r="E274" s="54"/>
       <c r="F274" s="14" t="s">
         <v>62</v>
       </c>
@@ -16623,13 +16699,13 @@
       </c>
     </row>
     <row r="275" spans="1:18" ht="150" customHeight="1">
-      <c r="A275" s="37"/>
-      <c r="B275" s="37"/>
+      <c r="A275" s="52"/>
+      <c r="B275" s="52"/>
       <c r="C275" s="9">
         <v>3</v>
       </c>
-      <c r="D275" s="37"/>
-      <c r="E275" s="36" t="s">
+      <c r="D275" s="52"/>
+      <c r="E275" s="59" t="s">
         <v>586</v>
       </c>
       <c r="F275" s="14" t="s">
@@ -16638,10 +16714,10 @@
       <c r="G275" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H275" s="57" t="s">
+      <c r="H275" s="41" t="s">
         <v>587</v>
       </c>
-      <c r="I275" s="58" t="s">
+      <c r="I275" s="42" t="s">
         <v>588</v>
       </c>
       <c r="J275" s="15"/>
@@ -16658,13 +16734,13 @@
       </c>
     </row>
     <row r="276" spans="1:18" ht="150" customHeight="1">
-      <c r="A276" s="37"/>
-      <c r="B276" s="37"/>
+      <c r="A276" s="52"/>
+      <c r="B276" s="52"/>
       <c r="C276" s="9">
         <v>4</v>
       </c>
-      <c r="D276" s="37"/>
-      <c r="E276" s="37"/>
+      <c r="D276" s="52"/>
+      <c r="E276" s="52"/>
       <c r="F276" s="14" t="s">
         <v>62</v>
       </c>
@@ -16691,23 +16767,23 @@
       </c>
     </row>
     <row r="277" spans="1:18" ht="150" customHeight="1">
-      <c r="A277" s="37"/>
-      <c r="B277" s="37"/>
+      <c r="A277" s="52"/>
+      <c r="B277" s="52"/>
       <c r="C277" s="9">
         <v>5</v>
       </c>
-      <c r="D277" s="37"/>
-      <c r="E277" s="37"/>
+      <c r="D277" s="52"/>
+      <c r="E277" s="52"/>
       <c r="F277" s="14" t="s">
         <v>62</v>
       </c>
       <c r="G277" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H277" s="57" t="s">
+      <c r="H277" s="41" t="s">
         <v>591</v>
       </c>
-      <c r="I277" s="58" t="s">
+      <c r="I277" s="42" t="s">
         <v>588</v>
       </c>
       <c r="J277" s="15"/>
@@ -16724,13 +16800,13 @@
       </c>
     </row>
     <row r="278" spans="1:18" ht="150" customHeight="1">
-      <c r="A278" s="37"/>
-      <c r="B278" s="37"/>
+      <c r="A278" s="52"/>
+      <c r="B278" s="52"/>
       <c r="C278" s="9">
         <v>6</v>
       </c>
-      <c r="D278" s="37"/>
-      <c r="E278" s="38"/>
+      <c r="D278" s="52"/>
+      <c r="E278" s="54"/>
       <c r="F278" s="14" t="s">
         <v>62</v>
       </c>
@@ -16757,13 +16833,13 @@
       </c>
     </row>
     <row r="279" spans="1:18" ht="150" customHeight="1">
-      <c r="A279" s="37"/>
-      <c r="B279" s="37"/>
+      <c r="A279" s="52"/>
+      <c r="B279" s="52"/>
       <c r="C279" s="9">
         <v>7</v>
       </c>
-      <c r="D279" s="37"/>
-      <c r="E279" s="36" t="s">
+      <c r="D279" s="52"/>
+      <c r="E279" s="59" t="s">
         <v>592</v>
       </c>
       <c r="F279" s="14" t="s">
@@ -16792,13 +16868,13 @@
       </c>
     </row>
     <row r="280" spans="1:18" ht="150" customHeight="1">
-      <c r="A280" s="37"/>
-      <c r="B280" s="37"/>
+      <c r="A280" s="52"/>
+      <c r="B280" s="52"/>
       <c r="C280" s="9">
         <v>8</v>
       </c>
-      <c r="D280" s="37"/>
-      <c r="E280" s="37"/>
+      <c r="D280" s="52"/>
+      <c r="E280" s="52"/>
       <c r="F280" s="14" t="s">
         <v>62</v>
       </c>
@@ -16825,13 +16901,13 @@
       </c>
     </row>
     <row r="281" spans="1:18" ht="150" customHeight="1">
-      <c r="A281" s="37"/>
-      <c r="B281" s="37"/>
+      <c r="A281" s="52"/>
+      <c r="B281" s="52"/>
       <c r="C281" s="9">
         <v>8</v>
       </c>
-      <c r="D281" s="37"/>
-      <c r="E281" s="37"/>
+      <c r="D281" s="52"/>
+      <c r="E281" s="52"/>
       <c r="F281" s="14" t="s">
         <v>62</v>
       </c>
@@ -16858,13 +16934,13 @@
       </c>
     </row>
     <row r="282" spans="1:18" ht="150" customHeight="1">
-      <c r="A282" s="37"/>
-      <c r="B282" s="37"/>
+      <c r="A282" s="52"/>
+      <c r="B282" s="52"/>
       <c r="C282" s="9">
         <v>9</v>
       </c>
-      <c r="D282" s="37"/>
-      <c r="E282" s="37"/>
+      <c r="D282" s="52"/>
+      <c r="E282" s="52"/>
       <c r="F282" s="14" t="s">
         <v>62</v>
       </c>
@@ -16891,13 +16967,13 @@
       </c>
     </row>
     <row r="283" spans="1:18" ht="150" customHeight="1">
-      <c r="A283" s="37"/>
-      <c r="B283" s="37"/>
+      <c r="A283" s="52"/>
+      <c r="B283" s="52"/>
       <c r="C283" s="9">
         <v>10</v>
       </c>
-      <c r="D283" s="37"/>
-      <c r="E283" s="37"/>
+      <c r="D283" s="52"/>
+      <c r="E283" s="52"/>
       <c r="F283" s="14" t="s">
         <v>62</v>
       </c>
@@ -16924,13 +17000,13 @@
       </c>
     </row>
     <row r="284" spans="1:18" ht="150" customHeight="1">
-      <c r="A284" s="37"/>
-      <c r="B284" s="37"/>
+      <c r="A284" s="52"/>
+      <c r="B284" s="52"/>
       <c r="C284" s="9">
         <v>11</v>
       </c>
-      <c r="D284" s="37"/>
-      <c r="E284" s="37"/>
+      <c r="D284" s="52"/>
+      <c r="E284" s="52"/>
       <c r="F284" s="14" t="s">
         <v>62</v>
       </c>
@@ -16957,13 +17033,13 @@
       </c>
     </row>
     <row r="285" spans="1:18" ht="150" customHeight="1">
-      <c r="A285" s="37"/>
-      <c r="B285" s="37"/>
+      <c r="A285" s="52"/>
+      <c r="B285" s="52"/>
       <c r="C285" s="9">
         <v>11</v>
       </c>
-      <c r="D285" s="37"/>
-      <c r="E285" s="37"/>
+      <c r="D285" s="52"/>
+      <c r="E285" s="52"/>
       <c r="F285" s="14" t="s">
         <v>62</v>
       </c>
@@ -16990,13 +17066,13 @@
       </c>
     </row>
     <row r="286" spans="1:18" ht="150" customHeight="1">
-      <c r="A286" s="37"/>
-      <c r="B286" s="37"/>
+      <c r="A286" s="52"/>
+      <c r="B286" s="52"/>
       <c r="C286" s="9">
         <v>12</v>
       </c>
-      <c r="D286" s="37"/>
-      <c r="E286" s="38"/>
+      <c r="D286" s="52"/>
+      <c r="E286" s="54"/>
       <c r="F286" s="14" t="s">
         <v>62</v>
       </c>
@@ -17023,13 +17099,13 @@
       </c>
     </row>
     <row r="287" spans="1:18" ht="150" customHeight="1">
-      <c r="A287" s="37"/>
-      <c r="B287" s="37"/>
+      <c r="A287" s="52"/>
+      <c r="B287" s="52"/>
       <c r="C287" s="9">
         <v>13</v>
       </c>
-      <c r="D287" s="37"/>
-      <c r="E287" s="36" t="s">
+      <c r="D287" s="52"/>
+      <c r="E287" s="59" t="s">
         <v>602</v>
       </c>
       <c r="F287" s="14" t="s">
@@ -17058,13 +17134,13 @@
       </c>
     </row>
     <row r="288" spans="1:18" ht="150" customHeight="1">
-      <c r="A288" s="37"/>
-      <c r="B288" s="37"/>
+      <c r="A288" s="52"/>
+      <c r="B288" s="52"/>
       <c r="C288" s="9">
         <v>14</v>
       </c>
-      <c r="D288" s="37"/>
-      <c r="E288" s="37"/>
+      <c r="D288" s="52"/>
+      <c r="E288" s="52"/>
       <c r="F288" s="14" t="s">
         <v>62</v>
       </c>
@@ -17091,13 +17167,13 @@
       </c>
     </row>
     <row r="289" spans="1:18" ht="150" customHeight="1">
-      <c r="A289" s="37"/>
-      <c r="B289" s="37"/>
+      <c r="A289" s="52"/>
+      <c r="B289" s="52"/>
       <c r="C289" s="9">
         <v>15</v>
       </c>
-      <c r="D289" s="37"/>
-      <c r="E289" s="37"/>
+      <c r="D289" s="52"/>
+      <c r="E289" s="52"/>
       <c r="F289" s="14" t="s">
         <v>62</v>
       </c>
@@ -17124,13 +17200,13 @@
       </c>
     </row>
     <row r="290" spans="1:18" ht="150" customHeight="1">
-      <c r="A290" s="37"/>
-      <c r="B290" s="37"/>
+      <c r="A290" s="52"/>
+      <c r="B290" s="52"/>
       <c r="C290" s="9">
         <v>16</v>
       </c>
-      <c r="D290" s="37"/>
-      <c r="E290" s="38"/>
+      <c r="D290" s="52"/>
+      <c r="E290" s="54"/>
       <c r="F290" s="14" t="s">
         <v>62</v>
       </c>
@@ -17157,13 +17233,13 @@
       </c>
     </row>
     <row r="291" spans="1:18" ht="150" customHeight="1">
-      <c r="A291" s="37"/>
-      <c r="B291" s="37"/>
+      <c r="A291" s="52"/>
+      <c r="B291" s="52"/>
       <c r="C291" s="9">
         <v>17</v>
       </c>
-      <c r="D291" s="37"/>
-      <c r="E291" s="36" t="s">
+      <c r="D291" s="52"/>
+      <c r="E291" s="59" t="s">
         <v>609</v>
       </c>
       <c r="F291" s="14" t="s">
@@ -17192,13 +17268,13 @@
       </c>
     </row>
     <row r="292" spans="1:18" ht="150" customHeight="1">
-      <c r="A292" s="37"/>
-      <c r="B292" s="37"/>
+      <c r="A292" s="52"/>
+      <c r="B292" s="52"/>
       <c r="C292" s="9">
         <v>18</v>
       </c>
-      <c r="D292" s="37"/>
-      <c r="E292" s="37"/>
+      <c r="D292" s="52"/>
+      <c r="E292" s="52"/>
       <c r="F292" s="14" t="s">
         <v>62</v>
       </c>
@@ -17225,13 +17301,13 @@
       </c>
     </row>
     <row r="293" spans="1:18" ht="150" customHeight="1">
-      <c r="A293" s="37"/>
-      <c r="B293" s="37"/>
+      <c r="A293" s="52"/>
+      <c r="B293" s="52"/>
       <c r="C293" s="9">
         <v>19</v>
       </c>
-      <c r="D293" s="37"/>
-      <c r="E293" s="37"/>
+      <c r="D293" s="52"/>
+      <c r="E293" s="52"/>
       <c r="F293" s="14" t="s">
         <v>62</v>
       </c>
@@ -17258,13 +17334,13 @@
       </c>
     </row>
     <row r="294" spans="1:18" ht="150" customHeight="1">
-      <c r="A294" s="38"/>
-      <c r="B294" s="38"/>
+      <c r="A294" s="54"/>
+      <c r="B294" s="54"/>
       <c r="C294" s="9">
         <v>20</v>
       </c>
-      <c r="D294" s="38"/>
-      <c r="E294" s="38"/>
+      <c r="D294" s="54"/>
+      <c r="E294" s="54"/>
       <c r="F294" s="14" t="s">
         <v>62</v>
       </c>
@@ -25058,77 +25134,134 @@
     </row>
   </sheetData>
   <mergeCells count="223">
-    <mergeCell ref="A11:A19"/>
-    <mergeCell ref="B11:B19"/>
-    <mergeCell ref="D11:D19"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="D4:D10"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="E54:E56"/>
-    <mergeCell ref="H26:H28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="A31:A56"/>
-    <mergeCell ref="B31:B56"/>
-    <mergeCell ref="D31:D56"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="A20:A28"/>
-    <mergeCell ref="B20:B28"/>
-    <mergeCell ref="D20:D28"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="A57:A60"/>
-    <mergeCell ref="B57:B63"/>
-    <mergeCell ref="D57:D63"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A65:A81"/>
-    <mergeCell ref="B65:B81"/>
-    <mergeCell ref="D65:D81"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="E72:E74"/>
-    <mergeCell ref="F72:F74"/>
-    <mergeCell ref="G72:G74"/>
-    <mergeCell ref="E78:E80"/>
-    <mergeCell ref="F78:F80"/>
-    <mergeCell ref="G78:G80"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="E69:E71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="G70:G71"/>
-    <mergeCell ref="H78:H80"/>
-    <mergeCell ref="A82:A95"/>
-    <mergeCell ref="B82:B95"/>
-    <mergeCell ref="D82:D95"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="F83:F85"/>
-    <mergeCell ref="G83:G85"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="E89:E90"/>
-    <mergeCell ref="E91:E92"/>
-    <mergeCell ref="F91:F92"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="F93:F94"/>
-    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="E291:E294"/>
+    <mergeCell ref="A270:A272"/>
+    <mergeCell ref="B270:B272"/>
+    <mergeCell ref="D270:D271"/>
+    <mergeCell ref="E270:E271"/>
+    <mergeCell ref="A273:A294"/>
+    <mergeCell ref="B273:B294"/>
+    <mergeCell ref="D273:D294"/>
+    <mergeCell ref="E273:E274"/>
+    <mergeCell ref="E275:E278"/>
+    <mergeCell ref="E279:E286"/>
+    <mergeCell ref="A249:A268"/>
+    <mergeCell ref="B249:B269"/>
+    <mergeCell ref="D249:D269"/>
+    <mergeCell ref="E250:E251"/>
+    <mergeCell ref="E252:E253"/>
+    <mergeCell ref="E254:E255"/>
+    <mergeCell ref="E257:E258"/>
+    <mergeCell ref="E260:E261"/>
+    <mergeCell ref="E287:E290"/>
+    <mergeCell ref="A235:A238"/>
+    <mergeCell ref="B235:B238"/>
+    <mergeCell ref="D235:D238"/>
+    <mergeCell ref="E235:E236"/>
+    <mergeCell ref="E237:E238"/>
+    <mergeCell ref="A239:A248"/>
+    <mergeCell ref="B239:B248"/>
+    <mergeCell ref="D239:D248"/>
+    <mergeCell ref="E240:E241"/>
+    <mergeCell ref="E243:E244"/>
+    <mergeCell ref="E246:E248"/>
+    <mergeCell ref="A223:A234"/>
+    <mergeCell ref="B223:B225"/>
+    <mergeCell ref="D223:D234"/>
+    <mergeCell ref="E223:E225"/>
+    <mergeCell ref="B226:B234"/>
+    <mergeCell ref="E226:E234"/>
+    <mergeCell ref="D203:D222"/>
+    <mergeCell ref="E203:E205"/>
+    <mergeCell ref="F203:F205"/>
+    <mergeCell ref="E206:E212"/>
+    <mergeCell ref="F206:F211"/>
+    <mergeCell ref="E213:E216"/>
+    <mergeCell ref="E217:E218"/>
+    <mergeCell ref="E220:E222"/>
+    <mergeCell ref="H190:H191"/>
+    <mergeCell ref="H192:H193"/>
+    <mergeCell ref="H194:H195"/>
+    <mergeCell ref="A197:A222"/>
+    <mergeCell ref="B197:B202"/>
+    <mergeCell ref="D197:D202"/>
+    <mergeCell ref="E197:E200"/>
+    <mergeCell ref="F197:F200"/>
+    <mergeCell ref="G197:G200"/>
+    <mergeCell ref="B203:B222"/>
+    <mergeCell ref="A187:A195"/>
+    <mergeCell ref="B187:B195"/>
+    <mergeCell ref="D187:D195"/>
+    <mergeCell ref="E187:E189"/>
+    <mergeCell ref="F188:F189"/>
+    <mergeCell ref="G188:G189"/>
+    <mergeCell ref="E190:E195"/>
+    <mergeCell ref="F190:F195"/>
+    <mergeCell ref="G190:G195"/>
+    <mergeCell ref="F220:F222"/>
+    <mergeCell ref="G220:G222"/>
+    <mergeCell ref="H220:H222"/>
+    <mergeCell ref="G203:G205"/>
+    <mergeCell ref="G206:G211"/>
+    <mergeCell ref="H180:H182"/>
+    <mergeCell ref="E183:E186"/>
+    <mergeCell ref="F184:F186"/>
+    <mergeCell ref="G184:G186"/>
+    <mergeCell ref="H172:H173"/>
+    <mergeCell ref="H174:H175"/>
+    <mergeCell ref="H176:H177"/>
+    <mergeCell ref="E178:E179"/>
+    <mergeCell ref="F178:F179"/>
+    <mergeCell ref="G178:G179"/>
+    <mergeCell ref="E169:E171"/>
+    <mergeCell ref="F170:F171"/>
+    <mergeCell ref="G170:G171"/>
+    <mergeCell ref="E172:E177"/>
+    <mergeCell ref="F172:F177"/>
+    <mergeCell ref="G172:G177"/>
+    <mergeCell ref="A160:A167"/>
+    <mergeCell ref="B160:B167"/>
+    <mergeCell ref="D160:D167"/>
+    <mergeCell ref="A169:A186"/>
+    <mergeCell ref="B169:B186"/>
+    <mergeCell ref="D169:D186"/>
+    <mergeCell ref="E180:E182"/>
+    <mergeCell ref="F180:F182"/>
+    <mergeCell ref="G180:G182"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="E145:E147"/>
+    <mergeCell ref="F145:F147"/>
+    <mergeCell ref="G145:G147"/>
+    <mergeCell ref="A148:A159"/>
+    <mergeCell ref="B148:B159"/>
+    <mergeCell ref="D148:D159"/>
+    <mergeCell ref="G131:G133"/>
+    <mergeCell ref="D134:D147"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="F134:F137"/>
+    <mergeCell ref="G134:G137"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="G138:G141"/>
+    <mergeCell ref="E143:E144"/>
+    <mergeCell ref="F143:F144"/>
+    <mergeCell ref="A121:A147"/>
+    <mergeCell ref="B121:B147"/>
+    <mergeCell ref="D121:D133"/>
+    <mergeCell ref="E131:E133"/>
+    <mergeCell ref="F131:F133"/>
+    <mergeCell ref="E111:E112"/>
+    <mergeCell ref="G121:G124"/>
+    <mergeCell ref="E125:E128"/>
+    <mergeCell ref="F125:F128"/>
+    <mergeCell ref="G125:G128"/>
+    <mergeCell ref="E129:E130"/>
+    <mergeCell ref="F129:F130"/>
+    <mergeCell ref="G129:G130"/>
+    <mergeCell ref="E119:E120"/>
+    <mergeCell ref="F119:F120"/>
+    <mergeCell ref="E121:E124"/>
+    <mergeCell ref="F121:F124"/>
     <mergeCell ref="A96:A104"/>
     <mergeCell ref="B96:B104"/>
     <mergeCell ref="D96:D104"/>
@@ -25153,134 +25286,77 @@
     <mergeCell ref="F107:F108"/>
     <mergeCell ref="E109:E110"/>
     <mergeCell ref="F109:F110"/>
-    <mergeCell ref="E111:E112"/>
-    <mergeCell ref="G121:G124"/>
-    <mergeCell ref="E125:E128"/>
-    <mergeCell ref="F125:F128"/>
-    <mergeCell ref="G125:G128"/>
-    <mergeCell ref="E129:E130"/>
-    <mergeCell ref="F129:F130"/>
-    <mergeCell ref="G129:G130"/>
-    <mergeCell ref="E119:E120"/>
-    <mergeCell ref="F119:F120"/>
-    <mergeCell ref="E121:E124"/>
-    <mergeCell ref="F121:F124"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="E145:E147"/>
-    <mergeCell ref="F145:F147"/>
-    <mergeCell ref="G145:G147"/>
-    <mergeCell ref="A148:A159"/>
-    <mergeCell ref="B148:B159"/>
-    <mergeCell ref="D148:D159"/>
-    <mergeCell ref="G131:G133"/>
-    <mergeCell ref="D134:D147"/>
-    <mergeCell ref="E134:E137"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="G134:G137"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="F138:F141"/>
-    <mergeCell ref="G138:G141"/>
-    <mergeCell ref="E143:E144"/>
-    <mergeCell ref="F143:F144"/>
-    <mergeCell ref="A121:A147"/>
-    <mergeCell ref="B121:B147"/>
-    <mergeCell ref="D121:D133"/>
-    <mergeCell ref="E131:E133"/>
-    <mergeCell ref="F131:F133"/>
-    <mergeCell ref="E169:E171"/>
-    <mergeCell ref="F170:F171"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="E172:E177"/>
-    <mergeCell ref="F172:F177"/>
-    <mergeCell ref="G172:G177"/>
-    <mergeCell ref="A160:A167"/>
-    <mergeCell ref="B160:B167"/>
-    <mergeCell ref="D160:D167"/>
-    <mergeCell ref="A169:A186"/>
-    <mergeCell ref="B169:B186"/>
-    <mergeCell ref="D169:D186"/>
-    <mergeCell ref="E180:E182"/>
-    <mergeCell ref="F180:F182"/>
-    <mergeCell ref="G180:G182"/>
-    <mergeCell ref="H180:H182"/>
-    <mergeCell ref="E183:E186"/>
-    <mergeCell ref="F184:F186"/>
-    <mergeCell ref="G184:G186"/>
-    <mergeCell ref="H172:H173"/>
-    <mergeCell ref="H174:H175"/>
-    <mergeCell ref="H176:H177"/>
-    <mergeCell ref="E178:E179"/>
-    <mergeCell ref="F178:F179"/>
-    <mergeCell ref="G178:G179"/>
-    <mergeCell ref="H190:H191"/>
-    <mergeCell ref="H192:H193"/>
-    <mergeCell ref="H194:H195"/>
-    <mergeCell ref="A197:A222"/>
-    <mergeCell ref="B197:B202"/>
-    <mergeCell ref="D197:D202"/>
-    <mergeCell ref="E197:E200"/>
-    <mergeCell ref="F197:F200"/>
-    <mergeCell ref="G197:G200"/>
-    <mergeCell ref="B203:B222"/>
-    <mergeCell ref="A187:A195"/>
-    <mergeCell ref="B187:B195"/>
-    <mergeCell ref="D187:D195"/>
-    <mergeCell ref="E187:E189"/>
-    <mergeCell ref="F188:F189"/>
-    <mergeCell ref="G188:G189"/>
-    <mergeCell ref="E190:E195"/>
-    <mergeCell ref="F190:F195"/>
-    <mergeCell ref="G190:G195"/>
-    <mergeCell ref="F220:F222"/>
-    <mergeCell ref="G220:G222"/>
-    <mergeCell ref="H220:H222"/>
-    <mergeCell ref="A223:A234"/>
-    <mergeCell ref="B223:B225"/>
-    <mergeCell ref="D223:D234"/>
-    <mergeCell ref="E223:E225"/>
-    <mergeCell ref="B226:B234"/>
-    <mergeCell ref="E226:E234"/>
-    <mergeCell ref="D203:D222"/>
-    <mergeCell ref="E203:E205"/>
-    <mergeCell ref="F203:F205"/>
-    <mergeCell ref="G203:G205"/>
-    <mergeCell ref="E206:E212"/>
-    <mergeCell ref="F206:F211"/>
-    <mergeCell ref="G206:G211"/>
-    <mergeCell ref="E213:E216"/>
-    <mergeCell ref="E217:E218"/>
-    <mergeCell ref="E220:E222"/>
-    <mergeCell ref="A235:A238"/>
-    <mergeCell ref="B235:B238"/>
-    <mergeCell ref="D235:D238"/>
-    <mergeCell ref="E235:E236"/>
-    <mergeCell ref="E237:E238"/>
-    <mergeCell ref="A239:A248"/>
-    <mergeCell ref="B239:B248"/>
-    <mergeCell ref="D239:D248"/>
-    <mergeCell ref="E240:E241"/>
-    <mergeCell ref="E243:E244"/>
-    <mergeCell ref="E246:E248"/>
-    <mergeCell ref="A249:A268"/>
-    <mergeCell ref="B249:B269"/>
-    <mergeCell ref="D249:D269"/>
-    <mergeCell ref="E250:E251"/>
-    <mergeCell ref="E252:E253"/>
-    <mergeCell ref="E254:E255"/>
-    <mergeCell ref="E257:E258"/>
-    <mergeCell ref="E260:E261"/>
-    <mergeCell ref="E287:E290"/>
-    <mergeCell ref="E291:E294"/>
-    <mergeCell ref="A270:A272"/>
-    <mergeCell ref="B270:B272"/>
-    <mergeCell ref="D270:D271"/>
-    <mergeCell ref="E270:E271"/>
-    <mergeCell ref="A273:A294"/>
-    <mergeCell ref="B273:B294"/>
-    <mergeCell ref="D273:D294"/>
-    <mergeCell ref="E273:E274"/>
-    <mergeCell ref="E275:E278"/>
-    <mergeCell ref="E279:E286"/>
+    <mergeCell ref="H78:H80"/>
+    <mergeCell ref="A82:A95"/>
+    <mergeCell ref="B82:B95"/>
+    <mergeCell ref="D82:D95"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="F83:F85"/>
+    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="E89:E90"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="F91:F92"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="F93:F94"/>
+    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="F72:F74"/>
+    <mergeCell ref="G72:G74"/>
+    <mergeCell ref="E78:E80"/>
+    <mergeCell ref="F78:F80"/>
+    <mergeCell ref="G78:G80"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="E69:E71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="G70:G71"/>
+    <mergeCell ref="A57:A60"/>
+    <mergeCell ref="B57:B63"/>
+    <mergeCell ref="D57:D63"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A65:A81"/>
+    <mergeCell ref="B65:B81"/>
+    <mergeCell ref="D65:D81"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="E72:E74"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="E54:E56"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="A31:A56"/>
+    <mergeCell ref="B31:B56"/>
+    <mergeCell ref="D31:D56"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="A20:A28"/>
+    <mergeCell ref="B20:B28"/>
+    <mergeCell ref="D20:D28"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="A11:A19"/>
+    <mergeCell ref="B11:B19"/>
+    <mergeCell ref="D11:D19"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="D4:D10"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
   </mergeCells>
   <conditionalFormatting sqref="I3">
     <cfRule type="cellIs" dxfId="79" priority="1" stopIfTrue="1" operator="equal">
